--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Confidential\Gathering_Island\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B381250F-7A3B-4D38-BA07-B0CCAE25D8D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A81FA887-2CFB-44BD-B4CD-AB7B862AE8BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26295" yWindow="3945" windowWidth="19725" windowHeight="10830" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19380" yWindow="2265" windowWidth="19725" windowHeight="10830" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="events" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="49">
   <si>
     <t>event_id</t>
   </si>
@@ -164,6 +164,28 @@
   </si>
   <si>
     <t>AI 與開發者設計的網路社群活動，提供最新技術分享與討論</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中秋烤肉大會</t>
+  </si>
+  <si>
+    <t>台北大安森林公園</t>
+  </si>
+  <si>
+    <t>一起享受烤肉、月餅與賞月的夜晚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2037-09-10 18:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2037-09-05 23:59:59</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2037-09-01 12:17:38</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -248,7 +270,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -266,6 +288,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="22" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -546,7 +569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.625" style="1" customWidth="1"/>
@@ -749,6 +772,53 @@
         <v>41</v>
       </c>
     </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="2">
+        <v>8</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="2">
+        <v>50</v>
+      </c>
+      <c r="H6" s="2">
+        <v>200</v>
+      </c>
+      <c r="I6" s="2">
+        <v>10</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="7"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="7"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="7"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Confidential\Gathering_Island\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCreation\Web\Gathering_Island\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A81FA887-2CFB-44BD-B4CD-AB7B862AE8BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EABFD6E-9BEE-4331-86D2-0B73EF787666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19380" yWindow="2265" windowWidth="19725" windowHeight="10830" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="events" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="105">
   <si>
     <t>event_id</t>
   </si>
@@ -186,6 +186,214 @@
   </si>
   <si>
     <t>2037-09-01 12:17:38</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI 學習營</t>
+  </si>
+  <si>
+    <t>台中市軟體園區</t>
+  </si>
+  <si>
+    <t>藝術展覽</t>
+  </si>
+  <si>
+    <t>台北市美術館</t>
+  </si>
+  <si>
+    <t>北海道之旅</t>
+  </si>
+  <si>
+    <t>日本北海道</t>
+  </si>
+  <si>
+    <t>馬拉松賽</t>
+  </si>
+  <si>
+    <t>台南市安平區</t>
+  </si>
+  <si>
+    <t>電玩同樂會</t>
+  </si>
+  <si>
+    <t>新北市板橋電競館</t>
+  </si>
+  <si>
+    <t>美食嘉年華</t>
+  </si>
+  <si>
+    <t>花博公園</t>
+  </si>
+  <si>
+    <t>桌遊之夜</t>
+  </si>
+  <si>
+    <t>桃園市青年活動中心</t>
+  </si>
+  <si>
+    <t>創客工作坊</t>
+  </si>
+  <si>
+    <t>台北市創客基地</t>
+  </si>
+  <si>
+    <t>這是一場週末的歡樂派對</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2027-09-10 19:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2027-09-08 23:59:59</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-08-29 15:22:14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>知名樂團現場表演</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2028-09-20 18:30:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2028-09-15 23:59:59</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-08-30 14:12:19</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三日 AI 技術密集課程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2030-03-05 09:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2030-03-01 23:59:59</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-01-15 11:05:22</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>當代藝術家聯展</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2029-05-12 10:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2029-05-10 23:59:59</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-03-10 09:40:11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>五天四夜溫泉雪景之旅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2032-12-01 07:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2032-11-20 23:59:59</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-07-08 19:12:45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>年度城市馬拉松，歡迎全民參與</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-11-15 06:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-11-01 23:59:59</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-12-20 08:15:33</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多人線下遊戲交流賽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2035-07-22 13:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2035-07-15 23:59:59</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2027-09-02 20:45:01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>匯集世界各地的特色小吃</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2031-04-18 11:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2031-04-10 23:59:59</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-05-30 16:22:17</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一起體驗多款經典與新款桌遊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-10-05 18:30:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-09-30 23:59:59</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-08-21 10:08:55</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DIY 機械手臂入門實作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2036-08-25 09:30:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2036-08-20 23:59:59</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2027-10-12 17:31:09</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -810,11 +1018,385 @@
         <v>48</v>
       </c>
     </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="2">
+        <v>50</v>
+      </c>
+      <c r="H7" s="2">
+        <v>300</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D8" s="2">
+        <v>2</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="2">
+        <v>2000</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1200</v>
+      </c>
+      <c r="I8" s="2">
+        <v>2</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9" s="2">
+        <v>3</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="2">
+        <v>80</v>
+      </c>
+      <c r="H9" s="2">
+        <v>6000</v>
+      </c>
+      <c r="I9" s="2">
+        <v>3</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D10" s="2">
+        <v>4</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="2">
+        <v>500</v>
+      </c>
+      <c r="H10" s="2">
+        <v>300</v>
+      </c>
+      <c r="I10" s="2">
+        <v>4</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" s="2">
+        <v>5</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="2">
+        <v>30</v>
+      </c>
+      <c r="H11" s="2">
+        <v>35000</v>
+      </c>
+      <c r="I11" s="2">
+        <v>5</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>10</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D12" s="2">
+        <v>6</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="2">
+        <v>5000</v>
+      </c>
+      <c r="H12" s="2">
+        <v>800</v>
+      </c>
+      <c r="I12" s="2">
+        <v>6</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>11</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D13" s="2">
+        <v>7</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="2">
+        <v>100</v>
+      </c>
+      <c r="H13" s="2">
+        <v>200</v>
+      </c>
+      <c r="I13" s="2">
+        <v>7</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>12</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D14" s="2">
+        <v>8</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="2">
+        <v>1000</v>
+      </c>
+      <c r="H14" s="2">
+        <v>150</v>
+      </c>
+      <c r="I14" s="2">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="7"/>
+      <c r="A15" s="2">
+        <v>13</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D15" s="2">
+        <v>7</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="2">
+        <v>60</v>
+      </c>
+      <c r="H15" s="2">
+        <v>100</v>
+      </c>
+      <c r="I15" s="2">
+        <v>9</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="7"/>
+      <c r="A16" s="2">
+        <v>14</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D16" s="2">
+        <v>3</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="2">
+        <v>40</v>
+      </c>
+      <c r="H16" s="2">
+        <v>2000</v>
+      </c>
+      <c r="I16" s="2">
+        <v>10</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="7"/>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCreation\Web\Gathering_Island\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EABFD6E-9BEE-4331-86D2-0B73EF787666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3497A71-CE9F-4E74-ADBA-2805429257AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="257">
   <si>
     <t>event_id</t>
   </si>
@@ -394,6 +394,565 @@
   </si>
   <si>
     <t>2027-10-12 17:31:09</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>惠婷的狂歡派對</t>
+  </si>
+  <si>
+    <t>技術運動會</t>
+  </si>
+  <si>
+    <t>通過學習營</t>
+  </si>
+  <si>
+    <t>蘆洲市旅行團</t>
+  </si>
+  <si>
+    <t>這些藝術展</t>
+  </si>
+  <si>
+    <t>不過運動會</t>
+  </si>
+  <si>
+    <t>永康音樂祭</t>
+  </si>
+  <si>
+    <t>文章學習營</t>
+  </si>
+  <si>
+    <t>雅涵的狂歡派對</t>
+  </si>
+  <si>
+    <t>欣怡的狂歡派對</t>
+  </si>
+  <si>
+    <t>能夠學習營</t>
+  </si>
+  <si>
+    <t>蘆竹市美食節</t>
+  </si>
+  <si>
+    <t>首頁學習營</t>
+  </si>
+  <si>
+    <t>記者學習營</t>
+  </si>
+  <si>
+    <t>合作藝術展</t>
+  </si>
+  <si>
+    <t>已經遊戲大賽</t>
+  </si>
+  <si>
+    <t>電話學習營</t>
+  </si>
+  <si>
+    <t>工程特別活動</t>
+  </si>
+  <si>
+    <t>中心學習營</t>
+  </si>
+  <si>
+    <t>台東市旅行團</t>
+  </si>
+  <si>
+    <t>新竹音樂祭</t>
+  </si>
+  <si>
+    <t>最大藝術展</t>
+  </si>
+  <si>
+    <t>斗六美食節</t>
+  </si>
+  <si>
+    <t>提供運動會</t>
+  </si>
+  <si>
+    <t>建宏的狂歡派對</t>
+  </si>
+  <si>
+    <t>雅芳的狂歡派對</t>
+  </si>
+  <si>
+    <t>不是學習營</t>
+  </si>
+  <si>
+    <t>這樣特別活動</t>
+  </si>
+  <si>
+    <t>一起探索當地景點與文化，留下美好回憶。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2027-12-27 12:18:18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2027-12-14 12:18:18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-10-30 20:08:59</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>邀請好友共度瘋狂夜晚，享受音樂與舞蹈。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2029-12-23 08:01:38</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2029-12-09 08:01:38</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-09-02 17:08:17</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>各類競賽與運動活動，挑戰體能與團隊合作。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2028-06-09 07:57:01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2028-05-31 07:57:01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-11-18 13:42:02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>專業講師授課，幫助提升技能與知識。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2031-11-09 07:56:01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2031-11-01 07:56:01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-12-29 05:11:12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2027-06-26 12:42:52</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2027-06-09 12:42:52</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-05-31 10:19:32</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>展出新銳藝術家的作品，探索創意與靈感。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2027-07-03 08:21:52</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2027-06-23 08:21:52</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-01-18 01:11:16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2027-11-21 19:39:34</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2027-11-09 19:39:34</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-03-03 19:46:17</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>現場有多組樂團表演，帶來搖滾與流行音樂盛宴。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2030-01-25 10:51:27</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2030-01-03 10:51:27</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-03-25 11:59:33</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2030-03-30 00:26:12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2030-03-15 00:26:12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-06-27 03:44:39</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2033-09-22 06:30:45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2033-09-17 06:30:45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-04-24 01:44:53</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2028-05-26 22:27:40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2028-04-26 22:27:40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-05-01 18:20:04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2037-09-18 22:44:04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2037-09-09 22:44:04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-10-15 20:24:02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-10-09 18:51:54</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-09-15 18:51:54</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-06-01 16:10:53</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>匯聚特色美食與料理，滿足你的味蕾。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2032-05-21 12:43:02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2032-04-25 12:43:02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-06-18 04:59:51</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-05-05 17:12:13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-04-19 17:12:13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-11-27 12:20:50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2030-03-19 10:49:09</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2030-02-20 10:49:09</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-06-15 08:21:43</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2028-09-29 14:09:24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2028-09-07 14:09:24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-05-24 07:41:46</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高手雲集的遊戲競賽，爭奪最強王者寶座。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2034-12-17 07:10:20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2034-11-24 07:10:20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-08-21 23:13:05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2036-10-18 12:33:07</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2036-09-27 12:33:07</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-04-02 14:01:34</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>特別策劃的主題活動，適合全家一同參加。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2032-06-13 12:09:23</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2032-05-26 12:09:23</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-10-06 11:08:03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2034-07-01 12:13:25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2034-06-06 12:13:25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-07-26 16:08:10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2031-04-25 11:27:29</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2031-04-20 11:27:29</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-09-11 17:08:34</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2034-10-21 08:47:17</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2034-09-21 08:47:17</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-12-12 10:47:45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2033-07-10 23:50:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2033-06-28 23:50:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-09-06 09:37:06</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-12-06 22:32:21</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-11-16 22:32:21</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-05-04 19:28:35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2037-05-07 21:21:13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2037-04-07 21:21:13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-08-05 06:11:12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2035-10-18 01:38:36</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2035-09-30 01:38:36</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-12-25 21:27:19</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2027-11-08 10:42:20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2027-10-10 10:42:20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-09-15 22:25:14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-06-12 13:29:26</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-05-16 13:29:26</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-01-27 10:43:18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2027-01-15 02:53:22</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-12-29 02:53:22</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-02-03 06:41:11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高雄市鳳山區光遠路161號</t>
+  </si>
+  <si>
+    <t>台中市大里區中興路二段689號</t>
+  </si>
+  <si>
+    <t>基隆市中正區義一路236號</t>
+  </si>
+  <si>
+    <t>台東縣卑南鄉卑南村中華路一段376號</t>
+  </si>
+  <si>
+    <t>彰化縣員林市中山路一段300號</t>
+  </si>
+  <si>
+    <t>彰化縣彰化市中山路二段416號</t>
+  </si>
+  <si>
+    <t>桃園市八德區介壽路二段777號</t>
+  </si>
+  <si>
+    <t>花蓮縣光復鄉中正路2號</t>
+  </si>
+  <si>
+    <t>新竹縣橫山鄉中山街11號</t>
+  </si>
+  <si>
+    <t>連江縣北竿鄉塘岐村116號</t>
+  </si>
+  <si>
+    <t>屏東縣竹田鄉竹田村中正路50號</t>
+  </si>
+  <si>
+    <t>台東縣台東市中山路276號</t>
+  </si>
+  <si>
+    <t>嘉義縣太保市祥和一路東段1號</t>
+  </si>
+  <si>
+    <t>台南市新營區中正路23號</t>
+  </si>
+  <si>
+    <t>連江縣南竿鄉介壽村88號</t>
+  </si>
+  <si>
+    <t>桃園市桃園區中山路325號</t>
+  </si>
+  <si>
+    <t>高雄市苓雅區四維三路2號</t>
+  </si>
+  <si>
+    <t>屏東縣屏東市自由路527號</t>
+  </si>
+  <si>
+    <t>台南市永康區中山南路1號</t>
+  </si>
+  <si>
+    <t>新北市板橋區中山路一段161號</t>
+  </si>
+  <si>
+    <t>南投縣南投市中興路660號</t>
+  </si>
+  <si>
+    <t>苗栗縣頭份市中正路120號</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>苗栗縣旅行團</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宜蘭縣宜蘭市中山路二段366號</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宜蘭市音樂祭</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -478,7 +1037,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -496,7 +1055,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="22" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -777,7 +1335,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L46"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.625" style="1" customWidth="1"/>
@@ -1398,8 +1956,1145 @@
         <v>104</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="7"/>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>15</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D17" s="2">
+        <v>5</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="2">
+        <v>273</v>
+      </c>
+      <c r="H17" s="2">
+        <v>215</v>
+      </c>
+      <c r="I17" s="2">
+        <v>1</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
+        <v>16</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D18" s="2">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" s="2">
+        <v>231</v>
+      </c>
+      <c r="H18" s="2">
+        <v>7353</v>
+      </c>
+      <c r="I18" s="2">
+        <v>12</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
+        <v>17</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D19" s="2">
+        <v>6</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" s="2">
+        <v>222</v>
+      </c>
+      <c r="H19" s="2">
+        <v>4471</v>
+      </c>
+      <c r="I19" s="2">
+        <v>20</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
+        <v>18</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D20" s="2">
+        <v>3</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" s="2">
+        <v>262</v>
+      </c>
+      <c r="H20" s="2">
+        <v>7621</v>
+      </c>
+      <c r="I20" s="2">
+        <v>4</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
+        <v>19</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D21" s="2">
+        <v>5</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21" s="2">
+        <v>109</v>
+      </c>
+      <c r="H21" s="2">
+        <v>6777</v>
+      </c>
+      <c r="I21" s="2">
+        <v>26</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="2">
+        <v>20</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D22" s="2">
+        <v>4</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" s="2">
+        <v>232</v>
+      </c>
+      <c r="H22" s="2">
+        <v>3049</v>
+      </c>
+      <c r="I22" s="2">
+        <v>12</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="2">
+        <v>21</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D23" s="2">
+        <v>6</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G23" s="2">
+        <v>69</v>
+      </c>
+      <c r="H23" s="2">
+        <v>7956</v>
+      </c>
+      <c r="I23" s="2">
+        <v>4</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
+        <v>22</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="D24" s="2">
+        <v>2</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24" s="2">
+        <v>285</v>
+      </c>
+      <c r="H24" s="2">
+        <v>4470</v>
+      </c>
+      <c r="I24" s="2">
+        <v>40</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" s="2">
+        <v>23</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D25" s="2">
+        <v>3</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" s="2">
+        <v>93</v>
+      </c>
+      <c r="H25" s="2">
+        <v>1890</v>
+      </c>
+      <c r="I25" s="2">
+        <v>48</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="2">
+        <v>24</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D26" s="2">
+        <v>1</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G26" s="2">
+        <v>109</v>
+      </c>
+      <c r="H26" s="2">
+        <v>6446</v>
+      </c>
+      <c r="I26" s="2">
+        <v>47</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="2">
+        <v>25</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D27" s="2">
+        <v>1</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G27" s="2">
+        <v>261</v>
+      </c>
+      <c r="H27" s="2">
+        <v>5998</v>
+      </c>
+      <c r="I27" s="2">
+        <v>4</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="2">
+        <v>26</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="D28" s="2">
+        <v>2</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28" s="2">
+        <v>207</v>
+      </c>
+      <c r="H28" s="2">
+        <v>5683</v>
+      </c>
+      <c r="I28" s="2">
+        <v>9</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="2">
+        <v>27</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D29" s="2">
+        <v>3</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G29" s="2">
+        <v>250</v>
+      </c>
+      <c r="H29" s="2">
+        <v>2300</v>
+      </c>
+      <c r="I29" s="2">
+        <v>21</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
+        <v>28</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D30" s="2">
+        <v>8</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G30" s="2">
+        <v>147</v>
+      </c>
+      <c r="H30" s="2">
+        <v>2125</v>
+      </c>
+      <c r="I30" s="2">
+        <v>39</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" s="2">
+        <v>29</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D31" s="2">
+        <v>3</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G31" s="2">
+        <v>55</v>
+      </c>
+      <c r="H31" s="2">
+        <v>732</v>
+      </c>
+      <c r="I31" s="2">
+        <v>20</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" s="2">
+        <v>30</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D32" s="2">
+        <v>3</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G32" s="2">
+        <v>126</v>
+      </c>
+      <c r="H32" s="2">
+        <v>2749</v>
+      </c>
+      <c r="I32" s="2">
+        <v>17</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" s="2">
+        <v>31</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D33" s="2">
+        <v>4</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G33" s="2">
+        <v>282</v>
+      </c>
+      <c r="H33" s="2">
+        <v>510</v>
+      </c>
+      <c r="I33" s="2">
+        <v>41</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" s="2">
+        <v>32</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D34" s="2">
+        <v>7</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G34" s="2">
+        <v>254</v>
+      </c>
+      <c r="H34" s="2">
+        <v>2057</v>
+      </c>
+      <c r="I34" s="2">
+        <v>46</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" s="2">
+        <v>33</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D35" s="2">
+        <v>3</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G35" s="2">
+        <v>278</v>
+      </c>
+      <c r="H35" s="2">
+        <v>4300</v>
+      </c>
+      <c r="I35" s="2">
+        <v>11</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" s="2">
+        <v>34</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="D36" s="2">
+        <v>9</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G36" s="2">
+        <v>130</v>
+      </c>
+      <c r="H36" s="2">
+        <v>7055</v>
+      </c>
+      <c r="I36" s="2">
+        <v>20</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" s="2">
+        <v>35</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D37" s="2">
+        <v>3</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G37" s="2">
+        <v>149</v>
+      </c>
+      <c r="H37" s="2">
+        <v>7205</v>
+      </c>
+      <c r="I37" s="2">
+        <v>19</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" s="2">
+        <v>36</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D38" s="2">
+        <v>5</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G38" s="2">
+        <v>229</v>
+      </c>
+      <c r="H38" s="2">
+        <v>1509</v>
+      </c>
+      <c r="I38" s="2">
+        <v>24</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A39" s="2">
+        <v>37</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="D39" s="2">
+        <v>2</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G39" s="2">
+        <v>185</v>
+      </c>
+      <c r="H39" s="2">
+        <v>4028</v>
+      </c>
+      <c r="I39" s="2">
+        <v>14</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40" s="2">
+        <v>38</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D40" s="2">
+        <v>4</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G40" s="2">
+        <v>97</v>
+      </c>
+      <c r="H40" s="2">
+        <v>1945</v>
+      </c>
+      <c r="I40" s="2">
+        <v>31</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A41" s="2">
+        <v>39</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D41" s="2">
+        <v>8</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G41" s="2">
+        <v>63</v>
+      </c>
+      <c r="H41" s="2">
+        <v>7414</v>
+      </c>
+      <c r="I41" s="2">
+        <v>11</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A42" s="2">
+        <v>40</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D42" s="2">
+        <v>6</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G42" s="2">
+        <v>165</v>
+      </c>
+      <c r="H42" s="2">
+        <v>7748</v>
+      </c>
+      <c r="I42" s="2">
+        <v>45</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A43" s="2">
+        <v>41</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D43" s="2">
+        <v>1</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G43" s="2">
+        <v>86</v>
+      </c>
+      <c r="H43" s="2">
+        <v>7262</v>
+      </c>
+      <c r="I43" s="2">
+        <v>40</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A44" s="2">
+        <v>42</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D44" s="2">
+        <v>1</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G44" s="2">
+        <v>94</v>
+      </c>
+      <c r="H44" s="2">
+        <v>7217</v>
+      </c>
+      <c r="I44" s="2">
+        <v>12</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A45" s="2">
+        <v>43</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D45" s="2">
+        <v>3</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G45" s="2">
+        <v>76</v>
+      </c>
+      <c r="H45" s="2">
+        <v>2344</v>
+      </c>
+      <c r="I45" s="2">
+        <v>40</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A46" s="2">
+        <v>44</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="D46" s="2">
+        <v>9</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G46" s="2">
+        <v>104</v>
+      </c>
+      <c r="H46" s="2">
+        <v>5971</v>
+      </c>
+      <c r="I46" s="2">
+        <v>14</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>231</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCreation\Web\Gathering_Island\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3497A71-CE9F-4E74-ADBA-2805429257AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ECAF7B9-7EC8-4C7E-AECE-3E5CCDB673C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="events" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">events!$A$1:$M$3</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -24,8 +27,44 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Romi</author>
+  </authors>
+  <commentList>
+    <comment ref="M2" authorId="0" shapeId="0" xr:uid="{17581C10-74D2-4259-AA8B-254741E2EF5B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">0 = </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t>未截止
+1 = 已截止</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="472">
   <si>
     <t>event_id</t>
   </si>
@@ -953,6 +992,832 @@
   </si>
   <si>
     <t>宜蘭市音樂祭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>is_ended</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>活動報名是否截止</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基隆市仁愛區愛三路55號</t>
+  </si>
+  <si>
+    <t>桃園市中壢區中山路200號</t>
+  </si>
+  <si>
+    <t>花蓮縣花蓮市中山路220號</t>
+  </si>
+  <si>
+    <t>交響樂盛典</t>
+  </si>
+  <si>
+    <t>台南市中西區永福路二段100號</t>
+  </si>
+  <si>
+    <t>自由交流會</t>
+  </si>
+  <si>
+    <t>路跑活動</t>
+  </si>
+  <si>
+    <t>聖誕派對</t>
+  </si>
+  <si>
+    <t>彰化縣彰化市中正路150號</t>
+  </si>
+  <si>
+    <t>新北市板橋區文化路一段66號</t>
+  </si>
+  <si>
+    <t>動漫展</t>
+  </si>
+  <si>
+    <t>攝影展</t>
+  </si>
+  <si>
+    <t>甜點市集</t>
+  </si>
+  <si>
+    <t>台中市西屯區文心路三段168號</t>
+  </si>
+  <si>
+    <t>夏日狂歡派對</t>
+  </si>
+  <si>
+    <t>新竹市東區光復路一段300號</t>
+  </si>
+  <si>
+    <t>羽球友誼賽</t>
+  </si>
+  <si>
+    <t>美食饗宴</t>
+  </si>
+  <si>
+    <t>創業分享會</t>
+  </si>
+  <si>
+    <t>寵物同樂日</t>
+  </si>
+  <si>
+    <t>台北市信義區松壽路12號</t>
+  </si>
+  <si>
+    <t>籃球比賽</t>
+  </si>
+  <si>
+    <t>文化探索團</t>
+  </si>
+  <si>
+    <t>密室逃脫挑戰</t>
+  </si>
+  <si>
+    <t>爵士之夜</t>
+  </si>
+  <si>
+    <t>高雄市前鎮區中華五路789號</t>
+  </si>
+  <si>
+    <t>手作體驗</t>
+  </si>
+  <si>
+    <t>語言學習班</t>
+  </si>
+  <si>
+    <t>技術工作坊</t>
+  </si>
+  <si>
+    <t>電玩比賽</t>
+  </si>
+  <si>
+    <t>攝影聚會</t>
+  </si>
+  <si>
+    <t>卡牌對戰賽</t>
+  </si>
+  <si>
+    <t>海島旅行</t>
+  </si>
+  <si>
+    <t>啤酒節</t>
+  </si>
+  <si>
+    <t>喜愛遊戲的朋友不能錯過的桌遊之夜。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-09-17 18:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-08-30 18:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-08-10 18:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>精選作品展出，帶來藝術與創意的藝術展覽。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-07-25 18:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-07-12 18:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-07-02 18:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-07-17 20:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-07-13 20:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-07-11 20:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>邀請知名樂團與表演者，帶來一場難忘的交響樂盛典。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-04-09 19:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-03-10 19:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-03-04 19:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>聚集志同道合的人，共度特別時光的自由交流會。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-08-01 13:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-07-03 13:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-07-01 13:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>參加路跑活動，挑戰自我並體驗運動的快樂。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-08-03 12:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-07-07 12:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-06-17 12:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>這是一場聖誕派對，讓你盡情享受音樂與舞蹈。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-04-05 12:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-03-22 12:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-03-05 12:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>這是一場週末派對，讓你盡情享受音樂與舞蹈。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-02-02 20:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-01-20 20:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-01-13 20:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>精選作品展出，帶來藝術與創意的動漫展。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-09-08 22:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-08-19 22:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-07-30 22:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>精選作品展出，帶來藝術與創意的攝影展。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-05-08 18:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-05-02 18:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-04-17 18:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>讓味蕾享受不同美食文化的甜點市集。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-01-22 12:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-01-19 12:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2023-12-28 12:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>這是一場夏日狂歡派對，讓你盡情享受音樂與舞蹈。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-05-16 22:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-04-28 22:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-04-03 22:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>參加羽球友誼賽，挑戰自我並體驗運動的快樂。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-05-23 10:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-05-14 10:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-04-18 10:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>讓味蕾享受不同美食文化的美食饗宴。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-09-14 19:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-08-24 19:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-07-29 19:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提供最新知識與技能交流，這是一場創業分享會。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-11-30 20:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-11-09 20:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-10-16 20:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-04-29 18:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-04-02 18:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-03-07 18:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>聚集志同道合的人，共度特別時光的寵物同樂日。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-12-29 17:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-12-21 17:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-11-30 17:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-12-26 22:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-12-05 22:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-11-21 22:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-05-04 17:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-04-12 17:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-03-13 17:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提供最新知識與技能交流，這是一場AI 開發者社群聚會。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-09-04 17:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-08-21 17:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-07-28 17:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>參加籃球比賽，挑戰自我並體驗運動的快樂。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-07-18 08:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-06-18 08:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-06-13 08:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一場特別的文化探索團，讓你探索不同風景與文化。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-12-10 14:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-11-14 14:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-10-16 14:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>邀請知名樂團與表演者，帶來一場難忘的音樂會。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-09-08 09:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-08-24 09:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-08-03 09:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>喜愛遊戲的朋友不能錯過的密室逃脫挑戰。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-07-12 18:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-07-03 18:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-06-03 18:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>邀請知名樂團與表演者，帶來一場難忘的爵士之夜。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-06-13 12:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-06-05 12:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-05-08 12:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-09-28 16:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-09-13 16:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-08-29 16:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>聚集志同道合的人，共度特別時光的手作體驗。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-04-28 21:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-04-14 21:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-03-18 21:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提供最新知識與技能交流，這是一場語言學習班。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-02-11 11:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-01-24 11:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-01-16 11:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-08-16 08:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-08-01 08:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-07-04 08:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-05-29 18:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-05-01 18:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-04-23 18:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提供最新知識與技能交流，這是一場技術工作坊。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-03-12 16:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-03-07 16:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-02-19 16:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>喜愛遊戲的朋友不能錯過的電玩比賽。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-01-05 10:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-01-01 10:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-12-04 10:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-12-15 17:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-12-07 17:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-11-25 17:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>聚集志同道合的人，共度特別時光的攝影聚會。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-06-11 11:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-05-23 11:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-05-07 11:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-09-11 15:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-08-31 15:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-08-24 15:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-04-09 20:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-03-18 20:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-02-23 20:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-12-04 15:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-11-13 15:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-10-26 15:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>喜愛遊戲的朋友不能錯過的卡牌對戰賽。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-01-12 13:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2023-12-22 13:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2023-12-08 13:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-08-25 20:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-08-12 20:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-07-19 20:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-10-03 17:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-09-24 17:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-09-22 17:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-12-23 14:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-12-09 14:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-11-15 14:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一場特別的海島旅行，讓你探索不同風景與文化。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-01-22 21:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-01-06 21:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-12-23 21:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-11-14 22:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-11-07 22:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-11-05 22:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-12-07 10:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-11-14 10:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-10-30 10:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-11-06 18:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-10-08 18:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-10-02 18:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-11-05 14:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-10-12 14:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-09-27 14:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-12-28 10:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-11-29 10:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-11-11 10:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>讓味蕾享受不同美食文化的啤酒節。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-03-04 18:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-02-11 18:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-02-02 18:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-09-20 17:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-08-25 17:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-08-16 17:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-10-17 21:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-09-27 21:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-09-05 21:00:00</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -960,7 +1825,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -989,6 +1854,21 @@
       <family val="2"/>
       <charset val="136"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1010,7 +1890,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1033,11 +1913,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1052,7 +1945,16 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1334,21 +2236,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L46"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:M96"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="18.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="23.875" style="1" customWidth="1"/>
     <col min="3" max="3" width="40.625" style="1" customWidth="1"/>
     <col min="4" max="4" width="23.875" style="1" customWidth="1"/>
     <col min="5" max="5" width="40.625" style="1" customWidth="1"/>
     <col min="6" max="9" width="23.875" style="1" customWidth="1"/>
-    <col min="10" max="12" width="28.625" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="1"/>
+    <col min="10" max="13" width="28.625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>26</v>
       </c>
@@ -1385,84 +2287,93 @@
       <c r="L1" s="5" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="6" t="s">
+      <c r="M1" s="5" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="9" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
+      <c r="M2" s="9" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="6">
         <v>1</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="2">
+      <c r="F3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="6">
         <v>50</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="6">
         <v>300</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="6">
         <v>1</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="8" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M3" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -1499,8 +2410,11 @@
       <c r="L4" s="3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M4" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -1537,8 +2451,11 @@
       <c r="L5" s="3" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M5" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -1575,8 +2492,11 @@
       <c r="L6" s="3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M6" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -1613,8 +2533,11 @@
       <c r="L7" s="3" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M7" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>6</v>
       </c>
@@ -1651,8 +2574,11 @@
       <c r="L8" s="3" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>7</v>
       </c>
@@ -1689,8 +2615,11 @@
       <c r="L9" s="3" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>8</v>
       </c>
@@ -1727,8 +2656,11 @@
       <c r="L10" s="3" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>9</v>
       </c>
@@ -1765,8 +2697,11 @@
       <c r="L11" s="3" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M11" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>10</v>
       </c>
@@ -1803,8 +2738,11 @@
       <c r="L12" s="3" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>11</v>
       </c>
@@ -1841,8 +2779,11 @@
       <c r="L13" s="3" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>12</v>
       </c>
@@ -1879,46 +2820,52 @@
       <c r="L14" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15" s="6">
         <v>13</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="6">
         <v>7</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15" s="2">
+      <c r="F15" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="6">
         <v>60</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="6">
         <v>100</v>
       </c>
-      <c r="I15" s="2">
+      <c r="I15" s="6">
         <v>9</v>
       </c>
-      <c r="J15" s="3" t="s">
+      <c r="J15" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="K15" s="3" t="s">
+      <c r="K15" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="L15" s="3" t="s">
+      <c r="L15" s="8" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M15" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>14</v>
       </c>
@@ -1955,8 +2902,11 @@
       <c r="L16" s="3" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M16" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>15</v>
       </c>
@@ -1993,8 +2943,11 @@
       <c r="L17" s="3" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>16</v>
       </c>
@@ -2031,8 +2984,11 @@
       <c r="L18" s="3" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>17</v>
       </c>
@@ -2069,8 +3025,11 @@
       <c r="L19" s="3" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M19" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>18</v>
       </c>
@@ -2107,8 +3066,11 @@
       <c r="L20" s="3" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>19</v>
       </c>
@@ -2145,8 +3107,11 @@
       <c r="L21" s="3" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>20</v>
       </c>
@@ -2183,8 +3148,11 @@
       <c r="L22" s="3" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>21</v>
       </c>
@@ -2221,8 +3189,11 @@
       <c r="L23" s="3" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>22</v>
       </c>
@@ -2259,8 +3230,11 @@
       <c r="L24" s="3" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>23</v>
       </c>
@@ -2297,8 +3271,11 @@
       <c r="L25" s="3" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>24</v>
       </c>
@@ -2335,8 +3312,11 @@
       <c r="L26" s="3" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>25</v>
       </c>
@@ -2373,8 +3353,11 @@
       <c r="L27" s="3" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>26</v>
       </c>
@@ -2411,8 +3394,11 @@
       <c r="L28" s="3" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>27</v>
       </c>
@@ -2449,8 +3435,11 @@
       <c r="L29" s="3" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>28</v>
       </c>
@@ -2487,8 +3476,11 @@
       <c r="L30" s="3" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>29</v>
       </c>
@@ -2525,8 +3517,11 @@
       <c r="L31" s="3" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>30</v>
       </c>
@@ -2563,8 +3558,11 @@
       <c r="L32" s="3" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>31</v>
       </c>
@@ -2601,8 +3599,11 @@
       <c r="L33" s="3" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>32</v>
       </c>
@@ -2639,8 +3640,11 @@
       <c r="L34" s="3" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>33</v>
       </c>
@@ -2677,8 +3681,11 @@
       <c r="L35" s="3" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>34</v>
       </c>
@@ -2715,8 +3722,11 @@
       <c r="L36" s="3" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M36" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>35</v>
       </c>
@@ -2753,8 +3763,11 @@
       <c r="L37" s="3" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M37" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>36</v>
       </c>
@@ -2791,8 +3804,11 @@
       <c r="L38" s="3" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M38" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>37</v>
       </c>
@@ -2829,8 +3845,11 @@
       <c r="L39" s="3" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M39" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>38</v>
       </c>
@@ -2867,8 +3886,11 @@
       <c r="L40" s="3" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M40" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>39</v>
       </c>
@@ -2905,8 +3927,11 @@
       <c r="L41" s="3" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>40</v>
       </c>
@@ -2943,8 +3968,11 @@
       <c r="L42" s="3" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>41</v>
       </c>
@@ -2981,8 +4009,11 @@
       <c r="L43" s="3" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>42</v>
       </c>
@@ -3019,8 +4050,11 @@
       <c r="L44" s="3" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>43</v>
       </c>
@@ -3057,8 +4091,11 @@
       <c r="L45" s="3" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>44</v>
       </c>
@@ -3095,9 +4132,2068 @@
       <c r="L46" s="3" t="s">
         <v>231</v>
       </c>
+      <c r="M46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A47" s="2">
+        <v>45</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="D47" s="2">
+        <v>7</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G47" s="2">
+        <v>847</v>
+      </c>
+      <c r="H47" s="2">
+        <v>0</v>
+      </c>
+      <c r="I47" s="2">
+        <v>21</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="M47" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A48" s="2">
+        <v>46</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="D48" s="2">
+        <v>4</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G48" s="2">
+        <v>1601</v>
+      </c>
+      <c r="H48" s="2">
+        <v>0</v>
+      </c>
+      <c r="I48" s="2">
+        <v>35</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="M48" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A49" s="2">
+        <v>47</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="D49" s="2">
+        <v>7</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G49" s="2">
+        <v>525</v>
+      </c>
+      <c r="H49" s="2">
+        <v>0</v>
+      </c>
+      <c r="I49" s="2">
+        <v>4</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="M49" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A50" s="2">
+        <v>48</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="D50" s="2">
+        <v>2</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G50" s="2">
+        <v>121</v>
+      </c>
+      <c r="H50" s="2">
+        <v>0</v>
+      </c>
+      <c r="I50" s="2">
+        <v>22</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="M50" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A51" s="2">
+        <v>49</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="D51" s="2">
+        <v>9</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G51" s="2">
+        <v>1469</v>
+      </c>
+      <c r="H51" s="2">
+        <v>0</v>
+      </c>
+      <c r="I51" s="2">
+        <v>42</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="L51" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A52" s="2">
+        <v>50</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D52" s="2">
+        <v>6</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G52" s="2">
+        <v>474</v>
+      </c>
+      <c r="H52" s="2">
+        <v>1293</v>
+      </c>
+      <c r="I52" s="2">
+        <v>2</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="M52" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A53" s="2">
+        <v>51</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="D53" s="2">
+        <v>1</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G53" s="2">
+        <v>1063</v>
+      </c>
+      <c r="H53" s="2">
+        <v>0</v>
+      </c>
+      <c r="I53" s="2">
+        <v>12</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A54" s="2">
+        <v>52</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="D54" s="2">
+        <v>1</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G54" s="2">
+        <v>1864</v>
+      </c>
+      <c r="H54" s="2">
+        <v>690</v>
+      </c>
+      <c r="I54" s="2">
+        <v>37</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="M54" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A55" s="2">
+        <v>53</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="D55" s="2">
+        <v>4</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G55" s="2">
+        <v>595</v>
+      </c>
+      <c r="H55" s="2">
+        <v>0</v>
+      </c>
+      <c r="I55" s="2">
+        <v>14</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="M55" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A56" s="2">
+        <v>54</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="D56" s="2">
+        <v>4</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G56" s="2">
+        <v>374</v>
+      </c>
+      <c r="H56" s="2">
+        <v>1992</v>
+      </c>
+      <c r="I56" s="2">
+        <v>49</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="L56" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="M56" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A57" s="2">
+        <v>55</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="D57" s="2">
+        <v>8</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G57" s="2">
+        <v>472</v>
+      </c>
+      <c r="H57" s="2">
+        <v>0</v>
+      </c>
+      <c r="I57" s="2">
+        <v>13</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="M57" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A58" s="2">
+        <v>56</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="D58" s="2">
+        <v>1</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G58" s="2">
+        <v>1478</v>
+      </c>
+      <c r="H58" s="2">
+        <v>725</v>
+      </c>
+      <c r="I58" s="2">
+        <v>8</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="M58" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A59" s="2">
+        <v>57</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="D59" s="2">
+        <v>6</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G59" s="2">
+        <v>926</v>
+      </c>
+      <c r="H59" s="2">
+        <v>697</v>
+      </c>
+      <c r="I59" s="2">
+        <v>41</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="M59" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A60" s="2">
+        <v>58</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="D60" s="2">
+        <v>8</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G60" s="2">
+        <v>1265</v>
+      </c>
+      <c r="H60" s="2">
+        <v>0</v>
+      </c>
+      <c r="I60" s="2">
+        <v>40</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="L60" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="M60" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A61" s="2">
+        <v>59</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="D61" s="2">
+        <v>3</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G61" s="2">
+        <v>83</v>
+      </c>
+      <c r="H61" s="2">
+        <v>0</v>
+      </c>
+      <c r="I61" s="2">
+        <v>30</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="K61" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="L61" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A62" s="2">
+        <v>60</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="D62" s="2">
+        <v>4</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G62" s="2">
+        <v>1525</v>
+      </c>
+      <c r="H62" s="2">
+        <v>0</v>
+      </c>
+      <c r="I62" s="2">
+        <v>20</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="M62" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A63" s="2">
+        <v>61</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="D63" s="2">
+        <v>9</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G63" s="2">
+        <v>149</v>
+      </c>
+      <c r="H63" s="2">
+        <v>0</v>
+      </c>
+      <c r="I63" s="2">
+        <v>38</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="K63" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="L63" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="M63" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A64" s="2">
+        <v>62</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="D64" s="2">
+        <v>9</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G64" s="2">
+        <v>432</v>
+      </c>
+      <c r="H64" s="2">
+        <v>0</v>
+      </c>
+      <c r="I64" s="2">
+        <v>35</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="L64" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A65" s="2">
+        <v>63</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="D65" s="2">
+        <v>4</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G65" s="2">
+        <v>1763</v>
+      </c>
+      <c r="H65" s="2">
+        <v>1050</v>
+      </c>
+      <c r="I65" s="2">
+        <v>29</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="K65" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="L65" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A66" s="2">
+        <v>64</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="D66" s="2">
+        <v>3</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G66" s="2">
+        <v>100</v>
+      </c>
+      <c r="H66" s="2">
+        <v>662</v>
+      </c>
+      <c r="I66" s="2">
+        <v>21</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="L66" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="M66" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A67" s="2">
+        <v>65</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="D67" s="2">
+        <v>6</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G67" s="2">
+        <v>1741</v>
+      </c>
+      <c r="H67" s="2">
+        <v>0</v>
+      </c>
+      <c r="I67" s="2">
+        <v>21</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="K67" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="L67" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="M67" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A68" s="2">
+        <v>66</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="D68" s="2">
+        <v>5</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G68" s="2">
+        <v>1894</v>
+      </c>
+      <c r="H68" s="2">
+        <v>0</v>
+      </c>
+      <c r="I68" s="2">
+        <v>42</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="K68" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="L68" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A69" s="2">
+        <v>67</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="D69" s="2">
+        <v>2</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G69" s="2">
+        <v>1396</v>
+      </c>
+      <c r="H69" s="2">
+        <v>1350</v>
+      </c>
+      <c r="I69" s="2">
+        <v>50</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="K69" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="L69" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A70" s="2">
+        <v>68</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="D70" s="2">
+        <v>7</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G70" s="2">
+        <v>1495</v>
+      </c>
+      <c r="H70" s="2">
+        <v>1361</v>
+      </c>
+      <c r="I70" s="2">
+        <v>49</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="K70" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="L70" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="M70" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A71" s="2">
+        <v>69</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="D71" s="2">
+        <v>2</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G71" s="2">
+        <v>983</v>
+      </c>
+      <c r="H71" s="2">
+        <v>0</v>
+      </c>
+      <c r="I71" s="2">
+        <v>49</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="K71" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="L71" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="M71" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A72" s="2">
+        <v>70</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="D72" s="2">
+        <v>4</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G72" s="2">
+        <v>1853</v>
+      </c>
+      <c r="H72" s="2">
+        <v>235</v>
+      </c>
+      <c r="I72" s="2">
+        <v>7</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="L72" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="M72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A73" s="2">
+        <v>71</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="D73" s="2">
+        <v>9</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G73" s="2">
+        <v>1033</v>
+      </c>
+      <c r="H73" s="2">
+        <v>776</v>
+      </c>
+      <c r="I73" s="2">
+        <v>27</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="K73" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="L73" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="M73" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A74" s="2">
+        <v>72</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="D74" s="2">
+        <v>3</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G74" s="2">
+        <v>398</v>
+      </c>
+      <c r="H74" s="2">
+        <v>0</v>
+      </c>
+      <c r="I74" s="2">
+        <v>2</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="K74" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="L74" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="M74" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A75" s="2">
+        <v>73</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="D75" s="2">
+        <v>7</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G75" s="2">
+        <v>171</v>
+      </c>
+      <c r="H75" s="2">
+        <v>0</v>
+      </c>
+      <c r="I75" s="2">
+        <v>9</v>
+      </c>
+      <c r="J75" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="K75" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="L75" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A76" s="2">
+        <v>74</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="D76" s="2">
+        <v>3</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G76" s="2">
+        <v>752</v>
+      </c>
+      <c r="H76" s="2">
+        <v>0</v>
+      </c>
+      <c r="I76" s="2">
+        <v>16</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="K76" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="L76" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="M76" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A77" s="2">
+        <v>75</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="D77" s="2">
+        <v>3</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G77" s="2">
+        <v>1165</v>
+      </c>
+      <c r="H77" s="2">
+        <v>179</v>
+      </c>
+      <c r="I77" s="2">
+        <v>2</v>
+      </c>
+      <c r="J77" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="K77" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="L77" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="M77" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A78" s="2">
+        <v>76</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="D78" s="2">
+        <v>7</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G78" s="2">
+        <v>1619</v>
+      </c>
+      <c r="H78" s="2">
+        <v>0</v>
+      </c>
+      <c r="I78" s="2">
+        <v>34</v>
+      </c>
+      <c r="J78" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="K78" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="L78" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="M78" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A79" s="2">
+        <v>77</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="D79" s="2">
+        <v>8</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G79" s="2">
+        <v>451</v>
+      </c>
+      <c r="H79" s="2">
+        <v>0</v>
+      </c>
+      <c r="I79" s="2">
+        <v>44</v>
+      </c>
+      <c r="J79" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="K79" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="L79" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="M79" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A80" s="2">
+        <v>78</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="D80" s="2">
+        <v>9</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G80" s="2">
+        <v>73</v>
+      </c>
+      <c r="H80" s="2">
+        <v>0</v>
+      </c>
+      <c r="I80" s="2">
+        <v>22</v>
+      </c>
+      <c r="J80" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="K80" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="L80" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="M80" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A81" s="2">
+        <v>79</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="D81" s="2">
+        <v>7</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G81" s="2">
+        <v>499</v>
+      </c>
+      <c r="H81" s="2">
+        <v>0</v>
+      </c>
+      <c r="I81" s="2">
+        <v>4</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="L81" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="M81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A82" s="2">
+        <v>80</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="D82" s="2">
+        <v>3</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G82" s="2">
+        <v>284</v>
+      </c>
+      <c r="H82" s="2">
+        <v>0</v>
+      </c>
+      <c r="I82" s="2">
+        <v>2</v>
+      </c>
+      <c r="J82" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="K82" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="L82" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="M82" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A83" s="2">
+        <v>81</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="D83" s="2">
+        <v>5</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G83" s="2">
+        <v>1153</v>
+      </c>
+      <c r="H83" s="2">
+        <v>0</v>
+      </c>
+      <c r="I83" s="2">
+        <v>10</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="M83" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A84" s="6">
+        <v>82</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="D84" s="6">
+        <v>7</v>
+      </c>
+      <c r="E84" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="F84" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G84" s="6">
+        <v>1977</v>
+      </c>
+      <c r="H84" s="6">
+        <v>1408</v>
+      </c>
+      <c r="I84" s="6">
+        <v>32</v>
+      </c>
+      <c r="J84" s="8" t="s">
+        <v>431</v>
+      </c>
+      <c r="K84" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="L84" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="M84" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A85" s="2">
+        <v>83</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="D85" s="2">
+        <v>7</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G85" s="2">
+        <v>995</v>
+      </c>
+      <c r="H85" s="2">
+        <v>1664</v>
+      </c>
+      <c r="I85" s="2">
+        <v>20</v>
+      </c>
+      <c r="J85" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="K85" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="L85" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A86" s="2">
+        <v>84</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="D86" s="2">
+        <v>1</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G86" s="2">
+        <v>88</v>
+      </c>
+      <c r="H86" s="2">
+        <v>1068</v>
+      </c>
+      <c r="I86" s="2">
+        <v>49</v>
+      </c>
+      <c r="J86" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="K86" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="L86" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="M86" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A87" s="2">
+        <v>85</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="D87" s="2">
+        <v>6</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G87" s="2">
+        <v>1999</v>
+      </c>
+      <c r="H87" s="2">
+        <v>0</v>
+      </c>
+      <c r="I87" s="2">
+        <v>15</v>
+      </c>
+      <c r="J87" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="K87" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="L87" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A88" s="2">
+        <v>86</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="D88" s="2">
+        <v>5</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G88" s="2">
+        <v>65</v>
+      </c>
+      <c r="H88" s="2">
+        <v>0</v>
+      </c>
+      <c r="I88" s="2">
+        <v>48</v>
+      </c>
+      <c r="J88" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="K88" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="L88" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A89" s="2">
+        <v>87</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="D89" s="2">
+        <v>8</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G89" s="2">
+        <v>241</v>
+      </c>
+      <c r="H89" s="2">
+        <v>0</v>
+      </c>
+      <c r="I89" s="2">
+        <v>30</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="L89" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="M89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A90" s="2">
+        <v>88</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="D90" s="2">
+        <v>7</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G90" s="2">
+        <v>1600</v>
+      </c>
+      <c r="H90" s="2">
+        <v>0</v>
+      </c>
+      <c r="I90" s="2">
+        <v>12</v>
+      </c>
+      <c r="J90" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="K90" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="L90" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="M90" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A91" s="2">
+        <v>89</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="D91" s="2">
+        <v>1</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G91" s="2">
+        <v>1791</v>
+      </c>
+      <c r="H91" s="2">
+        <v>264</v>
+      </c>
+      <c r="I91" s="2">
+        <v>16</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="M91" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A92" s="2">
+        <v>90</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="D92" s="2">
+        <v>6</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G92" s="2">
+        <v>1427</v>
+      </c>
+      <c r="H92" s="2">
+        <v>1616</v>
+      </c>
+      <c r="I92" s="2">
+        <v>6</v>
+      </c>
+      <c r="J92" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="K92" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="L92" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A93" s="2">
+        <v>91</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="D93" s="2">
+        <v>2</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G93" s="2">
+        <v>636</v>
+      </c>
+      <c r="H93" s="2">
+        <v>0</v>
+      </c>
+      <c r="I93" s="2">
+        <v>19</v>
+      </c>
+      <c r="J93" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="K93" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="L93" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="M93" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A94" s="2">
+        <v>92</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="D94" s="2">
+        <v>8</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G94" s="2">
+        <v>70</v>
+      </c>
+      <c r="H94" s="2">
+        <v>0</v>
+      </c>
+      <c r="I94" s="2">
+        <v>2</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="M94" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A95" s="2">
+        <v>93</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="D95" s="2">
+        <v>3</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G95" s="2">
+        <v>253</v>
+      </c>
+      <c r="H95" s="2">
+        <v>231</v>
+      </c>
+      <c r="I95" s="2">
+        <v>39</v>
+      </c>
+      <c r="J95" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="K95" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="L95" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="M95" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A96" s="2">
+        <v>94</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="D96" s="2">
+        <v>7</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G96" s="2">
+        <v>1751</v>
+      </c>
+      <c r="H96" s="2">
+        <v>0</v>
+      </c>
+      <c r="I96" s="2">
+        <v>46</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:M3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M97">
+      <sortCondition ref="A1:A3"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCreation\Web\Gathering_Island\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44B9627D-D17A-48A9-8939-0592B81198B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94195A66-04A2-4980-8ACA-E0DC52605529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="events" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">events!$A$1:$M$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">events!$A$1:$M$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,22 +40,11 @@
             <b/>
             <sz val="9"/>
             <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">0 = </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
             <rFont val="細明體"/>
             <family val="3"/>
             <charset val="136"/>
           </rPr>
-          <t>未截止
-1 = 已截止</t>
+          <t>預設為0</t>
         </r>
       </text>
     </comment>
@@ -64,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="957" uniqueCount="661">
   <si>
     <t>event_id</t>
   </si>
@@ -1262,286 +1251,882 @@
     <t>2025-10-05 21:00:00</t>
   </si>
   <si>
-    <t>2037-09-07 19:00:59</t>
-  </si>
-  <si>
-    <t>2037-09-19 18:30:59</t>
-  </si>
-  <si>
-    <t>2037-09-28 18:00:59</t>
-  </si>
-  <si>
-    <t>2037-09-05 18:00:59</t>
-  </si>
-  <si>
-    <t>2027-09-08 19:00:59</t>
-  </si>
-  <si>
-    <t>2028-09-18 18:30:59</t>
-  </si>
-  <si>
-    <t>2030-03-04 09:00:59</t>
-  </si>
-  <si>
-    <t>2029-05-08 10:00:59</t>
-  </si>
-  <si>
-    <t>2032-11-30 07:00:59</t>
-  </si>
-  <si>
-    <t>2026-11-11 06:00:59</t>
-  </si>
-  <si>
-    <t>2035-07-20 13:00:59</t>
-  </si>
-  <si>
-    <t>2031-04-17 11:00:59</t>
-  </si>
-  <si>
-    <t>2025-09-30 18:30:59</t>
-  </si>
-  <si>
-    <t>2036-08-22 09:30:59</t>
-  </si>
-  <si>
-    <t>2027-12-23 12:20:59</t>
-  </si>
-  <si>
-    <t>2029-12-20 08:00:59</t>
-  </si>
-  <si>
-    <t>2028-06-06 08:00:59</t>
-  </si>
-  <si>
-    <t>2031-11-08 08:00:59</t>
-  </si>
-  <si>
-    <t>2027-06-23 12:45:59</t>
-  </si>
-  <si>
-    <t>2027-06-28 08:20:59</t>
-  </si>
-  <si>
-    <t>2027-11-18 19:40:59</t>
-  </si>
-  <si>
-    <t>2030-01-24 10:50:59</t>
-  </si>
-  <si>
-    <t>2030-03-25 00:25:59</t>
-  </si>
-  <si>
-    <t>2033-09-20 06:30:59</t>
-  </si>
-  <si>
-    <t>2028-05-23 22:25:59</t>
-  </si>
-  <si>
-    <t>2037-09-17 22:45:59</t>
-  </si>
-  <si>
-    <t>2026-10-07 18:50:59</t>
-  </si>
-  <si>
-    <t>2032-05-19 12:45:59</t>
-  </si>
-  <si>
-    <t>2026-05-01 17:10:59</t>
-  </si>
-  <si>
-    <t>2030-03-14 10:50:59</t>
-  </si>
-  <si>
-    <t>2028-09-26 14:10:59</t>
-  </si>
-  <si>
-    <t>2034-12-16 07:10:59</t>
-  </si>
-  <si>
-    <t>2036-10-14 12:35:59</t>
-  </si>
-  <si>
-    <t>2032-06-08 12:10:59</t>
-  </si>
-  <si>
-    <t>2034-06-27 12:15:59</t>
-  </si>
-  <si>
-    <t>2031-04-20 11:25:59</t>
-  </si>
-  <si>
-    <t>2034-10-16 08:45:59</t>
-  </si>
-  <si>
-    <t>2033-07-07 23:50:59</t>
-  </si>
-  <si>
-    <t>2026-12-01 22:30:59</t>
-  </si>
-  <si>
-    <t>2037-05-03 21:20:59</t>
-  </si>
-  <si>
-    <t>2035-10-13 01:40:59</t>
-  </si>
-  <si>
-    <t>2027-11-05 10:40:59</t>
-  </si>
-  <si>
-    <t>2026-06-09 13:30:59</t>
-  </si>
-  <si>
-    <t>2027-01-11 02:55:59</t>
-  </si>
-  <si>
-    <t>2024-09-15 18:00:59</t>
-  </si>
-  <si>
-    <t>2024-07-23 18:00:59</t>
-  </si>
-  <si>
-    <t>2024-07-12 20:00:59</t>
-  </si>
-  <si>
-    <t>2024-04-08 19:00:59</t>
-  </si>
-  <si>
-    <t>2026-07-27 13:00:59</t>
-  </si>
-  <si>
-    <t>2025-07-30 12:00:59</t>
-  </si>
-  <si>
-    <t>2026-04-01 12:00:59</t>
-  </si>
-  <si>
-    <t>2025-01-29 20:00:59</t>
-  </si>
-  <si>
-    <t>2025-09-04 22:00:59</t>
-  </si>
-  <si>
-    <t>2024-05-04 18:00:59</t>
-  </si>
-  <si>
-    <t>2024-01-19 12:00:59</t>
-  </si>
-  <si>
-    <t>2024-05-14 22:00:59</t>
-  </si>
-  <si>
-    <t>2024-05-19 10:00:59</t>
-  </si>
-  <si>
-    <t>2024-09-13 19:00:59</t>
-  </si>
-  <si>
-    <t>2026-11-29 20:00:59</t>
-  </si>
-  <si>
-    <t>2024-04-28 18:00:59</t>
-  </si>
-  <si>
-    <t>2024-12-28 17:00:59</t>
-  </si>
-  <si>
-    <t>2026-12-23 22:00:59</t>
-  </si>
-  <si>
-    <t>2026-05-03 17:00:59</t>
-  </si>
-  <si>
-    <t>2025-08-31 17:00:59</t>
-  </si>
-  <si>
-    <t>2024-07-13 08:00:59</t>
-  </si>
-  <si>
-    <t>2025-12-09 14:00:59</t>
-  </si>
-  <si>
-    <t>2026-09-05 09:00:59</t>
-  </si>
-  <si>
-    <t>2025-07-09 18:00:59</t>
-  </si>
-  <si>
-    <t>2024-06-12 12:00:59</t>
-  </si>
-  <si>
-    <t>2025-09-23 16:00:59</t>
-  </si>
-  <si>
-    <t>2025-04-27 21:00:59</t>
-  </si>
-  <si>
-    <t>2024-02-08 11:00:59</t>
-  </si>
-  <si>
-    <t>2026-08-14 08:00:59</t>
-  </si>
-  <si>
-    <t>2025-05-25 18:00:59</t>
-  </si>
-  <si>
-    <t>2024-03-09 16:00:59</t>
-  </si>
-  <si>
-    <t>2025-01-04 10:00:59</t>
-  </si>
-  <si>
-    <t>2024-12-11 17:00:59</t>
-  </si>
-  <si>
-    <t>2026-06-10 11:00:59</t>
-  </si>
-  <si>
-    <t>2025-09-10 15:00:59</t>
-  </si>
-  <si>
-    <t>2026-04-07 20:00:59</t>
-  </si>
-  <si>
-    <t>2024-11-30 15:00:59</t>
-  </si>
-  <si>
-    <t>2024-01-08 13:00:59</t>
-  </si>
-  <si>
-    <t>2026-08-23 20:00:59</t>
-  </si>
-  <si>
-    <t>2024-09-30 17:00:59</t>
-  </si>
-  <si>
-    <t>2026-12-22 14:00:59</t>
-  </si>
-  <si>
-    <t>2026-01-17 21:00:59</t>
-  </si>
-  <si>
-    <t>2025-11-13 22:00:59</t>
-  </si>
-  <si>
-    <t>2025-12-06 10:00:59</t>
-  </si>
-  <si>
-    <t>2024-11-03 18:00:59</t>
-  </si>
-  <si>
-    <t>2026-11-04 14:00:59</t>
-  </si>
-  <si>
-    <t>2024-12-26 10:00:59</t>
-  </si>
-  <si>
-    <t>2025-03-02 18:00:59</t>
-  </si>
-  <si>
-    <t>2024-09-16 17:00:59</t>
-  </si>
-  <si>
-    <t>2025-10-12 21:00:59</t>
+    <t>2024-01-08 13:00:00</t>
+  </si>
+  <si>
+    <t>2024-01-19 12:00:00</t>
+  </si>
+  <si>
+    <t>2024-02-08 11:00:00</t>
+  </si>
+  <si>
+    <t>2024-03-09 16:00:00</t>
+  </si>
+  <si>
+    <t>2024-04-08 19:00:00</t>
+  </si>
+  <si>
+    <t>2024-05-04 18:00:00</t>
+  </si>
+  <si>
+    <t>2024-04-28 18:00:00</t>
+  </si>
+  <si>
+    <t>2024-05-14 22:00:00</t>
+  </si>
+  <si>
+    <t>2024-05-19 10:00:00</t>
+  </si>
+  <si>
+    <t>2024-06-12 12:00:00</t>
+  </si>
+  <si>
+    <t>2024-07-12 20:00:00</t>
+  </si>
+  <si>
+    <t>2024-07-23 18:00:00</t>
+  </si>
+  <si>
+    <t>2024-07-13 08:00:00</t>
+  </si>
+  <si>
+    <t>2024-09-13 19:00:00</t>
+  </si>
+  <si>
+    <t>2024-09-16 17:00:00</t>
+  </si>
+  <si>
+    <t>2024-09-15 18:00:00</t>
+  </si>
+  <si>
+    <t>2024-09-30 17:00:00</t>
+  </si>
+  <si>
+    <t>2024-11-03 18:00:00</t>
+  </si>
+  <si>
+    <t>2024-11-30 15:00:00</t>
+  </si>
+  <si>
+    <t>2024-12-11 17:00:00</t>
+  </si>
+  <si>
+    <t>2024-12-26 10:00:00</t>
+  </si>
+  <si>
+    <t>2024-12-28 17:00:00</t>
+  </si>
+  <si>
+    <t>2025-01-04 10:00:00</t>
+  </si>
+  <si>
+    <t>2025-01-29 20:00:00</t>
+  </si>
+  <si>
+    <t>2025-03-02 18:00:00</t>
+  </si>
+  <si>
+    <t>2025-04-27 21:00:00</t>
+  </si>
+  <si>
+    <t>2025-05-25 18:00:00</t>
+  </si>
+  <si>
+    <t>2025-07-09 18:00:00</t>
+  </si>
+  <si>
+    <t>2025-07-30 12:00:00</t>
+  </si>
+  <si>
+    <t>2025-09-10 15:00:00</t>
+  </si>
+  <si>
+    <t>2025-08-31 17:00:00</t>
+  </si>
+  <si>
+    <t>2025-09-04 22:00:00</t>
+  </si>
+  <si>
+    <t>2025-09-23 16:00:00</t>
+  </si>
+  <si>
+    <t>2025-09-30 18:30:00</t>
+  </si>
+  <si>
+    <t>2025-10-12 21:00:00</t>
+  </si>
+  <si>
+    <t>2025-11-13 22:00:00</t>
+  </si>
+  <si>
+    <t>2025-12-06 10:00:00</t>
+  </si>
+  <si>
+    <t>2025-12-09 14:00:00</t>
+  </si>
+  <si>
+    <t>2026-01-17 21:00:00</t>
+  </si>
+  <si>
+    <t>2026-04-01 12:00:00</t>
+  </si>
+  <si>
+    <t>2026-04-07 20:00:00</t>
+  </si>
+  <si>
+    <t>2026-05-03 17:00:00</t>
+  </si>
+  <si>
+    <t>2026-05-01 17:10:00</t>
+  </si>
+  <si>
+    <t>2026-06-10 11:00:00</t>
+  </si>
+  <si>
+    <t>2026-06-09 13:30:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 13:00:00</t>
+  </si>
+  <si>
+    <t>2026-08-14 08:00:00</t>
+  </si>
+  <si>
+    <t>2026-08-23 20:00:00</t>
+  </si>
+  <si>
+    <t>2026-09-05 09:00:00</t>
+  </si>
+  <si>
+    <t>2026-10-07 18:50:00</t>
+  </si>
+  <si>
+    <t>2026-11-04 14:00:00</t>
+  </si>
+  <si>
+    <t>2026-11-11 06:00:00</t>
+  </si>
+  <si>
+    <t>2026-12-01 22:30:00</t>
+  </si>
+  <si>
+    <t>2026-11-29 20:00:00</t>
+  </si>
+  <si>
+    <t>2026-12-22 14:00:00</t>
+  </si>
+  <si>
+    <t>2026-12-23 22:00:00</t>
+  </si>
+  <si>
+    <t>2027-01-11 02:55:00</t>
+  </si>
+  <si>
+    <t>2027-06-28 08:20:00</t>
+  </si>
+  <si>
+    <t>2027-06-23 12:45:00</t>
+  </si>
+  <si>
+    <t>2027-09-08 19:00:00</t>
+  </si>
+  <si>
+    <t>2027-11-05 10:40:00</t>
+  </si>
+  <si>
+    <t>2027-11-18 19:40:00</t>
+  </si>
+  <si>
+    <t>2027-12-23 12:20:00</t>
+  </si>
+  <si>
+    <t>2028-05-23 22:25:00</t>
+  </si>
+  <si>
+    <t>2028-06-06 08:00:00</t>
+  </si>
+  <si>
+    <t>2028-09-18 18:30:00</t>
+  </si>
+  <si>
+    <t>2028-09-26 14:10:00</t>
+  </si>
+  <si>
+    <t>2029-05-08 10:00:00</t>
+  </si>
+  <si>
+    <t>2029-12-20 08:00:00</t>
+  </si>
+  <si>
+    <t>2030-01-24 10:50:00</t>
+  </si>
+  <si>
+    <t>2030-03-04 09:00:00</t>
+  </si>
+  <si>
+    <t>2030-03-14 10:50:00</t>
+  </si>
+  <si>
+    <t>2030-03-25 00:25:00</t>
+  </si>
+  <si>
+    <t>2031-04-20 11:25:00</t>
+  </si>
+  <si>
+    <t>2031-04-17 11:00:00</t>
+  </si>
+  <si>
+    <t>2031-11-08 08:00:00</t>
+  </si>
+  <si>
+    <t>2032-05-19 12:45:00</t>
+  </si>
+  <si>
+    <t>2032-06-08 12:10:00</t>
+  </si>
+  <si>
+    <t>2032-11-30 07:00:00</t>
+  </si>
+  <si>
+    <t>2033-07-07 23:50:00</t>
+  </si>
+  <si>
+    <t>2033-09-20 06:30:00</t>
+  </si>
+  <si>
+    <t>2034-06-27 12:15:00</t>
+  </si>
+  <si>
+    <t>2034-10-16 08:45:00</t>
+  </si>
+  <si>
+    <t>2034-12-16 07:10:00</t>
+  </si>
+  <si>
+    <t>2035-07-20 13:00:00</t>
+  </si>
+  <si>
+    <t>2035-10-13 01:40:00</t>
+  </si>
+  <si>
+    <t>2036-08-22 09:30:00</t>
+  </si>
+  <si>
+    <t>2036-10-14 12:35:00</t>
+  </si>
+  <si>
+    <t>2037-05-03 21:20:00</t>
+  </si>
+  <si>
+    <t>2037-09-05 18:00:00</t>
+  </si>
+  <si>
+    <t>2037-09-19 18:30:00</t>
+  </si>
+  <si>
+    <t>2037-09-17 22:45:00</t>
+  </si>
+  <si>
+    <t>2037-09-07 19:00:00</t>
+  </si>
+  <si>
+    <t>2037-09-28 18:00:00</t>
+  </si>
+  <si>
+    <t>夏日電音派對</t>
+  </si>
+  <si>
+    <t>台北市大安區忠孝東路四段223巷10號</t>
+  </si>
+  <si>
+    <t>星光音樂會</t>
+  </si>
+  <si>
+    <t>台中市西區英才路600號（台中市民廣場）</t>
+  </si>
+  <si>
+    <t>AI科技講座</t>
+  </si>
+  <si>
+    <t>高雄市左營區博愛二路777號（高雄巨蛋會議廳）</t>
+  </si>
+  <si>
+    <t>當代攝影展</t>
+  </si>
+  <si>
+    <t>台北市中正區愛國西路49號（台北市立美術館）</t>
+  </si>
+  <si>
+    <t>花東慢活旅行</t>
+  </si>
+  <si>
+    <t>台東縣池上鄉中華路1號（池上車站前集合）</t>
+  </si>
+  <si>
+    <t>城市慢跑挑戰</t>
+  </si>
+  <si>
+    <t>台南市安平區健康路二段231號（安平運動公園）</t>
+  </si>
+  <si>
+    <t>RPG實境遊戲</t>
+  </si>
+  <si>
+    <t>新竹市東區林森路10號（新竹密室基地）</t>
+  </si>
+  <si>
+    <t>台灣小吃巡禮</t>
+  </si>
+  <si>
+    <t>台北市萬華區康定路173號（西門町集合）</t>
+  </si>
+  <si>
+    <t>廢墟攝影與探索</t>
+  </si>
+  <si>
+    <t>桃園市龍潭區文化路350號（龍潭老屋巷）</t>
+  </si>
+  <si>
+    <t>森林瑜伽週末</t>
+  </si>
+  <si>
+    <t>南投縣鹿谷鄉內湖村森林步道（溪頭教育中心）</t>
+  </si>
+  <si>
+    <t>一場結合水花與音樂的超嗨夏日派對</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>草地上享受星空與音樂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>談論最新人工智慧趨勢與應用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>展出台灣新銳攝影師的作品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>深入花東縱谷的自然與人文之旅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>晨跑活動＋健康餐盒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>團隊合作闖關的實境任務</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>帶你從北吃到南，認識特色小吃</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拍攝台灣廢棄建築的神祕之美</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>森林中進行瑜伽與靜心冥想</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>異國料理體驗營</t>
+  </si>
+  <si>
+    <t>花蓮縣花蓮市國聯一路100號（花蓮文化中心）</t>
+  </si>
+  <si>
+    <t>城市探索競賽</t>
+  </si>
+  <si>
+    <t>台中市西屯區文心路三段168號（文心森林公園）</t>
+  </si>
+  <si>
+    <t>慢食文化巡禮</t>
+  </si>
+  <si>
+    <t>新竹市東區光復路二段101號（清華大學）</t>
+  </si>
+  <si>
+    <t>夜跑派對</t>
+  </si>
+  <si>
+    <t>仲夏音樂祭</t>
+  </si>
+  <si>
+    <t>高雄市左營區博愛二路777號（高雄巨蛋）</t>
+  </si>
+  <si>
+    <t>親子DIY手作坊</t>
+  </si>
+  <si>
+    <t>桃園市中壢區中大路300號（中央大學）</t>
+  </si>
+  <si>
+    <t>原創桌遊大賽</t>
+  </si>
+  <si>
+    <t>南投縣魚池鄉日月村中山路163號（日月潭）</t>
+  </si>
+  <si>
+    <t>台北市信義區市府路45號（台北101）</t>
+  </si>
+  <si>
+    <t>AI未來論壇</t>
+  </si>
+  <si>
+    <t>嘉義市西區中山路1號（嘉義火車站前）</t>
+  </si>
+  <si>
+    <t>世界美食日</t>
+  </si>
+  <si>
+    <t>屏東縣恆春鎮墾丁路79號（墾丁大街）</t>
+  </si>
+  <si>
+    <t>台南市中西區南門路1號（台南孔廟）</t>
+  </si>
+  <si>
+    <t>森林寫生活動</t>
+  </si>
+  <si>
+    <t>街頭藝人之夜</t>
+  </si>
+  <si>
+    <t>華山文創園區</t>
+  </si>
+  <si>
+    <t>虛擬實境展覽</t>
+  </si>
+  <si>
+    <t>高雄流行音樂中心</t>
+  </si>
+  <si>
+    <t>新竹巨城</t>
+  </si>
+  <si>
+    <t>台中圓滿劇場</t>
+  </si>
+  <si>
+    <t>挑戰你的創造力與程式設計技能。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>專家講解人工智慧趨勢，適合對AI有興趣者。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在森林中靜心創作，與自然對話。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>動手做地中海料理，享受料理樂趣！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>匯集世界各地小吃，吃遍全球不出國！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>結合科技與藝術的創新展覽，啟發未來想像。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>透過鏡頭探索城市歷史與美學。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>看見街頭藝人的夢想與熱情。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>聚焦地方創新與永續發展。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>慢食文化與手工特色食材導覽體驗。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>認識在地飲食文化與手工特色食材。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>沙灘、音樂與比基尼的完美結合！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>享受涼爽夜晚與經典電影的陪伴。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>邀請知名樂團與DJ，一起搖滾整晚！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>夜色下的街道，與夥伴一起奔跑燃燒卡路里。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>親子共創屬於彼此的藝術品。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-08-20 18:00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:00:00</t>
+  </si>
+  <si>
+    <t>2027-10-01 18:00:00</t>
+  </si>
+  <si>
+    <t>2027-09-20 20:00:00</t>
+  </si>
+  <si>
+    <t>2027-07-10 10:00:00</t>
+  </si>
+  <si>
+    <t>2025-11-10 14:00:00</t>
+  </si>
+  <si>
+    <t>2025-11-01 18:00:00</t>
+  </si>
+  <si>
+    <t>2025-09-10 09:00:00</t>
+  </si>
+  <si>
+    <t>2024-03-15 10:00:00</t>
+  </si>
+  <si>
+    <t>2024-01-05 14:30:00</t>
+  </si>
+  <si>
+    <t>2025-05-01 08:00:00</t>
+  </si>
+  <si>
+    <t>2025-04-20 17:00:00</t>
+  </si>
+  <si>
+    <t>2025-03-01 10:00:00</t>
+  </si>
+  <si>
+    <t>2026-03-22 06:30:00</t>
+  </si>
+  <si>
+    <t>2026-02-01 11:00:00</t>
+  </si>
+  <si>
+    <t>2024-08-18 13:00:00</t>
+  </si>
+  <si>
+    <t>2024-08-10 18:00:00</t>
+  </si>
+  <si>
+    <t>2024-06-05 13:00:00</t>
+  </si>
+  <si>
+    <t>2027-02-10 10:00:00</t>
+  </si>
+  <si>
+    <t>2027-01-30 18:00:00</t>
+  </si>
+  <si>
+    <t>2026-12-01 16:30:00</t>
+  </si>
+  <si>
+    <t>2025-04-12 15:00:00</t>
+  </si>
+  <si>
+    <t>2025-04-01 20:00:00</t>
+  </si>
+  <si>
+    <t>2025-02-20 12:00:00</t>
+  </si>
+  <si>
+    <t>2030-09-28 09:00:00</t>
+  </si>
+  <si>
+    <t>2030-09-15 12:00:00</t>
+  </si>
+  <si>
+    <t>2030-08-01 11:45:00</t>
+  </si>
+  <si>
+    <t>2035-02-20 10:00:00</t>
+  </si>
+  <si>
+    <t>2035-02-03 10:00:00</t>
+  </si>
+  <si>
+    <t>2034-12-18 10:00:00</t>
+  </si>
+  <si>
+    <t>2024-08-08 11:00:00</t>
+  </si>
+  <si>
+    <t>2024-08-01 11:00:00</t>
+  </si>
+  <si>
+    <t>2024-06-17 11:00:00</t>
+  </si>
+  <si>
+    <t>2031-03-28 10:00:00</t>
+  </si>
+  <si>
+    <t>2031-03-18 10:00:00</t>
+  </si>
+  <si>
+    <t>2031-03-03 10:00:00</t>
+  </si>
+  <si>
+    <t>2031-05-12 19:00:00</t>
+  </si>
+  <si>
+    <t>2031-05-07 19:00:00</t>
+  </si>
+  <si>
+    <t>2031-03-22 19:00:00</t>
+  </si>
+  <si>
+    <t>2024-04-09 17:00:00</t>
+  </si>
+  <si>
+    <t>2024-03-26 17:00:00</t>
+  </si>
+  <si>
+    <t>2024-03-06 17:00:00</t>
+  </si>
+  <si>
+    <t>2029-08-29 12:00:00</t>
+  </si>
+  <si>
+    <t>2029-08-19 12:00:00</t>
+  </si>
+  <si>
+    <t>2029-07-30 12:00:00</t>
+  </si>
+  <si>
+    <t>2032-06-16 19:00:00</t>
+  </si>
+  <si>
+    <t>2032-06-07 19:00:00</t>
+  </si>
+  <si>
+    <t>2032-05-19 19:00:00</t>
+  </si>
+  <si>
+    <t>2027-08-06 09:00:00</t>
+  </si>
+  <si>
+    <t>2027-07-27 09:00:00</t>
+  </si>
+  <si>
+    <t>2027-07-01 09:00:00</t>
+  </si>
+  <si>
+    <t>2035-04-04 17:00:00</t>
+  </si>
+  <si>
+    <t>2035-03-15 17:00:00</t>
+  </si>
+  <si>
+    <t>2035-02-11 17:00:00</t>
+  </si>
+  <si>
+    <t>2031-06-08 09:00:00</t>
+  </si>
+  <si>
+    <t>2031-05-28 09:00:00</t>
+  </si>
+  <si>
+    <t>2031-04-26 09:00:00</t>
+  </si>
+  <si>
+    <t>2026-10-10 15:00:00</t>
+  </si>
+  <si>
+    <t>2026-10-01 15:00:00</t>
+  </si>
+  <si>
+    <t>2026-09-08 15:00:00</t>
+  </si>
+  <si>
+    <t>2033-11-24 12:00:00</t>
+  </si>
+  <si>
+    <t>2033-11-13 12:00:00</t>
+  </si>
+  <si>
+    <t>2033-10-05 12:00:00</t>
+  </si>
+  <si>
+    <t>2029-03-16 17:00:00</t>
+  </si>
+  <si>
+    <t>2029-03-07 17:00:00</t>
+  </si>
+  <si>
+    <t>2029-01-28 17:00:00</t>
+  </si>
+  <si>
+    <t>2031-03-09 10:00:00</t>
+  </si>
+  <si>
+    <t>2031-03-04 10:00:00</t>
+  </si>
+  <si>
+    <t>2031-01-27 10:00:00</t>
+  </si>
+  <si>
+    <t>2029-01-20 18:00:00</t>
+  </si>
+  <si>
+    <t>2029-01-05 18:00:00</t>
+  </si>
+  <si>
+    <t>2028-12-02 18:00:00</t>
+  </si>
+  <si>
+    <t>2026-06-10 15:00:00</t>
+  </si>
+  <si>
+    <t>2026-05-27 15:00:00</t>
+  </si>
+  <si>
+    <t>2026-04-24 15:00:00</t>
+  </si>
+  <si>
+    <t>2029-05-13 15:00:00</t>
+  </si>
+  <si>
+    <t>2029-05-03 15:00:00</t>
+  </si>
+  <si>
+    <t>2029-04-11 15:00:00</t>
+  </si>
+  <si>
+    <t>2023-04-24 11:00:00</t>
+  </si>
+  <si>
+    <t>2023-04-14 11:00:00</t>
+  </si>
+  <si>
+    <t>2023-03-01 11:00:00</t>
+  </si>
+  <si>
+    <t>2035-01-23 08:00:00</t>
+  </si>
+  <si>
+    <t>2035-01-14 08:00:00</t>
+  </si>
+  <si>
+    <t>2034-12-10 08:00:00</t>
+  </si>
+  <si>
+    <t>2034-03-14 19:00:00</t>
+  </si>
+  <si>
+    <t>2034-03-07 19:00:00</t>
+  </si>
+  <si>
+    <t>2034-01-21 19:00:00</t>
+  </si>
+  <si>
+    <t>2037-09-21 10:00:00</t>
+  </si>
+  <si>
+    <t>2037-09-11 10:00:00</t>
+  </si>
+  <si>
+    <t>2037-08-01 10:00:00</t>
+  </si>
+  <si>
+    <t>2026-05-22 09:00:00</t>
+  </si>
+  <si>
+    <t>2026-05-07 09:00:00</t>
+  </si>
+  <si>
+    <t>2026-03-24 09:00:00</t>
+  </si>
+  <si>
+    <t>2026-04-09 16:00:00</t>
+  </si>
+  <si>
+    <t>2026-03-23 16:00:00</t>
+  </si>
+  <si>
+    <t>2026-03-03 16:00:00</t>
+  </si>
+  <si>
+    <t>2030-12-09 11:00:00</t>
+  </si>
+  <si>
+    <t>2030-11-23 11:00:00</t>
+  </si>
+  <si>
+    <t>2030-10-13 11:00:00</t>
+  </si>
+  <si>
+    <t>2031-02-22 09:00:00</t>
+  </si>
+  <si>
+    <t>2031-02-08 09:00:00</t>
+  </si>
+  <si>
+    <t>2030-12-23 09:00:00</t>
+  </si>
+  <si>
+    <t>2032-04-21 18:00:00</t>
+  </si>
+  <si>
+    <t>2032-04-10 18:00:00</t>
+  </si>
+  <si>
+    <t>2032-03-01 18:00:00</t>
+  </si>
+  <si>
+    <t>2025-11-29 12:00:00</t>
+  </si>
+  <si>
+    <t>2025-11-12 12:00:00</t>
+  </si>
+  <si>
+    <t>2025-10-05 12:00:00</t>
+  </si>
+  <si>
+    <t>2036-12-03 15:00:00</t>
+  </si>
+  <si>
+    <t>2036-11-15 15:00:00</t>
+  </si>
+  <si>
+    <t>2036-10-01 15:00:00</t>
+  </si>
+  <si>
+    <t>2028-10-27 14:00:00</t>
+  </si>
+  <si>
+    <t>2028-10-12 14:00:00</t>
+  </si>
+  <si>
+    <t>2028-09-01 14:00:00</t>
+  </si>
+  <si>
+    <t>2026-08-16 00:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-03-11 00:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-03-16 00:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1551,7 +2136,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1584,16 +2169,26 @@
       <b/>
       <sz val="9"/>
       <color indexed="81"/>
-      <name val="Tahoma"/>
+      <name val="細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="新細明體"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="細明體"/>
-      <family val="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
       <charset val="136"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1625,10 +2220,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1640,17 +2236,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1658,25 +2245,31 @@
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="超連結" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1954,7 +2547,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q163"/>
+  <dimension ref="A1:Q160"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.125" style="1" customWidth="1"/>
@@ -1968,61 +2561,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="K1" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="L1" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="M1" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="N1" s="15"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="5" t="s">
         <v>185</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="9" t="s">
         <v>3</v>
       </c>
       <c r="F2" s="5" t="s">
@@ -2037,430 +2629,424 @@
       <c r="I2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="J2" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="K2" s="13" t="s">
+      <c r="K2" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="L2" s="13" t="s">
+      <c r="L2" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="M2" s="13" t="s">
+      <c r="M2" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" s="6">
+      <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="D3" s="2">
+        <v>3</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="2">
+        <v>177</v>
+      </c>
+      <c r="H3" s="2">
+        <v>500</v>
+      </c>
+      <c r="I3" s="2">
+        <v>78</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="M3" s="8">
+        <v>1</v>
+      </c>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C4" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D4" s="2">
         <v>5</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E4" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="6">
+      <c r="F4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="2">
         <v>30</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H4" s="2">
         <v>35000</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I4" s="2">
         <v>5</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J4" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="K3" s="8" t="s">
-        <v>459</v>
-      </c>
-      <c r="L3" s="8" t="s">
+      <c r="K4" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="L4" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="M3" s="16">
+      <c r="M4" s="8">
         <v>1</v>
       </c>
-      <c r="N3" s="15"/>
-      <c r="O3" s="10"/>
-      <c r="P3" s="10"/>
-      <c r="Q3" s="10"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="6">
-        <v>2</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="D4" s="6">
-        <v>8</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="6">
-        <v>70</v>
-      </c>
-      <c r="H4" s="6">
-        <v>0</v>
-      </c>
-      <c r="I4" s="6">
-        <v>2</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>432</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>338</v>
-      </c>
-      <c r="M4" s="16">
-        <v>1</v>
-      </c>
-      <c r="N4" s="15"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="10"/>
-      <c r="Q4" s="10"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>154</v>
+        <v>478</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>183</v>
+        <v>495</v>
       </c>
       <c r="D5" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>124</v>
+        <v>479</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G5" s="2">
+        <v>250</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
         <v>65</v>
       </c>
-      <c r="H5" s="2">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2">
-        <v>48</v>
-      </c>
       <c r="J5" s="3" t="s">
-        <v>261</v>
+        <v>552</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>449</v>
+        <v>659</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="M5" s="11">
+        <v>553</v>
+      </c>
+      <c r="M5" s="8">
         <v>1</v>
       </c>
-      <c r="N5" s="15"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="D6" s="2">
+        <v>8</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="2">
+        <v>70</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>2</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="M6" s="8">
         <v>1</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="2">
-        <v>1100</v>
-      </c>
-      <c r="H6" s="2">
-        <v>0</v>
-      </c>
-      <c r="I6" s="2">
-        <v>12</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="M6" s="11">
-        <v>1</v>
-      </c>
-      <c r="O6" s="10"/>
-      <c r="P6" s="10"/>
-      <c r="Q6" s="10"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>70</v>
+        <v>154</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>89</v>
+        <v>183</v>
       </c>
       <c r="D7" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G7" s="2">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H7" s="2">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>237</v>
+        <v>261</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>425</v>
+        <v>380</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="M7" s="11">
+        <v>355</v>
+      </c>
+      <c r="M7" s="8">
         <v>1</v>
       </c>
-      <c r="O7" s="10"/>
-      <c r="P7" s="10"/>
-      <c r="Q7" s="10"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>8</v>
+        <v>129</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G8" s="2">
-        <v>1900</v>
+        <v>1100</v>
       </c>
       <c r="H8" s="2">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>431</v>
+        <v>381</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="M8" s="11">
+        <v>358</v>
+      </c>
+      <c r="M8" s="8">
         <v>1</v>
       </c>
-      <c r="O8" s="10"/>
-      <c r="P8" s="10"/>
-      <c r="Q8" s="10"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>26</v>
+        <v>504</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>171</v>
+        <v>532</v>
       </c>
       <c r="D9" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>130</v>
+        <v>503</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G9" s="2">
-        <v>1000</v>
+        <v>226</v>
       </c>
       <c r="H9" s="2">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="I9" s="2">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>249</v>
+        <v>583</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>437</v>
+        <v>584</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="M9" s="11">
+        <v>585</v>
+      </c>
+      <c r="M9" s="8">
         <v>1</v>
       </c>
-      <c r="O9" s="10"/>
-      <c r="P9" s="10"/>
-      <c r="Q9" s="10"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>148</v>
+        <v>70</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>177</v>
+        <v>89</v>
       </c>
       <c r="D10" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G10" s="2">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="H10" s="2">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="I10" s="2">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>433</v>
+        <v>382</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="M10" s="11">
+        <v>331</v>
+      </c>
+      <c r="M10" s="8">
         <v>1</v>
       </c>
-      <c r="O10" s="10"/>
-      <c r="P10" s="10"/>
-      <c r="Q10" s="10"/>
+      <c r="O10" s="7"/>
+      <c r="P10" s="7"/>
+      <c r="Q10" s="7"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="D11" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G11" s="2">
-        <v>800</v>
+        <v>1900</v>
       </c>
       <c r="H11" s="2">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="I11" s="2">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>434</v>
+        <v>383</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="M11" s="11">
+        <v>337</v>
+      </c>
+      <c r="M11" s="8">
         <v>1</v>
       </c>
-      <c r="O11" s="10"/>
-      <c r="P11" s="10"/>
-      <c r="Q11" s="10"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>153</v>
+        <v>26</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="D12" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>130</v>
@@ -2469,262 +3055,262 @@
         <v>11</v>
       </c>
       <c r="G12" s="2">
-        <v>1600</v>
+        <v>1000</v>
       </c>
       <c r="H12" s="2">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="I12" s="2">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>446</v>
+        <v>384</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="M12" s="11">
+        <v>343</v>
+      </c>
+      <c r="M12" s="8">
         <v>1</v>
       </c>
-      <c r="O12" s="10"/>
-      <c r="P12" s="10"/>
-      <c r="Q12" s="10"/>
+      <c r="O12" s="7"/>
+      <c r="P12" s="7"/>
+      <c r="Q12" s="7"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>11</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D13" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G13" s="2">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="H13" s="2">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="I13" s="2">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>424</v>
+        <v>385</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="M13" s="11">
+        <v>339</v>
+      </c>
+      <c r="M13" s="8">
         <v>1</v>
       </c>
-      <c r="O13" s="10"/>
-      <c r="P13" s="10"/>
-      <c r="Q13" s="10"/>
+      <c r="O13" s="7"/>
+      <c r="P13" s="7"/>
+      <c r="Q13" s="7"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>88</v>
+        <v>171</v>
       </c>
       <c r="D14" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>96</v>
+        <v>142</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G14" s="2">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="H14" s="2">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>423</v>
+        <v>386</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="M14" s="11">
+        <v>340</v>
+      </c>
+      <c r="M14" s="8">
         <v>1</v>
       </c>
-      <c r="O14" s="10"/>
-      <c r="P14" s="10"/>
-      <c r="Q14" s="10"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="7"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>13</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>34</v>
+        <v>153</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="D15" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G15" s="2">
-        <v>1900</v>
+        <v>1600</v>
       </c>
       <c r="H15" s="2">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>442</v>
+        <v>387</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="M15" s="11">
+        <v>352</v>
+      </c>
+      <c r="M15" s="8">
         <v>1</v>
       </c>
-      <c r="O15" s="10"/>
-      <c r="P15" s="10"/>
-      <c r="Q15" s="10"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>14</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>145</v>
+        <v>484</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>175</v>
+        <v>498</v>
       </c>
       <c r="D16" s="2">
         <v>7</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>124</v>
+        <v>485</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G16" s="2">
-        <v>1500</v>
+        <v>60</v>
       </c>
       <c r="H16" s="2">
-        <v>1400</v>
+        <v>600</v>
       </c>
       <c r="I16" s="2">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>247</v>
+        <v>559</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>435</v>
+        <v>560</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="M16" s="11">
+        <v>561</v>
+      </c>
+      <c r="M16" s="8">
         <v>1</v>
       </c>
-      <c r="O16" s="10"/>
-      <c r="P16" s="10"/>
-      <c r="Q16" s="10"/>
+      <c r="O16" s="7"/>
+      <c r="P16" s="7"/>
+      <c r="Q16" s="7"/>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>15</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>26</v>
+        <v>504</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>28</v>
+        <v>529</v>
       </c>
       <c r="D17" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>27</v>
+        <v>505</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G17" s="2">
-        <v>1000</v>
+        <v>406</v>
       </c>
       <c r="H17" s="2">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="I17" s="2">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>282</v>
+        <v>574</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>470</v>
+        <v>575</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="M17" s="11">
+        <v>576</v>
+      </c>
+      <c r="M17" s="8">
         <v>1</v>
       </c>
-      <c r="O17" s="10"/>
-      <c r="P17" s="10"/>
-      <c r="Q17" s="10"/>
+      <c r="O17" s="7"/>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>16</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>12</v>
+        <v>134</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="D18" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>122</v>
@@ -2733,95 +3319,95 @@
         <v>11</v>
       </c>
       <c r="G18" s="2">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="H18" s="2">
         <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>422</v>
+        <v>388</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="M18" s="11">
+        <v>330</v>
+      </c>
+      <c r="M18" s="8">
         <v>1</v>
       </c>
-      <c r="O18" s="10"/>
-      <c r="P18" s="10"/>
-      <c r="Q18" s="10"/>
+      <c r="O18" s="7"/>
+      <c r="P18" s="7"/>
+      <c r="Q18" s="7"/>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>17</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>174</v>
+        <v>88</v>
       </c>
       <c r="D19" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G19" s="2">
-        <v>1400</v>
+        <v>200</v>
       </c>
       <c r="H19" s="2">
-        <v>1400</v>
+        <v>4500</v>
       </c>
       <c r="I19" s="2">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>273</v>
+        <v>235</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>461</v>
+        <v>389</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="M19" s="11">
+        <v>329</v>
+      </c>
+      <c r="M19" s="8">
         <v>1</v>
       </c>
-      <c r="O19" s="10"/>
-      <c r="P19" s="10"/>
-      <c r="Q19" s="10"/>
+      <c r="O19" s="7"/>
+      <c r="P19" s="7"/>
+      <c r="Q19" s="7"/>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>18</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>54</v>
+        <v>157</v>
       </c>
       <c r="D20" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>41</v>
+        <v>147</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G20" s="2">
-        <v>1000</v>
+        <v>1900</v>
       </c>
       <c r="H20" s="2">
         <v>200</v>
@@ -2830,960 +3416,960 @@
         <v>7</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>278</v>
+        <v>254</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>466</v>
+        <v>390</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="M20" s="11">
+        <v>348</v>
+      </c>
+      <c r="M20" s="8">
         <v>1</v>
       </c>
-      <c r="O20" s="10"/>
-      <c r="P20" s="10"/>
-      <c r="Q20" s="10"/>
+      <c r="O20" s="7"/>
+      <c r="P20" s="7"/>
+      <c r="Q20" s="7"/>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>19</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>44</v>
+        <v>145</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="D21" s="2">
         <v>7</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G21" s="2">
-        <v>200</v>
+        <v>1500</v>
       </c>
       <c r="H21" s="2">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="I21" s="2">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>270</v>
+        <v>247</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>458</v>
+        <v>391</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="M21" s="11">
+        <v>341</v>
+      </c>
+      <c r="M21" s="8">
         <v>1</v>
       </c>
-      <c r="O21" s="10"/>
-      <c r="P21" s="10"/>
-      <c r="Q21" s="10"/>
+      <c r="O21" s="7"/>
+      <c r="P21" s="7"/>
+      <c r="Q21" s="7"/>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>20</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>132</v>
+        <v>26</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>163</v>
+        <v>28</v>
       </c>
       <c r="D22" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>142</v>
+        <v>27</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G22" s="2">
-        <v>1800</v>
+        <v>1000</v>
       </c>
       <c r="H22" s="2">
-        <v>1100</v>
+        <v>300</v>
       </c>
       <c r="I22" s="2">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>454</v>
+        <v>392</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="M22" s="11">
+        <v>376</v>
+      </c>
+      <c r="M22" s="8">
         <v>1</v>
       </c>
-      <c r="O22" s="10"/>
-      <c r="P22" s="10"/>
-      <c r="Q22" s="10"/>
+      <c r="O22" s="7"/>
+      <c r="P22" s="7"/>
+      <c r="Q22" s="7"/>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>21</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="6">
+      <c r="B23" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="D23" s="2">
+        <v>2</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23" s="2">
+        <v>600</v>
+      </c>
+      <c r="H23" s="2">
+        <v>0</v>
+      </c>
+      <c r="I23" s="2">
+        <v>19</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="M23" s="8">
         <v>1</v>
       </c>
-      <c r="E23" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G23" s="6">
-        <v>50</v>
-      </c>
-      <c r="H23" s="6">
-        <v>300</v>
-      </c>
-      <c r="I23" s="6">
-        <v>1</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="M23" s="11">
-        <v>1</v>
-      </c>
-      <c r="O23" s="10"/>
-      <c r="P23" s="10"/>
-      <c r="Q23" s="10"/>
+      <c r="O23" s="7"/>
+      <c r="P23" s="7"/>
+      <c r="Q23" s="7"/>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>22</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>132</v>
+        <v>12</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="D24" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G24" s="2">
-        <v>600</v>
+        <v>1400</v>
       </c>
       <c r="H24" s="2">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="I24" s="2">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>250</v>
+        <v>273</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>438</v>
+        <v>394</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="M24" s="11">
+        <v>367</v>
+      </c>
+      <c r="M24" s="8">
         <v>1</v>
       </c>
-      <c r="O24" s="10"/>
-      <c r="P24" s="10"/>
-      <c r="Q24" s="10"/>
+      <c r="O24" s="7"/>
+      <c r="P24" s="7"/>
+      <c r="Q24" s="7"/>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>23</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D25" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G25" s="2">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="H25" s="2">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I25" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>453</v>
+        <v>395</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="M25" s="11">
+        <v>372</v>
+      </c>
+      <c r="M25" s="8">
         <v>1</v>
       </c>
-      <c r="O25" s="10"/>
-      <c r="P25" s="10"/>
-      <c r="Q25" s="10"/>
+      <c r="O25" s="7"/>
+      <c r="P25" s="7"/>
+      <c r="Q25" s="7"/>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>24</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>87</v>
+        <v>156</v>
       </c>
       <c r="D26" s="2">
+        <v>7</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26" s="2">
+        <v>200</v>
+      </c>
+      <c r="H26" s="2">
+        <v>0</v>
+      </c>
+      <c r="I26" s="2">
+        <v>9</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="M26" s="8">
         <v>1</v>
       </c>
-      <c r="E26" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G26" s="2">
-        <v>85</v>
-      </c>
-      <c r="H26" s="2">
-        <v>7300</v>
-      </c>
-      <c r="I26" s="2">
-        <v>40</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="M26" s="11">
-        <v>1</v>
-      </c>
-      <c r="O26" s="10"/>
-      <c r="P26" s="10"/>
-      <c r="Q26" s="10"/>
+      <c r="O26" s="7"/>
+      <c r="P26" s="7"/>
+      <c r="Q26" s="7"/>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>25</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>12</v>
+        <v>132</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
       <c r="D27" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>14</v>
+        <v>142</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G27" s="2">
-        <v>2000</v>
+        <v>1800</v>
       </c>
       <c r="H27" s="2">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="I27" s="2">
+        <v>29</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="M27" s="8">
         <v>1</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="M27" s="11">
-        <v>1</v>
-      </c>
-      <c r="O27" s="10"/>
-      <c r="P27" s="10"/>
-      <c r="Q27" s="10"/>
+      <c r="O27" s="7"/>
+      <c r="P27" s="7"/>
+      <c r="Q27" s="7"/>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>26</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G28" s="2">
-        <v>5000</v>
+        <v>50</v>
       </c>
       <c r="H28" s="2">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="I28" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>448</v>
+        <v>398</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="M28" s="11">
+        <v>374</v>
+      </c>
+      <c r="M28" s="8">
         <v>1</v>
       </c>
-      <c r="O28" s="10"/>
-      <c r="P28" s="10"/>
-      <c r="Q28" s="10"/>
+      <c r="O28" s="7"/>
+      <c r="P28" s="7"/>
+      <c r="Q28" s="7"/>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>27</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>26</v>
+        <v>132</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="D29" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G29" s="2">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="H29" s="2">
         <v>0</v>
       </c>
       <c r="I29" s="2">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>451</v>
+        <v>399</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="M29" s="11">
+        <v>344</v>
+      </c>
+      <c r="M29" s="8">
         <v>1</v>
       </c>
-      <c r="O29" s="10"/>
-      <c r="P29" s="10"/>
-      <c r="Q29" s="10"/>
+      <c r="O29" s="7"/>
+      <c r="P29" s="7"/>
+      <c r="Q29" s="7"/>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>28</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>144</v>
+        <v>34</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>173</v>
+        <v>51</v>
       </c>
       <c r="D30" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>130</v>
+        <v>35</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G30" s="2">
-        <v>1900</v>
+        <v>500</v>
       </c>
       <c r="H30" s="2">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I30" s="2">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>445</v>
+        <v>400</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="M30" s="11">
+        <v>359</v>
+      </c>
+      <c r="M30" s="8">
         <v>1</v>
       </c>
-      <c r="O30" s="10"/>
-      <c r="P30" s="10"/>
-      <c r="Q30" s="10"/>
+      <c r="O30" s="7"/>
+      <c r="P30" s="7"/>
+      <c r="Q30" s="7"/>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>29</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>180</v>
+        <v>87</v>
       </c>
       <c r="D31" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>147</v>
+        <v>114</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G31" s="2">
-        <v>1600</v>
+        <v>85</v>
       </c>
       <c r="H31" s="2">
-        <v>0</v>
+        <v>7300</v>
       </c>
       <c r="I31" s="2">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>427</v>
+        <v>401</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="M31" s="11">
+        <v>335</v>
+      </c>
+      <c r="M31" s="8">
         <v>1</v>
       </c>
-      <c r="O31" s="10"/>
-      <c r="P31" s="10"/>
-      <c r="Q31" s="10"/>
+      <c r="O31" s="7"/>
+      <c r="P31" s="7"/>
+      <c r="Q31" s="7"/>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>30</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="D32" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G32" s="2">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="H32" s="2">
-        <v>150</v>
+        <v>1200</v>
       </c>
       <c r="I32" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>456</v>
+        <v>402</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="M32" s="11">
-        <v>0</v>
-      </c>
-      <c r="O32" s="10"/>
-      <c r="P32" s="10"/>
-      <c r="Q32" s="10"/>
+        <v>375</v>
+      </c>
+      <c r="M32" s="8">
+        <v>1</v>
+      </c>
+      <c r="O32" s="7"/>
+      <c r="P32" s="7"/>
+      <c r="Q32" s="7"/>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>31</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>8</v>
+        <v>488</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="D33" s="2">
+        <v>9</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G33" s="2">
+        <v>15</v>
+      </c>
+      <c r="H33" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I33" s="2">
+        <v>61</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="M33" s="8">
         <v>1</v>
       </c>
-      <c r="E33" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G33" s="2">
-        <v>50</v>
-      </c>
-      <c r="H33" s="2">
-        <v>300</v>
-      </c>
-      <c r="I33" s="2">
-        <v>1</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="M33" s="11">
-        <v>1</v>
-      </c>
-      <c r="O33" s="10"/>
-      <c r="P33" s="10"/>
-      <c r="Q33" s="10"/>
+      <c r="O33" s="7"/>
+      <c r="P33" s="7"/>
+      <c r="Q33" s="7"/>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>32</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>60</v>
+        <v>480</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>89</v>
+        <v>496</v>
       </c>
       <c r="D34" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>97</v>
+        <v>481</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G34" s="2">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="H34" s="2">
-        <v>7600</v>
+        <v>4000</v>
       </c>
       <c r="I34" s="2">
-        <v>4</v>
+        <v>99</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>242</v>
+        <v>554</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>430</v>
+        <v>555</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="M34" s="11">
+        <v>556</v>
+      </c>
+      <c r="M34" s="8">
         <v>1</v>
       </c>
-      <c r="O34" s="10"/>
-      <c r="P34" s="10"/>
-      <c r="Q34" s="10"/>
+      <c r="O34" s="7"/>
+      <c r="P34" s="7"/>
+      <c r="Q34" s="7"/>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>33</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>168</v>
+        <v>53</v>
       </c>
       <c r="D35" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>126</v>
+        <v>39</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G35" s="2">
-        <v>200</v>
+        <v>5000</v>
       </c>
       <c r="H35" s="2">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="I35" s="2">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>447</v>
+        <v>403</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="M35" s="11">
-        <v>0</v>
-      </c>
-      <c r="O35" s="10"/>
-      <c r="P35" s="10"/>
-      <c r="Q35" s="10"/>
+        <v>354</v>
+      </c>
+      <c r="M35" s="8">
+        <v>1</v>
+      </c>
+      <c r="O35" s="7"/>
+      <c r="P35" s="7"/>
+      <c r="Q35" s="7"/>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>34</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>136</v>
+        <v>26</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D36" s="2">
+        <v>3</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G36" s="2">
+        <v>300</v>
+      </c>
+      <c r="H36" s="2">
+        <v>0</v>
+      </c>
+      <c r="I36" s="2">
+        <v>2</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="M36" s="8">
         <v>1</v>
       </c>
-      <c r="E36" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G36" s="2">
-        <v>1500</v>
-      </c>
-      <c r="H36" s="2">
-        <v>700</v>
-      </c>
-      <c r="I36" s="2">
-        <v>8</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="K36" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="L36" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="M36" s="11">
-        <v>0</v>
-      </c>
-      <c r="O36" s="10"/>
-      <c r="P36" s="10"/>
-      <c r="Q36" s="10"/>
+      <c r="O36" s="7"/>
+      <c r="P36" s="7"/>
+      <c r="Q36" s="7"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>35</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>29</v>
+        <v>144</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>31</v>
+        <v>173</v>
       </c>
       <c r="D37" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>30</v>
+        <v>130</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G37" s="2">
-        <v>50</v>
+        <v>1900</v>
       </c>
       <c r="H37" s="2">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I37" s="2">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>471</v>
+        <v>405</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="M37" s="11">
-        <v>0</v>
-      </c>
-      <c r="O37" s="10"/>
-      <c r="P37" s="10"/>
-      <c r="Q37" s="10"/>
+        <v>351</v>
+      </c>
+      <c r="M37" s="8">
+        <v>1</v>
+      </c>
+      <c r="O37" s="7"/>
+      <c r="P37" s="7"/>
+      <c r="Q37" s="7"/>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>36</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="D38" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G38" s="2">
-        <v>2000</v>
+        <v>1600</v>
       </c>
       <c r="H38" s="2">
         <v>0</v>
       </c>
       <c r="I38" s="2">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>276</v>
+        <v>239</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>464</v>
+        <v>406</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="M38" s="11">
-        <v>0</v>
-      </c>
-      <c r="O38" s="10"/>
-      <c r="P38" s="10"/>
-      <c r="Q38" s="10"/>
+        <v>333</v>
+      </c>
+      <c r="M38" s="8">
+        <v>1</v>
+      </c>
+      <c r="O38" s="7"/>
+      <c r="P38" s="7"/>
+      <c r="Q38" s="7"/>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>37</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>141</v>
+        <v>42</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>170</v>
+        <v>55</v>
       </c>
       <c r="D39" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>137</v>
+        <v>43</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G39" s="2">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="H39" s="2">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="I39" s="2">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>465</v>
+        <v>407</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="M39" s="11">
-        <v>0</v>
-      </c>
-      <c r="O39" s="10"/>
-      <c r="P39" s="10"/>
-      <c r="Q39" s="10"/>
+        <v>362</v>
+      </c>
+      <c r="M39" s="8">
+        <v>0</v>
+      </c>
+      <c r="O39" s="7"/>
+      <c r="P39" s="7"/>
+      <c r="Q39" s="7"/>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>38</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D40" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G40" s="2">
-        <v>2000</v>
+        <v>50</v>
       </c>
       <c r="H40" s="2">
-        <v>1200</v>
+        <v>300</v>
       </c>
       <c r="I40" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>443</v>
+        <v>408</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="M40" s="11">
-        <v>0</v>
-      </c>
-      <c r="O40" s="10"/>
-      <c r="P40" s="10"/>
-      <c r="Q40" s="10"/>
+        <v>347</v>
+      </c>
+      <c r="M40" s="8">
+        <v>1</v>
+      </c>
+      <c r="O40" s="7"/>
+      <c r="P40" s="7"/>
+      <c r="Q40" s="7"/>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>39</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>169</v>
+        <v>89</v>
       </c>
       <c r="D41" s="2">
         <v>3</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>124</v>
+        <v>97</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G41" s="2">
-        <v>85</v>
+        <v>300</v>
       </c>
       <c r="H41" s="2">
-        <v>0</v>
+        <v>7600</v>
       </c>
       <c r="I41" s="2">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>275</v>
+        <v>242</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>463</v>
+        <v>409</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="M41" s="11">
-        <v>0</v>
-      </c>
-      <c r="O41" s="10"/>
-      <c r="P41" s="10"/>
-      <c r="Q41" s="10"/>
+        <v>336</v>
+      </c>
+      <c r="M41" s="8">
+        <v>1</v>
+      </c>
+      <c r="O41" s="7"/>
+      <c r="P41" s="7"/>
+      <c r="Q41" s="7"/>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>40</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>91</v>
+        <v>168</v>
       </c>
       <c r="D42" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>11</v>
@@ -3792,246 +4378,246 @@
         <v>200</v>
       </c>
       <c r="H42" s="2">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="I42" s="2">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>428</v>
+        <v>410</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="M42" s="11">
-        <v>0</v>
-      </c>
-      <c r="O42" s="10"/>
-      <c r="P42" s="10"/>
-      <c r="Q42" s="10"/>
+        <v>353</v>
+      </c>
+      <c r="M42" s="8">
+        <v>0</v>
+      </c>
+      <c r="O42" s="7"/>
+      <c r="P42" s="7"/>
+      <c r="Q42" s="7"/>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>41</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>127</v>
+        <v>476</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>159</v>
+        <v>494</v>
       </c>
       <c r="D43" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>126</v>
+        <v>477</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G43" s="2">
-        <v>1500</v>
+        <v>80</v>
       </c>
       <c r="H43" s="2">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I43" s="2">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>269</v>
+        <v>549</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>457</v>
+        <v>550</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="M43" s="11">
-        <v>0</v>
-      </c>
-      <c r="O43" s="10"/>
-      <c r="P43" s="10"/>
-      <c r="Q43" s="10"/>
+        <v>551</v>
+      </c>
+      <c r="M43" s="8">
+        <v>0</v>
+      </c>
+      <c r="O43" s="7"/>
+      <c r="P43" s="7"/>
+      <c r="Q43" s="7"/>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>42</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="D44" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G44" s="2">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="H44" s="2">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="I44" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>252</v>
+        <v>202</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>440</v>
+        <v>411</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="M44" s="11">
-        <v>0</v>
-      </c>
-      <c r="O44" s="10"/>
-      <c r="P44" s="10"/>
-      <c r="Q44" s="10"/>
+        <v>296</v>
+      </c>
+      <c r="M44" s="8">
+        <v>0</v>
+      </c>
+      <c r="O44" s="7"/>
+      <c r="P44" s="7"/>
+      <c r="Q44" s="7"/>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>43</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>76</v>
+        <v>506</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>89</v>
+        <v>533</v>
       </c>
       <c r="D45" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>111</v>
+        <v>526</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G45" s="2">
-        <v>150</v>
+        <v>121</v>
       </c>
       <c r="H45" s="2">
-        <v>7200</v>
+        <v>2000</v>
       </c>
       <c r="I45" s="2">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>218</v>
+        <v>649</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>406</v>
+        <v>650</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="M45" s="11">
-        <v>0</v>
-      </c>
-      <c r="O45" s="10"/>
-      <c r="P45" s="10"/>
-      <c r="Q45" s="10"/>
+        <v>651</v>
+      </c>
+      <c r="M45" s="8">
+        <v>0</v>
+      </c>
+      <c r="O45" s="7"/>
+      <c r="P45" s="7"/>
+      <c r="Q45" s="7"/>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>44</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>152</v>
+        <v>29</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>181</v>
+        <v>31</v>
       </c>
       <c r="D46" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G46" s="2">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H46" s="2">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I46" s="2">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>455</v>
+        <v>412</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="M46" s="11">
-        <v>0</v>
-      </c>
-      <c r="O46" s="10"/>
-      <c r="P46" s="10"/>
-      <c r="Q46" s="10"/>
+        <v>377</v>
+      </c>
+      <c r="M46" s="8">
+        <v>0</v>
+      </c>
+      <c r="O46" s="7"/>
+      <c r="P46" s="7"/>
+      <c r="Q46" s="7"/>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>45</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D47" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G47" s="2">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="H47" s="2">
         <v>0</v>
       </c>
       <c r="I47" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>232</v>
+        <v>276</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="M47" s="11">
-        <v>0</v>
-      </c>
-      <c r="O47" s="10"/>
-      <c r="P47" s="10"/>
-      <c r="Q47" s="10"/>
+        <v>370</v>
+      </c>
+      <c r="M47" s="8">
+        <v>0</v>
+      </c>
+      <c r="O47" s="7"/>
+      <c r="P47" s="7"/>
+      <c r="Q47" s="7"/>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
@@ -4053,265 +4639,265 @@
         <v>11</v>
       </c>
       <c r="G48" s="2">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H48" s="2">
         <v>0</v>
       </c>
       <c r="I48" s="2">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>238</v>
+        <v>277</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="M48" s="11">
-        <v>0</v>
-      </c>
-      <c r="O48" s="10"/>
-      <c r="P48" s="10"/>
-      <c r="Q48" s="10"/>
+        <v>371</v>
+      </c>
+      <c r="M48" s="8">
+        <v>0</v>
+      </c>
+      <c r="O48" s="7"/>
+      <c r="P48" s="7"/>
+      <c r="Q48" s="7"/>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>47</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D49" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G49" s="2">
-        <v>80</v>
+        <v>2000</v>
       </c>
       <c r="H49" s="2">
-        <v>6000</v>
+        <v>1200</v>
       </c>
       <c r="I49" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>450</v>
+        <v>415</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="M49" s="11">
-        <v>0</v>
-      </c>
-      <c r="O49" s="10"/>
-      <c r="P49" s="10"/>
-      <c r="Q49" s="10"/>
+        <v>349</v>
+      </c>
+      <c r="M49" s="8">
+        <v>0</v>
+      </c>
+      <c r="O49" s="7"/>
+      <c r="P49" s="7"/>
+      <c r="Q49" s="7"/>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>48</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>44</v>
+        <v>140</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="D50" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G50" s="2">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="H50" s="2">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="I50" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>460</v>
+        <v>416</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="M50" s="11">
-        <v>0</v>
-      </c>
-      <c r="O50" s="10"/>
-      <c r="P50" s="10"/>
-      <c r="Q50" s="10"/>
+        <v>369</v>
+      </c>
+      <c r="M50" s="8">
+        <v>0</v>
+      </c>
+      <c r="O50" s="7"/>
+      <c r="P50" s="7"/>
+      <c r="Q50" s="7"/>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>49</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>44</v>
+        <v>482</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>156</v>
+        <v>497</v>
       </c>
       <c r="D51" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>131</v>
+        <v>483</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G51" s="2">
-        <v>1800</v>
+        <v>150</v>
       </c>
       <c r="H51" s="2">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="I51" s="2">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>256</v>
+        <v>557</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>444</v>
+        <v>660</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="M51" s="11">
-        <v>0</v>
-      </c>
-      <c r="O51" s="10"/>
-      <c r="P51" s="10"/>
-      <c r="Q51" s="10"/>
+        <v>558</v>
+      </c>
+      <c r="M51" s="8">
+        <v>0</v>
+      </c>
+      <c r="O51" s="7"/>
+      <c r="P51" s="7"/>
+      <c r="Q51" s="7"/>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>50</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>34</v>
+        <v>522</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>157</v>
+        <v>541</v>
       </c>
       <c r="D52" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>123</v>
+        <v>514</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G52" s="2">
-        <v>1600</v>
+        <v>394</v>
       </c>
       <c r="H52" s="2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I52" s="2">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>216</v>
+        <v>637</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>404</v>
+        <v>638</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="M52" s="11">
-        <v>0</v>
-      </c>
-      <c r="O52" s="10"/>
-      <c r="P52" s="10"/>
-      <c r="Q52" s="10"/>
+        <v>639</v>
+      </c>
+      <c r="M52" s="8">
+        <v>0</v>
+      </c>
+      <c r="O52" s="7"/>
+      <c r="P52" s="7"/>
+      <c r="Q52" s="7"/>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>51</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="D53" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>47</v>
+        <v>108</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G53" s="2">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="H53" s="2">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="I53" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>279</v>
+        <v>240</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>467</v>
+        <v>417</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="M53" s="11">
-        <v>0</v>
-      </c>
-      <c r="O53" s="10"/>
-      <c r="P53" s="10"/>
-      <c r="Q53" s="10"/>
+        <v>334</v>
+      </c>
+      <c r="M53" s="8">
+        <v>0</v>
+      </c>
+      <c r="O53" s="7"/>
+      <c r="P53" s="7"/>
+      <c r="Q53" s="7"/>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>52</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D54" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>11</v>
@@ -4323,83 +4909,83 @@
         <v>0</v>
       </c>
       <c r="I54" s="2">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>199</v>
+        <v>269</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>387</v>
+        <v>418</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="M54" s="11">
-        <v>0</v>
-      </c>
-      <c r="O54" s="10"/>
-      <c r="P54" s="10"/>
-      <c r="Q54" s="10"/>
+        <v>363</v>
+      </c>
+      <c r="M54" s="8">
+        <v>0</v>
+      </c>
+      <c r="O54" s="7"/>
+      <c r="P54" s="7"/>
+      <c r="Q54" s="7"/>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>53</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>136</v>
+        <v>521</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>166</v>
+        <v>540</v>
       </c>
       <c r="D55" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>137</v>
+        <v>523</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G55" s="2">
-        <v>90</v>
+        <v>215</v>
       </c>
       <c r="H55" s="2">
-        <v>1100</v>
+        <v>200</v>
       </c>
       <c r="I55" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>228</v>
+        <v>634</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>416</v>
+        <v>635</v>
       </c>
       <c r="L55" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="M55" s="11">
-        <v>0</v>
-      </c>
-      <c r="O55" s="10"/>
-      <c r="P55" s="10"/>
-      <c r="Q55" s="10"/>
+        <v>636</v>
+      </c>
+      <c r="M55" s="8">
+        <v>0</v>
+      </c>
+      <c r="O55" s="7"/>
+      <c r="P55" s="7"/>
+      <c r="Q55" s="7"/>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>54</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="D56" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>11</v>
@@ -4408,869 +4994,869 @@
         <v>500</v>
       </c>
       <c r="H56" s="2">
-        <v>1300</v>
+        <v>0</v>
       </c>
       <c r="I56" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>436</v>
+        <v>419</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="M56" s="11">
-        <v>0</v>
-      </c>
-      <c r="O56" s="10"/>
-      <c r="P56" s="10"/>
-      <c r="Q56" s="10"/>
+        <v>346</v>
+      </c>
+      <c r="M56" s="8">
+        <v>0</v>
+      </c>
+      <c r="O56" s="7"/>
+      <c r="P56" s="7"/>
+      <c r="Q56" s="7"/>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>55</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>138</v>
+        <v>76</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>167</v>
+        <v>89</v>
       </c>
       <c r="D57" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G57" s="2">
-        <v>1400</v>
+        <v>150</v>
       </c>
       <c r="H57" s="2">
-        <v>1600</v>
+        <v>7200</v>
       </c>
       <c r="I57" s="2">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>274</v>
+        <v>218</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>462</v>
+        <v>420</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="M57" s="11">
-        <v>0</v>
-      </c>
-      <c r="O57" s="10"/>
-      <c r="P57" s="10"/>
-      <c r="Q57" s="10"/>
+        <v>312</v>
+      </c>
+      <c r="M57" s="8">
+        <v>0</v>
+      </c>
+      <c r="O57" s="7"/>
+      <c r="P57" s="7"/>
+      <c r="Q57" s="7"/>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>56</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>44</v>
+        <v>522</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>56</v>
+        <v>533</v>
       </c>
       <c r="D58" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>45</v>
+        <v>512</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G58" s="2">
-        <v>100</v>
+        <v>290</v>
       </c>
       <c r="H58" s="2">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I58" s="2">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>251</v>
+        <v>616</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>439</v>
+        <v>617</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="M58" s="11">
-        <v>0</v>
-      </c>
-      <c r="O58" s="10"/>
-      <c r="P58" s="10"/>
-      <c r="Q58" s="10"/>
+        <v>618</v>
+      </c>
+      <c r="M58" s="8">
+        <v>0</v>
+      </c>
+      <c r="O58" s="7"/>
+      <c r="P58" s="7"/>
+      <c r="Q58" s="7"/>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>57</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>117</v>
+        <v>152</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>86</v>
+        <v>181</v>
       </c>
       <c r="D59" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G59" s="2">
-        <v>300</v>
+        <v>75</v>
       </c>
       <c r="H59" s="2">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I59" s="2">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>233</v>
+        <v>267</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>421</v>
       </c>
       <c r="L59" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="M59" s="11">
-        <v>0</v>
-      </c>
-      <c r="O59" s="10"/>
-      <c r="P59" s="10"/>
-      <c r="Q59" s="10"/>
+        <v>361</v>
+      </c>
+      <c r="M59" s="8">
+        <v>0</v>
+      </c>
+      <c r="O59" s="7"/>
+      <c r="P59" s="7"/>
+      <c r="Q59" s="7"/>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>58</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>72</v>
+        <v>144</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>90</v>
+        <v>173</v>
       </c>
       <c r="D60" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G60" s="2">
-        <v>300</v>
+        <v>1200</v>
       </c>
       <c r="H60" s="2">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="I60" s="2">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>397</v>
+        <v>422</v>
       </c>
       <c r="L60" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="M60" s="11">
-        <v>0</v>
-      </c>
-      <c r="O60" s="10"/>
-      <c r="P60" s="10"/>
-      <c r="Q60" s="10"/>
+        <v>326</v>
+      </c>
+      <c r="M60" s="8">
+        <v>0</v>
+      </c>
+      <c r="O60" s="7"/>
+      <c r="P60" s="7"/>
+      <c r="Q60" s="7"/>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>59</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>146</v>
+        <v>472</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>176</v>
+        <v>492</v>
       </c>
       <c r="D61" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>126</v>
+        <v>473</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G61" s="2">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="H61" s="2">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="I61" s="2">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>208</v>
+        <v>544</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>396</v>
+        <v>658</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="M61" s="11">
-        <v>0</v>
-      </c>
-      <c r="O61" s="10"/>
-      <c r="P61" s="10"/>
-      <c r="Q61" s="10"/>
+        <v>545</v>
+      </c>
+      <c r="M61" s="8">
+        <v>0</v>
+      </c>
+      <c r="O61" s="7"/>
+      <c r="P61" s="7"/>
+      <c r="Q61" s="7"/>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>60</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>84</v>
+        <v>141</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>89</v>
+        <v>170</v>
       </c>
       <c r="D62" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G62" s="2">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="H62" s="2">
-        <v>2300</v>
+        <v>0</v>
       </c>
       <c r="I62" s="2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>194</v>
+        <v>238</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>382</v>
+        <v>423</v>
       </c>
       <c r="L62" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="M62" s="11">
-        <v>0</v>
-      </c>
-      <c r="O62" s="10"/>
-      <c r="P62" s="10"/>
-      <c r="Q62" s="10"/>
+        <v>332</v>
+      </c>
+      <c r="M62" s="8">
+        <v>0</v>
+      </c>
+      <c r="O62" s="7"/>
+      <c r="P62" s="7"/>
+      <c r="Q62" s="7"/>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>61</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>119</v>
+        <v>32</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>91</v>
+        <v>50</v>
       </c>
       <c r="D63" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>118</v>
+        <v>33</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G63" s="2">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="H63" s="2">
-        <v>5700</v>
+        <v>6000</v>
       </c>
       <c r="I63" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>231</v>
+        <v>262</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="L63" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="M63" s="11">
-        <v>0</v>
-      </c>
-      <c r="O63" s="10"/>
-      <c r="P63" s="10"/>
-      <c r="Q63" s="10"/>
+        <v>356</v>
+      </c>
+      <c r="M63" s="8">
+        <v>0</v>
+      </c>
+      <c r="O63" s="7"/>
+      <c r="P63" s="7"/>
+      <c r="Q63" s="7"/>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>62</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>86</v>
+        <v>156</v>
       </c>
       <c r="D64" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>98</v>
+        <v>131</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G64" s="2">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H64" s="2">
-        <v>6800</v>
+        <v>1700</v>
       </c>
       <c r="I64" s="2">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>210</v>
+        <v>272</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>398</v>
+        <v>425</v>
       </c>
       <c r="L64" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="M64" s="11">
-        <v>0</v>
-      </c>
-      <c r="O64" s="10"/>
-      <c r="P64" s="10"/>
-      <c r="Q64" s="10"/>
+        <v>366</v>
+      </c>
+      <c r="M64" s="8">
+        <v>0</v>
+      </c>
+      <c r="O64" s="7"/>
+      <c r="P64" s="7"/>
+      <c r="Q64" s="7"/>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>63</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="D65" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G65" s="2">
-        <v>900</v>
+        <v>1800</v>
       </c>
       <c r="H65" s="2">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="I65" s="2">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>204</v>
+        <v>256</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>392</v>
+        <v>426</v>
       </c>
       <c r="L65" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="M65" s="11">
-        <v>0</v>
-      </c>
-      <c r="O65" s="10"/>
-      <c r="P65" s="10"/>
-      <c r="Q65" s="10"/>
+        <v>350</v>
+      </c>
+      <c r="M65" s="8">
+        <v>0</v>
+      </c>
+      <c r="O65" s="7"/>
+      <c r="P65" s="7"/>
+      <c r="Q65" s="7"/>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>64</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>69</v>
+        <v>518</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>92</v>
+        <v>537</v>
       </c>
       <c r="D66" s="2">
         <v>8</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>106</v>
+        <v>519</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G66" s="2">
-        <v>10</v>
+        <v>355</v>
       </c>
       <c r="H66" s="2">
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="I66" s="2">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>214</v>
+        <v>601</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>402</v>
+        <v>602</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="M66" s="11">
-        <v>0</v>
-      </c>
-      <c r="O66" s="10"/>
-      <c r="P66" s="10"/>
-      <c r="Q66" s="10"/>
+        <v>603</v>
+      </c>
+      <c r="M66" s="8">
+        <v>0</v>
+      </c>
+      <c r="O66" s="7"/>
+      <c r="P66" s="7"/>
+      <c r="Q66" s="7"/>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>65</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>87</v>
+        <v>157</v>
       </c>
       <c r="D67" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G67" s="2">
-        <v>260</v>
+        <v>1600</v>
       </c>
       <c r="H67" s="2">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="I67" s="2">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>394</v>
+        <v>427</v>
       </c>
       <c r="L67" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="M67" s="11">
-        <v>0</v>
-      </c>
-      <c r="O67" s="10"/>
-      <c r="P67" s="10"/>
-      <c r="Q67" s="10"/>
+        <v>310</v>
+      </c>
+      <c r="M67" s="8">
+        <v>0</v>
+      </c>
+      <c r="O67" s="7"/>
+      <c r="P67" s="7"/>
+      <c r="Q67" s="7"/>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>66</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="D68" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>110</v>
+        <v>47</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G68" s="2">
-        <v>105</v>
+        <v>40</v>
       </c>
       <c r="H68" s="2">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="I68" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>195</v>
+        <v>279</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>383</v>
+        <v>428</v>
       </c>
       <c r="L68" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="M68" s="11">
-        <v>0</v>
-      </c>
-      <c r="O68" s="10"/>
-      <c r="P68" s="10"/>
-      <c r="Q68" s="10"/>
+        <v>373</v>
+      </c>
+      <c r="M68" s="8">
+        <v>0</v>
+      </c>
+      <c r="O68" s="7"/>
+      <c r="P68" s="7"/>
+      <c r="Q68" s="7"/>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>67</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>88</v>
+        <v>163</v>
       </c>
       <c r="D69" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G69" s="2">
-        <v>165</v>
+        <v>1500</v>
       </c>
       <c r="H69" s="2">
-        <v>7700</v>
+        <v>0</v>
       </c>
       <c r="I69" s="2">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>220</v>
+        <v>199</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>408</v>
+        <v>429</v>
       </c>
       <c r="L69" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="M69" s="11">
-        <v>0</v>
-      </c>
-      <c r="O69" s="10"/>
-      <c r="P69" s="10"/>
-      <c r="Q69" s="10"/>
+        <v>293</v>
+      </c>
+      <c r="M69" s="8">
+        <v>0</v>
+      </c>
+      <c r="O69" s="7"/>
+      <c r="P69" s="7"/>
+      <c r="Q69" s="7"/>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>68</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>63</v>
+        <v>136</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>88</v>
+        <v>166</v>
       </c>
       <c r="D70" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G70" s="2">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="H70" s="2">
-        <v>8000</v>
+        <v>1100</v>
       </c>
       <c r="I70" s="2">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>197</v>
+        <v>228</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>385</v>
+        <v>430</v>
       </c>
       <c r="L70" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="M70" s="11">
-        <v>0</v>
-      </c>
-      <c r="O70" s="10"/>
-      <c r="P70" s="10"/>
-      <c r="Q70" s="10"/>
+        <v>322</v>
+      </c>
+      <c r="M70" s="8">
+        <v>0</v>
+      </c>
+      <c r="O70" s="7"/>
+      <c r="P70" s="7"/>
+      <c r="Q70" s="7"/>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
         <v>69</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>66</v>
+        <v>128</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>87</v>
+        <v>160</v>
       </c>
       <c r="D71" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G71" s="2">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="H71" s="2">
-        <v>6400</v>
+        <v>1300</v>
       </c>
       <c r="I71" s="2">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>205</v>
+        <v>248</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>393</v>
+        <v>431</v>
       </c>
       <c r="L71" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="M71" s="11">
-        <v>0</v>
-      </c>
-      <c r="O71" s="10"/>
-      <c r="P71" s="10"/>
-      <c r="Q71" s="10"/>
+        <v>342</v>
+      </c>
+      <c r="M71" s="8">
+        <v>0</v>
+      </c>
+      <c r="O71" s="7"/>
+      <c r="P71" s="7"/>
+      <c r="Q71" s="7"/>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
         <v>70</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>68</v>
+        <v>486</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>89</v>
+        <v>499</v>
       </c>
       <c r="D72" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>105</v>
+        <v>487</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G72" s="2">
-        <v>250</v>
+        <v>30</v>
       </c>
       <c r="H72" s="2">
-        <v>2300</v>
+        <v>1800</v>
       </c>
       <c r="I72" s="2">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>211</v>
+        <v>562</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>399</v>
+        <v>563</v>
       </c>
       <c r="L72" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="M72" s="11">
-        <v>0</v>
-      </c>
-      <c r="O72" s="10"/>
-      <c r="P72" s="10"/>
-      <c r="Q72" s="10"/>
+        <v>564</v>
+      </c>
+      <c r="M72" s="8">
+        <v>0</v>
+      </c>
+      <c r="O72" s="7"/>
+      <c r="P72" s="7"/>
+      <c r="Q72" s="7"/>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
         <v>71</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="D73" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G73" s="2">
-        <v>1165</v>
+        <v>1400</v>
       </c>
       <c r="H73" s="2">
-        <v>180</v>
+        <v>1600</v>
       </c>
       <c r="I73" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>196</v>
+        <v>274</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>384</v>
+        <v>432</v>
       </c>
       <c r="L73" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="M73" s="11">
-        <v>0</v>
-      </c>
-      <c r="O73" s="10"/>
-      <c r="P73" s="10"/>
-      <c r="Q73" s="10"/>
+        <v>368</v>
+      </c>
+      <c r="M73" s="8">
+        <v>0</v>
+      </c>
+      <c r="O73" s="7"/>
+      <c r="P73" s="7"/>
+      <c r="Q73" s="7"/>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
         <v>72</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>139</v>
+        <v>44</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>168</v>
+        <v>56</v>
       </c>
       <c r="D74" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>122</v>
+        <v>45</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G74" s="2">
-        <v>1265</v>
+        <v>100</v>
       </c>
       <c r="H74" s="2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I74" s="2">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>219</v>
+        <v>251</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>407</v>
+        <v>433</v>
       </c>
       <c r="L74" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="M74" s="11">
-        <v>0</v>
-      </c>
-      <c r="O74" s="10"/>
-      <c r="P74" s="10"/>
-      <c r="Q74" s="10"/>
+        <v>345</v>
+      </c>
+      <c r="M74" s="8">
+        <v>0</v>
+      </c>
+      <c r="O74" s="7"/>
+      <c r="P74" s="7"/>
+      <c r="Q74" s="7"/>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
         <v>73</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>143</v>
+        <v>117</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>172</v>
+        <v>86</v>
       </c>
       <c r="D75" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G75" s="2">
-        <v>1740</v>
+        <v>300</v>
       </c>
       <c r="H75" s="2">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I75" s="2">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>400</v>
+        <v>434</v>
       </c>
       <c r="L75" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="M75" s="11">
-        <v>0</v>
-      </c>
-      <c r="O75" s="10"/>
-      <c r="P75" s="10"/>
-      <c r="Q75" s="10"/>
+        <v>327</v>
+      </c>
+      <c r="M75" s="8">
+        <v>0</v>
+      </c>
+      <c r="O75" s="7"/>
+      <c r="P75" s="7"/>
+      <c r="Q75" s="7"/>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
         <v>74</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>90</v>
@@ -5285,1253 +5871,2699 @@
         <v>11</v>
       </c>
       <c r="G76" s="2">
-        <v>95</v>
+        <v>300</v>
       </c>
       <c r="H76" s="2">
-        <v>1900</v>
+        <v>500</v>
       </c>
       <c r="I76" s="2">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>413</v>
+        <v>435</v>
       </c>
       <c r="L76" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="M76" s="11">
-        <v>0</v>
-      </c>
-      <c r="O76" s="10"/>
-      <c r="P76" s="10"/>
-      <c r="Q76" s="10"/>
+        <v>303</v>
+      </c>
+      <c r="M76" s="8">
+        <v>0</v>
+      </c>
+      <c r="O76" s="7"/>
+      <c r="P76" s="7"/>
+      <c r="Q76" s="7"/>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
         <v>75</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>74</v>
+        <v>146</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>89</v>
+        <v>176</v>
       </c>
       <c r="D77" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G77" s="2">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="H77" s="2">
-        <v>4300</v>
+        <v>0</v>
       </c>
       <c r="I77" s="2">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>389</v>
+        <v>436</v>
       </c>
       <c r="L77" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="M77" s="11">
-        <v>0</v>
-      </c>
-      <c r="O77" s="10"/>
-      <c r="P77" s="10"/>
-      <c r="Q77" s="10"/>
+        <v>302</v>
+      </c>
+      <c r="M77" s="8">
+        <v>0</v>
+      </c>
+      <c r="O77" s="7"/>
+      <c r="P77" s="7"/>
+      <c r="Q77" s="7"/>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
         <v>76</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>80</v>
+        <v>513</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>92</v>
+        <v>534</v>
       </c>
       <c r="D78" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>113</v>
+        <v>514</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G78" s="2">
-        <v>65</v>
+        <v>327</v>
       </c>
       <c r="H78" s="2">
-        <v>7400</v>
+        <v>2000</v>
       </c>
       <c r="I78" s="2">
-        <v>11</v>
+        <v>99</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>207</v>
+        <v>592</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>395</v>
+        <v>593</v>
       </c>
       <c r="L78" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="M78" s="11">
-        <v>0</v>
-      </c>
-      <c r="O78" s="10"/>
-      <c r="P78" s="10"/>
-      <c r="Q78" s="10"/>
+        <v>594</v>
+      </c>
+      <c r="M78" s="8">
+        <v>0</v>
+      </c>
+      <c r="O78" s="7"/>
+      <c r="P78" s="7"/>
+      <c r="Q78" s="7"/>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
         <v>77</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>44</v>
+        <v>474</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>156</v>
+        <v>493</v>
       </c>
       <c r="D79" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>124</v>
+        <v>475</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G79" s="2">
-        <v>525</v>
+        <v>300</v>
       </c>
       <c r="H79" s="2">
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="I79" s="2">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>217</v>
+        <v>546</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>405</v>
+        <v>547</v>
       </c>
       <c r="L79" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="M79" s="11">
-        <v>0</v>
-      </c>
-      <c r="O79" s="10"/>
-      <c r="P79" s="10"/>
-      <c r="Q79" s="10"/>
+        <v>548</v>
+      </c>
+      <c r="M79" s="8">
+        <v>0</v>
+      </c>
+      <c r="O79" s="7"/>
+      <c r="P79" s="7"/>
+      <c r="Q79" s="7"/>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
         <v>78</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D80" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G80" s="2">
-        <v>255</v>
+        <v>75</v>
       </c>
       <c r="H80" s="2">
-        <v>2100</v>
+        <v>2300</v>
       </c>
       <c r="I80" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>223</v>
+        <v>194</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>411</v>
+        <v>437</v>
       </c>
       <c r="L80" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="M80" s="11">
-        <v>0</v>
-      </c>
-      <c r="O80" s="10"/>
-      <c r="P80" s="10"/>
-      <c r="Q80" s="10"/>
+        <v>288</v>
+      </c>
+      <c r="M80" s="8">
+        <v>0</v>
+      </c>
+      <c r="O80" s="7"/>
+      <c r="P80" s="7"/>
+      <c r="Q80" s="7"/>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
         <v>79</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>158</v>
+        <v>91</v>
       </c>
       <c r="D81" s="2">
         <v>2</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G81" s="2">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="H81" s="2">
-        <v>0</v>
+        <v>5700</v>
       </c>
       <c r="I81" s="2">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>198</v>
+        <v>231</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>386</v>
+        <v>438</v>
       </c>
       <c r="L81" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="M81" s="11">
-        <v>0</v>
-      </c>
-      <c r="O81" s="10"/>
-      <c r="P81" s="10"/>
-      <c r="Q81" s="10"/>
+        <v>325</v>
+      </c>
+      <c r="M81" s="8">
+        <v>0</v>
+      </c>
+      <c r="O81" s="7"/>
+      <c r="P81" s="7"/>
+      <c r="Q81" s="7"/>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
         <v>80</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D82" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G82" s="2">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="H82" s="2">
-        <v>7200</v>
+        <v>6800</v>
       </c>
       <c r="I82" s="2">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>227</v>
+        <v>210</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>415</v>
+        <v>439</v>
       </c>
       <c r="L82" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="M82" s="11">
-        <v>0</v>
-      </c>
-      <c r="O82" s="10"/>
-      <c r="P82" s="10"/>
-      <c r="Q82" s="10"/>
+        <v>304</v>
+      </c>
+      <c r="M82" s="8">
+        <v>0</v>
+      </c>
+      <c r="O82" s="7"/>
+      <c r="P82" s="7"/>
+      <c r="Q82" s="7"/>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
         <v>81</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>71</v>
+        <v>138</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>89</v>
+        <v>167</v>
       </c>
       <c r="D83" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G83" s="2">
-        <v>125</v>
+        <v>900</v>
       </c>
       <c r="H83" s="2">
-        <v>2700</v>
+        <v>700</v>
       </c>
       <c r="I83" s="2">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>401</v>
+        <v>440</v>
       </c>
       <c r="L83" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="M83" s="11">
-        <v>0</v>
-      </c>
-      <c r="O83" s="10"/>
-      <c r="P83" s="10"/>
-      <c r="Q83" s="10"/>
+        <v>298</v>
+      </c>
+      <c r="M83" s="8">
+        <v>0</v>
+      </c>
+      <c r="O83" s="7"/>
+      <c r="P83" s="7"/>
+      <c r="Q83" s="7"/>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
         <v>82</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D84" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G84" s="2">
-        <v>230</v>
+        <v>10</v>
       </c>
       <c r="H84" s="2">
-        <v>7400</v>
+        <v>2100</v>
       </c>
       <c r="I84" s="2">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K84" s="3" t="s">
-        <v>412</v>
+        <v>441</v>
       </c>
       <c r="L84" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="M84" s="11">
-        <v>0</v>
-      </c>
-      <c r="O84" s="10"/>
-      <c r="P84" s="10"/>
-      <c r="Q84" s="10"/>
+        <v>308</v>
+      </c>
+      <c r="M84" s="8">
+        <v>0</v>
+      </c>
+      <c r="O84" s="7"/>
+      <c r="P84" s="7"/>
+      <c r="Q84" s="7"/>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
         <v>83</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D85" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G85" s="2">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="H85" s="2">
-        <v>1500</v>
+        <v>6000</v>
       </c>
       <c r="I85" s="2">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>414</v>
+        <v>442</v>
       </c>
       <c r="L85" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="M85" s="11">
-        <v>0</v>
-      </c>
-      <c r="O85" s="10"/>
-      <c r="P85" s="10"/>
-      <c r="Q85" s="10"/>
+        <v>300</v>
+      </c>
+      <c r="M85" s="8">
+        <v>0</v>
+      </c>
+      <c r="O85" s="7"/>
+      <c r="P85" s="7"/>
+      <c r="Q85" s="7"/>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
         <v>84</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>156</v>
+        <v>94</v>
       </c>
       <c r="D86" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G86" s="2">
-        <v>845</v>
+        <v>105</v>
       </c>
       <c r="H86" s="2">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="I86" s="2">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>221</v>
+        <v>195</v>
       </c>
       <c r="K86" s="3" t="s">
-        <v>409</v>
+        <v>443</v>
       </c>
       <c r="L86" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="M86" s="11">
-        <v>0</v>
-      </c>
-      <c r="O86" s="10"/>
-      <c r="P86" s="10"/>
-      <c r="Q86" s="10"/>
+        <v>289</v>
+      </c>
+      <c r="M86" s="8">
+        <v>0</v>
+      </c>
+      <c r="O86" s="7"/>
+      <c r="P86" s="7"/>
+      <c r="Q86" s="7"/>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
         <v>85</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D87" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G87" s="2">
-        <v>285</v>
+        <v>165</v>
       </c>
       <c r="H87" s="2">
-        <v>4500</v>
+        <v>7700</v>
       </c>
       <c r="I87" s="2">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="K87" s="3" t="s">
-        <v>388</v>
+        <v>444</v>
       </c>
       <c r="L87" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="M87" s="11">
-        <v>0</v>
-      </c>
-      <c r="O87" s="10"/>
-      <c r="P87" s="10"/>
-      <c r="Q87" s="10"/>
+        <v>314</v>
+      </c>
+      <c r="M87" s="8">
+        <v>0</v>
+      </c>
+      <c r="O87" s="7"/>
+      <c r="P87" s="7"/>
+      <c r="Q87" s="7"/>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
         <v>86</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>75</v>
+        <v>518</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>94</v>
+        <v>531</v>
       </c>
       <c r="D88" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>110</v>
+        <v>527</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G88" s="2">
-        <v>130</v>
+        <v>250</v>
       </c>
       <c r="H88" s="2">
-        <v>7100</v>
+        <v>1000</v>
       </c>
       <c r="I88" s="2">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>230</v>
+        <v>655</v>
       </c>
       <c r="K88" s="3" t="s">
-        <v>418</v>
+        <v>656</v>
       </c>
       <c r="L88" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="M88" s="11">
-        <v>0</v>
-      </c>
-      <c r="O88" s="10"/>
-      <c r="P88" s="10"/>
-      <c r="Q88" s="10"/>
+        <v>657</v>
+      </c>
+      <c r="M88" s="8">
+        <v>0</v>
+      </c>
+      <c r="O88" s="7"/>
+      <c r="P88" s="7"/>
+      <c r="Q88" s="7"/>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
         <v>87</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>133</v>
+        <v>509</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>164</v>
+        <v>529</v>
       </c>
       <c r="D89" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>122</v>
+        <v>510</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G89" s="2">
-        <v>375</v>
+        <v>339</v>
       </c>
       <c r="H89" s="2">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I89" s="2">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>203</v>
+        <v>613</v>
       </c>
       <c r="K89" s="3" t="s">
-        <v>391</v>
+        <v>614</v>
       </c>
       <c r="L89" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="M89" s="11">
-        <v>0</v>
-      </c>
-      <c r="O89" s="10"/>
-      <c r="P89" s="10"/>
-      <c r="Q89" s="10"/>
+        <v>615</v>
+      </c>
+      <c r="M89" s="8">
+        <v>0</v>
+      </c>
+      <c r="O89" s="7"/>
+      <c r="P89" s="7"/>
+      <c r="Q89" s="7"/>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
         <v>88</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>149</v>
+        <v>521</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>178</v>
+        <v>537</v>
       </c>
       <c r="D90" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>142</v>
+        <v>505</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G90" s="2">
-        <v>255</v>
+        <v>123</v>
       </c>
       <c r="H90" s="2">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="I90" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>222</v>
+        <v>607</v>
       </c>
       <c r="K90" s="3" t="s">
-        <v>410</v>
+        <v>608</v>
       </c>
       <c r="L90" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="M90" s="11">
-        <v>0</v>
-      </c>
-      <c r="O90" s="10"/>
-      <c r="P90" s="10"/>
-      <c r="Q90" s="10"/>
+        <v>609</v>
+      </c>
+      <c r="M90" s="8">
+        <v>0</v>
+      </c>
+      <c r="O90" s="7"/>
+      <c r="P90" s="7"/>
+      <c r="Q90" s="7"/>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
         <v>89</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>136</v>
+        <v>522</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>166</v>
+        <v>535</v>
       </c>
       <c r="D91" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>130</v>
+        <v>507</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G91" s="2">
-        <v>1790</v>
+        <v>111</v>
       </c>
       <c r="H91" s="2">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="I91" s="2">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>229</v>
+        <v>619</v>
       </c>
       <c r="K91" s="3" t="s">
-        <v>417</v>
+        <v>620</v>
       </c>
       <c r="L91" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="M91" s="11">
-        <v>0</v>
-      </c>
-      <c r="O91" s="10"/>
-      <c r="P91" s="10"/>
-      <c r="Q91" s="10"/>
+        <v>621</v>
+      </c>
+      <c r="M91" s="8">
+        <v>0</v>
+      </c>
+      <c r="O91" s="7"/>
+      <c r="P91" s="7"/>
+      <c r="Q91" s="7"/>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
         <v>90</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D92" s="2">
+        <v>6</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G92" s="2">
+        <v>70</v>
+      </c>
+      <c r="H92" s="2">
+        <v>8000</v>
+      </c>
+      <c r="I92" s="2">
         <v>4</v>
       </c>
-      <c r="E92" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G92" s="2">
-        <v>230</v>
-      </c>
-      <c r="H92" s="2">
-        <v>3000</v>
-      </c>
-      <c r="I92" s="2">
-        <v>12</v>
-      </c>
       <c r="J92" s="3" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="K92" s="3" t="s">
-        <v>381</v>
+        <v>445</v>
       </c>
       <c r="L92" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="M92" s="11">
-        <v>0</v>
-      </c>
-      <c r="O92" s="10"/>
-      <c r="P92" s="10"/>
-      <c r="Q92" s="10"/>
+        <v>291</v>
+      </c>
+      <c r="M92" s="8">
+        <v>0</v>
+      </c>
+      <c r="O92" s="7"/>
+      <c r="P92" s="7"/>
+      <c r="Q92" s="7"/>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
         <v>91</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>134</v>
+        <v>509</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>165</v>
+        <v>533</v>
       </c>
       <c r="D93" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>135</v>
+        <v>510</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G93" s="2">
-        <v>470</v>
+        <v>30</v>
       </c>
       <c r="H93" s="2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I93" s="2">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>191</v>
+        <v>586</v>
       </c>
       <c r="K93" s="3" t="s">
-        <v>379</v>
+        <v>587</v>
       </c>
       <c r="L93" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="M93" s="11">
-        <v>0</v>
-      </c>
-      <c r="O93" s="10"/>
-      <c r="P93" s="10"/>
-      <c r="Q93" s="10"/>
+        <v>588</v>
+      </c>
+      <c r="M93" s="8">
+        <v>0</v>
+      </c>
+      <c r="O93" s="7"/>
+      <c r="P93" s="7"/>
+      <c r="Q93" s="7"/>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
         <v>92</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D94" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G94" s="2">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="H94" s="2">
-        <v>1900</v>
+        <v>6400</v>
       </c>
       <c r="I94" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="K94" s="3" t="s">
-        <v>403</v>
+        <v>446</v>
       </c>
       <c r="L94" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="M94" s="11">
-        <v>0</v>
-      </c>
-      <c r="O94" s="10"/>
-      <c r="P94" s="10"/>
-      <c r="Q94" s="10"/>
+        <v>299</v>
+      </c>
+      <c r="M94" s="8">
+        <v>0</v>
+      </c>
+      <c r="O94" s="7"/>
+      <c r="P94" s="7"/>
+      <c r="Q94" s="7"/>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
         <v>93</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>153</v>
+        <v>68</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>182</v>
+        <v>89</v>
       </c>
       <c r="D95" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G95" s="2">
-        <v>1980</v>
+        <v>250</v>
       </c>
       <c r="H95" s="2">
-        <v>1400</v>
+        <v>2300</v>
       </c>
       <c r="I95" s="2">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="K95" s="3" t="s">
-        <v>378</v>
+        <v>447</v>
       </c>
       <c r="L95" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="M95" s="11">
-        <v>0</v>
-      </c>
-      <c r="O95" s="10"/>
-      <c r="P95" s="10"/>
-      <c r="Q95" s="10"/>
+        <v>305</v>
+      </c>
+      <c r="M95" s="8">
+        <v>0</v>
+      </c>
+      <c r="O95" s="7"/>
+      <c r="P95" s="7"/>
+      <c r="Q95" s="7"/>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
         <v>94</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D96" s="2">
         <v>3</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G96" s="2">
-        <v>400</v>
+        <v>1165</v>
       </c>
       <c r="H96" s="2">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="I96" s="2">
         <v>2</v>
       </c>
       <c r="J96" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="M96" s="8">
+        <v>0</v>
+      </c>
+      <c r="O96" s="7"/>
+      <c r="P96" s="7"/>
+      <c r="Q96" s="7"/>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A97" s="2">
+        <v>95</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D97" s="2">
+        <v>8</v>
+      </c>
+      <c r="E97" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G97" s="2">
+        <v>1265</v>
+      </c>
+      <c r="H97" s="2">
+        <v>0</v>
+      </c>
+      <c r="I97" s="2">
+        <v>40</v>
+      </c>
+      <c r="J97" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="K97" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="L97" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="M97" s="8">
+        <v>0</v>
+      </c>
+      <c r="O97" s="7"/>
+      <c r="P97" s="7"/>
+      <c r="Q97" s="7"/>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A98" s="2">
+        <v>96</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="D98" s="2">
+        <v>6</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G98" s="2">
+        <v>1740</v>
+      </c>
+      <c r="H98" s="2">
+        <v>0</v>
+      </c>
+      <c r="I98" s="2">
+        <v>21</v>
+      </c>
+      <c r="J98" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="K98" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="L98" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="M98" s="8">
+        <v>0</v>
+      </c>
+      <c r="O98" s="7"/>
+      <c r="P98" s="7"/>
+      <c r="Q98" s="7"/>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A99" s="2">
+        <v>97</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="D99" s="2">
+        <v>6</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G99" s="2">
+        <v>25</v>
+      </c>
+      <c r="H99" s="2">
+        <v>2500</v>
+      </c>
+      <c r="I99" s="2">
+        <v>90</v>
+      </c>
+      <c r="J99" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="K99" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="L99" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="M99" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A100" s="2">
+        <v>98</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="D100" s="2">
+        <v>4</v>
+      </c>
+      <c r="E100" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G100" s="2">
+        <v>325</v>
+      </c>
+      <c r="H100" s="2">
+        <v>100</v>
+      </c>
+      <c r="I100" s="2">
+        <v>79</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="M100" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A101" s="2">
+        <v>99</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="D101" s="2">
+        <v>1</v>
+      </c>
+      <c r="E101" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G101" s="2">
+        <v>386</v>
+      </c>
+      <c r="H101" s="2">
+        <v>200</v>
+      </c>
+      <c r="I101" s="2">
+        <v>65</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="M101" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A102" s="2">
+        <v>100</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="D102" s="2">
+        <v>3</v>
+      </c>
+      <c r="E102" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G102" s="2">
+        <v>369</v>
+      </c>
+      <c r="H102" s="2">
+        <v>350</v>
+      </c>
+      <c r="I102" s="2">
+        <v>89</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="L102" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="M102" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A103" s="2">
+        <v>101</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="D103" s="2">
+        <v>1</v>
+      </c>
+      <c r="E103" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G103" s="2">
+        <v>462</v>
+      </c>
+      <c r="H103" s="2">
+        <v>0</v>
+      </c>
+      <c r="I103" s="2">
+        <v>30</v>
+      </c>
+      <c r="J103" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="K103" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="L103" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="M103" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A104" s="2">
+        <v>102</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="D104" s="2">
+        <v>3</v>
+      </c>
+      <c r="E104" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G104" s="2">
+        <v>291</v>
+      </c>
+      <c r="H104" s="2">
+        <v>100</v>
+      </c>
+      <c r="I104" s="2">
+        <v>74</v>
+      </c>
+      <c r="J104" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="K104" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="L104" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="M104" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A105" s="2">
+        <v>103</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D105" s="2">
+        <v>4</v>
+      </c>
+      <c r="E105" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G105" s="2">
+        <v>95</v>
+      </c>
+      <c r="H105" s="2">
+        <v>1900</v>
+      </c>
+      <c r="I105" s="2">
+        <v>31</v>
+      </c>
+      <c r="J105" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="K105" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="L105" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="M105" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A106" s="2">
+        <v>104</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D106" s="2">
+        <v>3</v>
+      </c>
+      <c r="E106" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G106" s="2">
+        <v>280</v>
+      </c>
+      <c r="H106" s="2">
+        <v>4300</v>
+      </c>
+      <c r="I106" s="2">
+        <v>11</v>
+      </c>
+      <c r="J106" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="K106" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="L106" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="M106" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A107" s="2">
+        <v>105</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="D107" s="2">
+        <v>3</v>
+      </c>
+      <c r="E107" s="4" t="s">
+        <v>517</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G107" s="2">
+        <v>243</v>
+      </c>
+      <c r="H107" s="2">
+        <v>2000</v>
+      </c>
+      <c r="I107" s="2">
+        <v>98</v>
+      </c>
+      <c r="J107" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="K107" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="L107" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="M107" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A108" s="2">
+        <v>106</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D108" s="2">
+        <v>8</v>
+      </c>
+      <c r="E108" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G108" s="2">
+        <v>65</v>
+      </c>
+      <c r="H108" s="2">
+        <v>7400</v>
+      </c>
+      <c r="I108" s="2">
+        <v>11</v>
+      </c>
+      <c r="J108" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="K108" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="L108" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="M108" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A109" s="2">
+        <v>107</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="D109" s="2">
+        <v>1</v>
+      </c>
+      <c r="E109" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G109" s="2">
+        <v>246</v>
+      </c>
+      <c r="H109" s="2">
+        <v>350</v>
+      </c>
+      <c r="I109" s="2">
+        <v>32</v>
+      </c>
+      <c r="J109" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="K109" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="L109" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="M109" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A110" s="2">
+        <v>108</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="D110" s="2">
+        <v>7</v>
+      </c>
+      <c r="E110" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G110" s="2">
+        <v>525</v>
+      </c>
+      <c r="H110" s="2">
+        <v>0</v>
+      </c>
+      <c r="I110" s="2">
+        <v>4</v>
+      </c>
+      <c r="J110" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="K110" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="L110" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="M110" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A111" s="2">
+        <v>109</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D111" s="2">
+        <v>7</v>
+      </c>
+      <c r="E111" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G111" s="2">
+        <v>255</v>
+      </c>
+      <c r="H111" s="2">
+        <v>2100</v>
+      </c>
+      <c r="I111" s="2">
+        <v>46</v>
+      </c>
+      <c r="J111" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="K111" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="L111" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="M111" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A112" s="2">
+        <v>110</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>533</v>
+      </c>
+      <c r="D112" s="2">
+        <v>9</v>
+      </c>
+      <c r="E112" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G112" s="2">
+        <v>143</v>
+      </c>
+      <c r="H112" s="2">
+        <v>2000</v>
+      </c>
+      <c r="I112" s="2">
+        <v>37</v>
+      </c>
+      <c r="J112" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="K112" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="L112" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="M112" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A113" s="2">
+        <v>111</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="D113" s="2">
+        <v>2</v>
+      </c>
+      <c r="E113" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G113" s="2">
+        <v>120</v>
+      </c>
+      <c r="H113" s="2">
+        <v>0</v>
+      </c>
+      <c r="I113" s="2">
+        <v>22</v>
+      </c>
+      <c r="J113" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="K113" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="L113" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="M113" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A114" s="2">
+        <v>112</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D114" s="2">
+        <v>1</v>
+      </c>
+      <c r="E114" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G114" s="2">
+        <v>95</v>
+      </c>
+      <c r="H114" s="2">
+        <v>7200</v>
+      </c>
+      <c r="I114" s="2">
+        <v>12</v>
+      </c>
+      <c r="J114" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="K114" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="L114" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="M114" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A115" s="2">
+        <v>113</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D115" s="2">
+        <v>3</v>
+      </c>
+      <c r="E115" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G115" s="2">
+        <v>125</v>
+      </c>
+      <c r="H115" s="2">
+        <v>2700</v>
+      </c>
+      <c r="I115" s="2">
+        <v>17</v>
+      </c>
+      <c r="J115" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="K115" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="L115" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="M115" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A116" s="2">
+        <v>114</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="D116" s="2">
+        <v>2</v>
+      </c>
+      <c r="E116" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G116" s="2">
+        <v>362</v>
+      </c>
+      <c r="H116" s="2">
+        <v>3000</v>
+      </c>
+      <c r="I116" s="2">
+        <v>49</v>
+      </c>
+      <c r="J116" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="K116" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="L116" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="M116" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A117" s="2">
+        <v>115</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="D117" s="2">
+        <v>1</v>
+      </c>
+      <c r="E117" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G117" s="2">
+        <v>134</v>
+      </c>
+      <c r="H117" s="2">
+        <v>2000</v>
+      </c>
+      <c r="I117" s="2">
+        <v>45</v>
+      </c>
+      <c r="J117" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="K117" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="L117" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="M117" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A118" s="2">
+        <v>116</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D118" s="2">
+        <v>1</v>
+      </c>
+      <c r="E118" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G118" s="2">
+        <v>230</v>
+      </c>
+      <c r="H118" s="2">
+        <v>7400</v>
+      </c>
+      <c r="I118" s="2">
+        <v>12</v>
+      </c>
+      <c r="J118" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="K118" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="L118" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="M118" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A119" s="2">
+        <v>117</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D119" s="2">
+        <v>5</v>
+      </c>
+      <c r="E119" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G119" s="2">
+        <v>230</v>
+      </c>
+      <c r="H119" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I119" s="2">
+        <v>24</v>
+      </c>
+      <c r="J119" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="K119" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="L119" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="M119" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A120" s="2">
+        <v>118</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="D120" s="2">
+        <v>7</v>
+      </c>
+      <c r="E120" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G120" s="2">
+        <v>845</v>
+      </c>
+      <c r="H120" s="2">
+        <v>0</v>
+      </c>
+      <c r="I120" s="2">
+        <v>21</v>
+      </c>
+      <c r="J120" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="K120" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="L120" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="M120" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A121" s="2">
+        <v>119</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="D121" s="2">
+        <v>4</v>
+      </c>
+      <c r="E121" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G121" s="2">
+        <v>339</v>
+      </c>
+      <c r="H121" s="2">
+        <v>500</v>
+      </c>
+      <c r="I121" s="2">
+        <v>62</v>
+      </c>
+      <c r="J121" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="K121" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="L121" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="M121" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A122" s="2">
+        <v>120</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="D122" s="2">
+        <v>8</v>
+      </c>
+      <c r="E122" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G122" s="2">
+        <v>275</v>
+      </c>
+      <c r="H122" s="2">
+        <v>500</v>
+      </c>
+      <c r="I122" s="2">
+        <v>30</v>
+      </c>
+      <c r="J122" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="K122" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="L122" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="M122" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A123" s="2">
+        <v>121</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="D123" s="2">
+        <v>2</v>
+      </c>
+      <c r="E123" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G123" s="2">
+        <v>345</v>
+      </c>
+      <c r="H123" s="2">
+        <v>350</v>
+      </c>
+      <c r="I123" s="2">
+        <v>82</v>
+      </c>
+      <c r="J123" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="K123" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="L123" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="M123" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A124" s="2">
+        <v>122</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C124" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D124" s="2">
+        <v>2</v>
+      </c>
+      <c r="E124" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G124" s="2">
+        <v>285</v>
+      </c>
+      <c r="H124" s="2">
+        <v>4500</v>
+      </c>
+      <c r="I124" s="2">
+        <v>40</v>
+      </c>
+      <c r="J124" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="K124" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="L124" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="M124" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A125" s="2">
+        <v>123</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D125" s="2">
+        <v>9</v>
+      </c>
+      <c r="E125" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G125" s="2">
+        <v>130</v>
+      </c>
+      <c r="H125" s="2">
+        <v>7100</v>
+      </c>
+      <c r="I125" s="2">
+        <v>20</v>
+      </c>
+      <c r="J125" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="K125" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="L125" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="M125" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A126" s="2">
+        <v>124</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="D126" s="2">
+        <v>4</v>
+      </c>
+      <c r="E126" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G126" s="2">
+        <v>375</v>
+      </c>
+      <c r="H126" s="2">
+        <v>2000</v>
+      </c>
+      <c r="I126" s="2">
+        <v>49</v>
+      </c>
+      <c r="J126" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="K126" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="L126" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="M126" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A127" s="2">
+        <v>125</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="D127" s="2">
+        <v>3</v>
+      </c>
+      <c r="E127" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="F127" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G127" s="2">
+        <v>181</v>
+      </c>
+      <c r="H127" s="2">
+        <v>500</v>
+      </c>
+      <c r="I127" s="2">
+        <v>18</v>
+      </c>
+      <c r="J127" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="K127" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="L127" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="M127" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A128" s="2">
+        <v>126</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C128" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D128" s="2">
+        <v>3</v>
+      </c>
+      <c r="E128" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="F128" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G128" s="2">
+        <v>255</v>
+      </c>
+      <c r="H128" s="2">
+        <v>230</v>
+      </c>
+      <c r="I128" s="2">
+        <v>39</v>
+      </c>
+      <c r="J128" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="K128" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="L128" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="M128" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A129" s="2">
+        <v>127</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D129" s="2">
+        <v>1</v>
+      </c>
+      <c r="E129" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="F129" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G129" s="2">
+        <v>1790</v>
+      </c>
+      <c r="H129" s="2">
+        <v>300</v>
+      </c>
+      <c r="I129" s="2">
+        <v>16</v>
+      </c>
+      <c r="J129" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="K129" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="L129" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="M129" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A130" s="2">
+        <v>128</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="C130" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="D130" s="2">
+        <v>7</v>
+      </c>
+      <c r="E130" s="4" t="s">
+        <v>517</v>
+      </c>
+      <c r="F130" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G130" s="2">
+        <v>447</v>
+      </c>
+      <c r="H130" s="2">
+        <v>500</v>
+      </c>
+      <c r="I130" s="2">
+        <v>56</v>
+      </c>
+      <c r="J130" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="K130" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="L130" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="M130" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A131" s="2">
+        <v>129</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D131" s="2">
+        <v>4</v>
+      </c>
+      <c r="E131" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G131" s="2">
+        <v>230</v>
+      </c>
+      <c r="H131" s="2">
+        <v>3000</v>
+      </c>
+      <c r="I131" s="2">
+        <v>12</v>
+      </c>
+      <c r="J131" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="K131" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="L131" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="M131" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A132" s="2">
+        <v>130</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="D132" s="2">
+        <v>8</v>
+      </c>
+      <c r="E132" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G132" s="2">
+        <v>470</v>
+      </c>
+      <c r="H132" s="2">
+        <v>0</v>
+      </c>
+      <c r="I132" s="2">
+        <v>13</v>
+      </c>
+      <c r="J132" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="K132" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="L132" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="M132" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A133" s="2">
+        <v>131</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D133" s="2">
+        <v>3</v>
+      </c>
+      <c r="E133" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G133" s="2">
+        <v>95</v>
+      </c>
+      <c r="H133" s="2">
+        <v>1900</v>
+      </c>
+      <c r="I133" s="2">
+        <v>48</v>
+      </c>
+      <c r="J133" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="K133" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="L133" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="M133" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A134" s="2">
+        <v>132</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="D134" s="2">
+        <v>7</v>
+      </c>
+      <c r="E134" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G134" s="2">
+        <v>1980</v>
+      </c>
+      <c r="H134" s="2">
+        <v>1400</v>
+      </c>
+      <c r="I134" s="2">
+        <v>32</v>
+      </c>
+      <c r="J134" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K134" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="L134" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="M134" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A135" s="2">
+        <v>133</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D135" s="2">
+        <v>3</v>
+      </c>
+      <c r="E135" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F135" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G135" s="2">
+        <v>400</v>
+      </c>
+      <c r="H135" s="2">
+        <v>0</v>
+      </c>
+      <c r="I135" s="2">
+        <v>2</v>
+      </c>
+      <c r="J135" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="L96" s="3" t="s">
+      <c r="K135" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="L135" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="M96" s="11">
-        <v>0</v>
-      </c>
-      <c r="O96" s="10"/>
-      <c r="P96" s="10"/>
-      <c r="Q96" s="10"/>
-    </row>
-    <row r="97" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J97" s="9"/>
-      <c r="K97" s="9"/>
-      <c r="L97" s="9"/>
-    </row>
-    <row r="98" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J98" s="9"/>
-      <c r="K98" s="9"/>
-      <c r="L98" s="9"/>
-    </row>
-    <row r="99" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J99" s="9"/>
-      <c r="K99" s="9"/>
-      <c r="L99" s="9"/>
-    </row>
-    <row r="100" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J100" s="9"/>
-      <c r="K100" s="9"/>
-      <c r="L100" s="9"/>
-    </row>
-    <row r="101" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J101" s="9"/>
-      <c r="K101" s="9"/>
-      <c r="L101" s="9"/>
-    </row>
-    <row r="102" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J102" s="9"/>
-      <c r="K102" s="9"/>
-      <c r="L102" s="9"/>
-    </row>
-    <row r="103" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J103" s="9"/>
-      <c r="K103" s="9"/>
-      <c r="L103" s="9"/>
-    </row>
-    <row r="104" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J104" s="9"/>
-      <c r="K104" s="9"/>
-      <c r="L104" s="9"/>
-    </row>
-    <row r="105" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J105" s="9"/>
-      <c r="K105" s="9"/>
-      <c r="L105" s="9"/>
-    </row>
-    <row r="106" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J106" s="9"/>
-      <c r="K106" s="9"/>
-      <c r="L106" s="9"/>
-    </row>
-    <row r="107" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J107" s="9"/>
-      <c r="K107" s="9"/>
-      <c r="L107" s="9"/>
-    </row>
-    <row r="108" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J108" s="9"/>
-      <c r="K108" s="9"/>
-      <c r="L108" s="9"/>
-    </row>
-    <row r="109" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J109" s="9"/>
-      <c r="K109" s="9"/>
-      <c r="L109" s="9"/>
-    </row>
-    <row r="110" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J110" s="9"/>
-      <c r="K110" s="9"/>
-      <c r="L110" s="9"/>
-    </row>
-    <row r="111" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J111" s="9"/>
-      <c r="K111" s="9"/>
-      <c r="L111" s="9"/>
-    </row>
-    <row r="112" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J112" s="9"/>
-      <c r="K112" s="9"/>
-      <c r="L112" s="9"/>
-    </row>
-    <row r="113" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J113" s="9"/>
-      <c r="K113" s="9"/>
-      <c r="L113" s="9"/>
-    </row>
-    <row r="114" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J114" s="9"/>
-      <c r="K114" s="9"/>
-      <c r="L114" s="9"/>
-    </row>
-    <row r="115" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J115" s="9"/>
-      <c r="K115" s="9"/>
-      <c r="L115" s="9"/>
-    </row>
-    <row r="116" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J116" s="9"/>
-      <c r="K116" s="9"/>
-      <c r="L116" s="9"/>
-    </row>
-    <row r="117" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J117" s="9"/>
-      <c r="K117" s="9"/>
-      <c r="L117" s="9"/>
-    </row>
-    <row r="118" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J118" s="9"/>
-      <c r="K118" s="9"/>
-      <c r="L118" s="9"/>
-    </row>
-    <row r="119" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J119" s="9"/>
-      <c r="K119" s="9"/>
-      <c r="L119" s="9"/>
-    </row>
-    <row r="120" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J120" s="9"/>
-      <c r="K120" s="9"/>
-      <c r="L120" s="9"/>
-    </row>
-    <row r="121" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J121" s="9"/>
-      <c r="K121" s="9"/>
-      <c r="L121" s="9"/>
-    </row>
-    <row r="122" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J122" s="9"/>
-      <c r="K122" s="9"/>
-      <c r="L122" s="9"/>
-    </row>
-    <row r="123" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J123" s="9"/>
-      <c r="K123" s="9"/>
-      <c r="L123" s="9"/>
-    </row>
-    <row r="124" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J124" s="9"/>
-      <c r="K124" s="9"/>
-      <c r="L124" s="9"/>
-    </row>
-    <row r="125" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J125" s="9"/>
-      <c r="K125" s="9"/>
-      <c r="L125" s="9"/>
-    </row>
-    <row r="126" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J126" s="9"/>
-      <c r="K126" s="9"/>
-      <c r="L126" s="9"/>
-    </row>
-    <row r="127" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J127" s="9"/>
-      <c r="K127" s="9"/>
-      <c r="L127" s="9"/>
-    </row>
-    <row r="128" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J128" s="9"/>
-      <c r="K128" s="9"/>
-      <c r="L128" s="9"/>
-    </row>
-    <row r="129" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J129" s="9"/>
-      <c r="K129" s="9"/>
-      <c r="L129" s="9"/>
-    </row>
-    <row r="130" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J130" s="9"/>
-      <c r="K130" s="9"/>
-      <c r="L130" s="9"/>
-    </row>
-    <row r="131" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J131" s="9"/>
-      <c r="K131" s="9"/>
-      <c r="L131" s="9"/>
-    </row>
-    <row r="132" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J132" s="9"/>
-      <c r="K132" s="9"/>
-      <c r="L132" s="9"/>
-    </row>
-    <row r="133" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J133" s="9"/>
-      <c r="K133" s="9"/>
-      <c r="L133" s="9"/>
-    </row>
-    <row r="134" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J134" s="9"/>
-      <c r="K134" s="9"/>
-      <c r="L134" s="9"/>
-    </row>
-    <row r="135" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J135" s="9"/>
-      <c r="K135" s="9"/>
-      <c r="L135" s="9"/>
-    </row>
-    <row r="136" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J136" s="9"/>
-      <c r="K136" s="9"/>
-      <c r="L136" s="9"/>
-    </row>
-    <row r="137" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J137" s="9"/>
-      <c r="K137" s="9"/>
-      <c r="L137" s="9"/>
-    </row>
-    <row r="138" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J138" s="9"/>
-      <c r="K138" s="9"/>
-      <c r="L138" s="9"/>
-    </row>
-    <row r="139" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J139" s="9"/>
-      <c r="K139" s="9"/>
-      <c r="L139" s="9"/>
-    </row>
-    <row r="140" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J140" s="9"/>
-      <c r="K140" s="9"/>
-      <c r="L140" s="9"/>
-    </row>
-    <row r="141" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J141" s="9"/>
-      <c r="K141" s="9"/>
-      <c r="L141" s="9"/>
-    </row>
-    <row r="142" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J142" s="9"/>
-      <c r="K142" s="9"/>
-      <c r="L142" s="9"/>
-    </row>
-    <row r="143" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J143" s="9"/>
-      <c r="K143" s="9"/>
-      <c r="L143" s="9"/>
-    </row>
-    <row r="144" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J144" s="9"/>
-      <c r="K144" s="9"/>
-      <c r="L144" s="9"/>
-    </row>
-    <row r="145" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J145" s="9"/>
-      <c r="K145" s="9"/>
-      <c r="L145" s="9"/>
-    </row>
-    <row r="146" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J146" s="9"/>
-      <c r="K146" s="9"/>
-      <c r="L146" s="9"/>
-    </row>
-    <row r="147" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J147" s="9"/>
-      <c r="K147" s="9"/>
-      <c r="L147" s="9"/>
-    </row>
-    <row r="148" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J148" s="9"/>
-      <c r="K148" s="9"/>
-      <c r="L148" s="9"/>
-    </row>
-    <row r="149" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J149" s="9"/>
-      <c r="K149" s="9"/>
-      <c r="L149" s="9"/>
-    </row>
-    <row r="150" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J150" s="9"/>
-      <c r="K150" s="9"/>
-      <c r="L150" s="9"/>
-    </row>
-    <row r="151" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J151" s="9"/>
-      <c r="K151" s="9"/>
-      <c r="L151" s="9"/>
-    </row>
-    <row r="152" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J152" s="9"/>
-      <c r="K152" s="9"/>
-      <c r="L152" s="9"/>
-    </row>
-    <row r="153" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J153" s="9"/>
-      <c r="K153" s="9"/>
-      <c r="L153" s="9"/>
-    </row>
-    <row r="154" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J154" s="9"/>
-      <c r="K154" s="9"/>
-      <c r="L154" s="9"/>
-    </row>
-    <row r="155" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J155" s="9"/>
-      <c r="K155" s="9"/>
-      <c r="L155" s="9"/>
-    </row>
-    <row r="156" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J156" s="9"/>
-      <c r="K156" s="9"/>
-      <c r="L156" s="9"/>
-    </row>
-    <row r="157" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J157" s="9"/>
-      <c r="K157" s="9"/>
-      <c r="L157" s="9"/>
-    </row>
-    <row r="158" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J158" s="9"/>
-      <c r="K158" s="9"/>
-      <c r="L158" s="9"/>
-    </row>
-    <row r="159" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J159" s="9"/>
-      <c r="K159" s="9"/>
-      <c r="L159" s="9"/>
-    </row>
-    <row r="160" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J160" s="9"/>
-      <c r="K160" s="9"/>
-      <c r="L160" s="9"/>
-    </row>
-    <row r="161" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J161" s="9"/>
-      <c r="K161" s="9"/>
-      <c r="L161" s="9"/>
-    </row>
-    <row r="162" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J162" s="9"/>
-      <c r="K162" s="9"/>
-      <c r="L162" s="9"/>
-    </row>
-    <row r="163" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J163" s="9"/>
-      <c r="K163" s="9"/>
-      <c r="L163" s="9"/>
+      <c r="M135" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F136" s="12"/>
+      <c r="G136" s="12"/>
+      <c r="H136" s="12"/>
+      <c r="I136" s="12"/>
+      <c r="J136" s="14"/>
+      <c r="K136" s="12"/>
+      <c r="L136" s="12"/>
+      <c r="M136" s="12"/>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F137" s="12"/>
+      <c r="G137" s="12"/>
+      <c r="H137" s="12"/>
+      <c r="I137" s="12"/>
+      <c r="J137" s="14"/>
+      <c r="K137" s="12"/>
+      <c r="L137" s="12"/>
+      <c r="M137" s="12"/>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F138" s="12"/>
+      <c r="G138" s="12"/>
+      <c r="H138" s="12"/>
+      <c r="I138" s="12"/>
+      <c r="J138" s="14"/>
+      <c r="K138" s="12"/>
+      <c r="L138" s="12"/>
+      <c r="M138" s="12"/>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F139" s="12"/>
+      <c r="G139" s="12"/>
+      <c r="H139" s="12"/>
+      <c r="I139" s="12"/>
+      <c r="J139" s="14"/>
+      <c r="K139" s="12"/>
+      <c r="L139" s="12"/>
+      <c r="M139" s="12"/>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F140" s="12"/>
+      <c r="G140" s="12"/>
+      <c r="H140" s="12"/>
+      <c r="I140" s="12"/>
+      <c r="J140" s="14"/>
+      <c r="K140" s="12"/>
+      <c r="L140" s="12"/>
+      <c r="M140" s="12"/>
+    </row>
+    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F141" s="12"/>
+      <c r="G141" s="12"/>
+      <c r="H141" s="12"/>
+      <c r="I141" s="12"/>
+      <c r="J141" s="14"/>
+      <c r="K141" s="12"/>
+      <c r="L141" s="12"/>
+      <c r="M141" s="12"/>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F142" s="12"/>
+      <c r="G142" s="12"/>
+      <c r="H142" s="12"/>
+      <c r="I142" s="12"/>
+      <c r="J142" s="14"/>
+      <c r="K142" s="12"/>
+      <c r="L142" s="12"/>
+      <c r="M142" s="12"/>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F143" s="12"/>
+      <c r="G143" s="12"/>
+      <c r="H143" s="12"/>
+      <c r="I143" s="12"/>
+      <c r="J143" s="14"/>
+      <c r="K143" s="12"/>
+      <c r="L143" s="12"/>
+      <c r="M143" s="12"/>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F144" s="12"/>
+      <c r="G144" s="12"/>
+      <c r="H144" s="12"/>
+      <c r="I144" s="12"/>
+      <c r="J144" s="14"/>
+      <c r="K144" s="12"/>
+      <c r="L144" s="12"/>
+      <c r="M144" s="12"/>
+    </row>
+    <row r="145" spans="6:13" x14ac:dyDescent="0.3">
+      <c r="F145" s="12"/>
+      <c r="G145" s="12"/>
+      <c r="H145" s="12"/>
+      <c r="I145" s="12"/>
+      <c r="J145" s="14"/>
+      <c r="K145" s="12"/>
+      <c r="L145" s="12"/>
+      <c r="M145" s="12"/>
+    </row>
+    <row r="146" spans="6:13" x14ac:dyDescent="0.3">
+      <c r="J146" s="6"/>
+      <c r="K146" s="6"/>
+      <c r="L146" s="6"/>
+    </row>
+    <row r="147" spans="6:13" x14ac:dyDescent="0.3">
+      <c r="J147" s="6"/>
+      <c r="K147" s="6"/>
+      <c r="L147" s="6"/>
+    </row>
+    <row r="148" spans="6:13" x14ac:dyDescent="0.3">
+      <c r="J148" s="6"/>
+      <c r="K148" s="6"/>
+      <c r="L148" s="6"/>
+    </row>
+    <row r="149" spans="6:13" x14ac:dyDescent="0.3">
+      <c r="J149" s="6"/>
+      <c r="K149" s="6"/>
+      <c r="L149" s="6"/>
+    </row>
+    <row r="150" spans="6:13" x14ac:dyDescent="0.3">
+      <c r="J150" s="6"/>
+      <c r="K150" s="6"/>
+      <c r="L150" s="6"/>
+    </row>
+    <row r="151" spans="6:13" x14ac:dyDescent="0.3">
+      <c r="J151" s="6"/>
+      <c r="K151" s="6"/>
+      <c r="L151" s="6"/>
+    </row>
+    <row r="152" spans="6:13" x14ac:dyDescent="0.3">
+      <c r="J152" s="6"/>
+      <c r="K152" s="6"/>
+      <c r="L152" s="6"/>
+    </row>
+    <row r="153" spans="6:13" x14ac:dyDescent="0.3">
+      <c r="J153" s="6"/>
+      <c r="K153" s="6"/>
+      <c r="L153" s="6"/>
+    </row>
+    <row r="154" spans="6:13" x14ac:dyDescent="0.3">
+      <c r="J154" s="6"/>
+      <c r="K154" s="6"/>
+      <c r="L154" s="6"/>
+    </row>
+    <row r="155" spans="6:13" x14ac:dyDescent="0.3">
+      <c r="J155" s="6"/>
+      <c r="K155" s="6"/>
+      <c r="L155" s="6"/>
+    </row>
+    <row r="156" spans="6:13" x14ac:dyDescent="0.3">
+      <c r="J156" s="6"/>
+      <c r="K156" s="6"/>
+      <c r="L156" s="6"/>
+    </row>
+    <row r="157" spans="6:13" x14ac:dyDescent="0.3">
+      <c r="J157" s="6"/>
+      <c r="K157" s="6"/>
+      <c r="L157" s="6"/>
+    </row>
+    <row r="158" spans="6:13" x14ac:dyDescent="0.3">
+      <c r="J158" s="6"/>
+      <c r="K158" s="6"/>
+      <c r="L158" s="6"/>
+    </row>
+    <row r="159" spans="6:13" x14ac:dyDescent="0.3">
+      <c r="J159" s="6"/>
+      <c r="K159" s="6"/>
+      <c r="L159" s="6"/>
+    </row>
+    <row r="160" spans="6:13" x14ac:dyDescent="0.3">
+      <c r="J160" s="6"/>
+      <c r="K160" s="6"/>
+      <c r="L160" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M6" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M97">
-      <sortCondition ref="A1:A6"/>
+  <autoFilter ref="A1:M8" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M136">
+      <sortCondition ref="A1:A8"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCreation\Web\Gathering_Island\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Confidential\Gathering_Island\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94195A66-04A2-4980-8ACA-E0DC52605529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A08EF74-25C2-4BFA-9CC9-9438294711E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-18255" yWindow="2790" windowWidth="19725" windowHeight="10830" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="events" sheetId="1" r:id="rId1"/>
+    <sheet name="工作表1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">events!$A$1:$M$8</definedName>
@@ -53,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="957" uniqueCount="661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="675">
   <si>
     <t>event_id</t>
   </si>
@@ -166,9 +167,6 @@
     <t>台北市美術館</t>
   </si>
   <si>
-    <t>北海道之旅</t>
-  </si>
-  <si>
     <t>日本北海道</t>
   </si>
   <si>
@@ -218,10 +216,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>五天四夜溫泉雪景之旅</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>年度城市馬拉松，歡迎全民參與</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -278,9 +272,6 @@
     <t>蘆竹市美食節</t>
   </si>
   <si>
-    <t>首頁學習營</t>
-  </si>
-  <si>
     <t>記者學習營</t>
   </si>
   <si>
@@ -470,9 +461,6 @@
     <t>路跑活動</t>
   </si>
   <si>
-    <t>聖誕派對</t>
-  </si>
-  <si>
     <t>彰化縣彰化市中正路150號</t>
   </si>
   <si>
@@ -545,12 +533,6 @@
     <t>卡牌對戰賽</t>
   </si>
   <si>
-    <t>海島旅行</t>
-  </si>
-  <si>
-    <t>啤酒節</t>
-  </si>
-  <si>
     <t>喜愛遊戲的朋友不能錯過的桌遊之夜。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -571,14 +553,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>這是一場聖誕派對，讓你盡情享受音樂與舞蹈。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>這是一場週末派對，讓你盡情享受音樂與舞蹈。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>精選作品展出，帶來藝術與創意的動漫展。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -659,14 +633,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>一場特別的海島旅行，讓你探索不同風景與文化。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>讓味蕾享受不同美食文化的啤酒節。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>event_description</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -828,9 +794,6 @@
     <t>2024-07-17 20:00:00</t>
   </si>
   <si>
-    <t>2024-04-09 19:00:00</t>
-  </si>
-  <si>
     <t>2026-08-01 13:00:00</t>
   </si>
   <si>
@@ -846,12 +809,6 @@
     <t>2025-09-08 22:00:00</t>
   </si>
   <si>
-    <t>2024-05-08 18:00:00</t>
-  </si>
-  <si>
-    <t>2024-01-22 12:00:00</t>
-  </si>
-  <si>
     <t>2024-05-16 22:00:00</t>
   </si>
   <si>
@@ -864,9 +821,6 @@
     <t>2026-11-30 20:00:00</t>
   </si>
   <si>
-    <t>2024-04-29 18:00:00</t>
-  </si>
-  <si>
     <t>2024-12-29 17:00:00</t>
   </si>
   <si>
@@ -900,18 +854,12 @@
     <t>2025-04-28 21:00:00</t>
   </si>
   <si>
-    <t>2024-02-11 11:00:00</t>
-  </si>
-  <si>
     <t>2026-08-16 08:00:00</t>
   </si>
   <si>
     <t>2025-05-29 18:00:00</t>
   </si>
   <si>
-    <t>2024-03-12 16:00:00</t>
-  </si>
-  <si>
     <t>2025-01-05 10:00:00</t>
   </si>
   <si>
@@ -930,9 +878,6 @@
     <t>2024-12-04 15:00:00</t>
   </si>
   <si>
-    <t>2024-01-12 13:00:00</t>
-  </si>
-  <si>
     <t>2026-08-25 20:00:00</t>
   </si>
   <si>
@@ -1110,9 +1055,6 @@
     <t>2024-06-23 20:00:00</t>
   </si>
   <si>
-    <t>2024-03-24 19:00:00</t>
-  </si>
-  <si>
     <t>2026-07-11 13:00:00</t>
   </si>
   <si>
@@ -1128,12 +1070,6 @@
     <t>2025-08-16 22:00:00</t>
   </si>
   <si>
-    <t>2024-04-12 18:00:00</t>
-  </si>
-  <si>
-    <t>2024-01-09 12:00:00</t>
-  </si>
-  <si>
     <t>2024-04-19 22:00:00</t>
   </si>
   <si>
@@ -1146,9 +1082,6 @@
     <t>2026-11-19 20:00:00</t>
   </si>
   <si>
-    <t>2024-04-14 18:00:00</t>
-  </si>
-  <si>
     <t>2024-12-10 17:00:00</t>
   </si>
   <si>
@@ -1182,18 +1115,12 @@
     <t>2025-04-11 21:00:00</t>
   </si>
   <si>
-    <t>2024-01-19 11:00:00</t>
-  </si>
-  <si>
     <t>2026-07-30 08:00:00</t>
   </si>
   <si>
     <t>2025-04-29 18:00:00</t>
   </si>
   <si>
-    <t>2024-02-16 16:00:00</t>
-  </si>
-  <si>
     <t>2024-12-14 10:00:00</t>
   </si>
   <si>
@@ -1212,9 +1139,6 @@
     <t>2024-11-16 15:00:00</t>
   </si>
   <si>
-    <t>2023-12-19 13:00:00</t>
-  </si>
-  <si>
     <t>2026-08-03 20:00:00</t>
   </si>
   <si>
@@ -1251,27 +1175,6 @@
     <t>2025-10-05 21:00:00</t>
   </si>
   <si>
-    <t>2024-01-08 13:00:00</t>
-  </si>
-  <si>
-    <t>2024-01-19 12:00:00</t>
-  </si>
-  <si>
-    <t>2024-02-08 11:00:00</t>
-  </si>
-  <si>
-    <t>2024-03-09 16:00:00</t>
-  </si>
-  <si>
-    <t>2024-04-08 19:00:00</t>
-  </si>
-  <si>
-    <t>2024-05-04 18:00:00</t>
-  </si>
-  <si>
-    <t>2024-04-28 18:00:00</t>
-  </si>
-  <si>
     <t>2024-05-14 22:00:00</t>
   </si>
   <si>
@@ -1551,9 +1454,6 @@
     <t>高雄市左營區博愛二路777號（高雄巨蛋會議廳）</t>
   </si>
   <si>
-    <t>當代攝影展</t>
-  </si>
-  <si>
     <t>台北市中正區愛國西路49號（台北市立美術館）</t>
   </si>
   <si>
@@ -1605,10 +1505,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>展出台灣新銳攝影師的作品</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>深入花東縱谷的自然與人文之旅</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1751,10 +1647,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>認識在地飲食文化與手工特色食材。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>沙灘、音樂與比基尼的完美結合！</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1799,12 +1691,6 @@
     <t>2025-09-10 09:00:00</t>
   </si>
   <si>
-    <t>2024-03-15 10:00:00</t>
-  </si>
-  <si>
-    <t>2024-01-05 14:30:00</t>
-  </si>
-  <si>
     <t>2025-05-01 08:00:00</t>
   </si>
   <si>
@@ -1892,15 +1778,6 @@
     <t>2031-03-22 19:00:00</t>
   </si>
   <si>
-    <t>2024-04-09 17:00:00</t>
-  </si>
-  <si>
-    <t>2024-03-26 17:00:00</t>
-  </si>
-  <si>
-    <t>2024-03-06 17:00:00</t>
-  </si>
-  <si>
     <t>2029-08-29 12:00:00</t>
   </si>
   <si>
@@ -2009,15 +1886,6 @@
     <t>2029-04-11 15:00:00</t>
   </si>
   <si>
-    <t>2023-04-24 11:00:00</t>
-  </si>
-  <si>
-    <t>2023-04-14 11:00:00</t>
-  </si>
-  <si>
-    <t>2023-03-01 11:00:00</t>
-  </si>
-  <si>
     <t>2035-01-23 08:00:00</t>
   </si>
   <si>
@@ -2121,12 +1989,188 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2024-03-11 00:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>2026-03-16 00:00:00</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>event_description</t>
+  </si>
+  <si>
+    <t>要不要來學AI（有冷氣）</t>
+  </si>
+  <si>
+    <t>很怕報名的人都跑了所以先說：前面會有吃的，然後才是講座。一起坐一起滑手機也可以。</t>
+  </si>
+  <si>
+    <t>北海道泡湯團（雪厚到爆）</t>
+  </si>
+  <si>
+    <t>純粹想泡湯，有人要跟嗎？白天行程我應該會亂走一通。</t>
+  </si>
+  <si>
+    <t>攝影展揪一波（不保證會看懂）</t>
+  </si>
+  <si>
+    <t>主揪可能只會拍人，不一定在看展，想來亂晃的可以+1。</t>
+  </si>
+  <si>
+    <t>啤酒節生死鬥</t>
+  </si>
+  <si>
+    <t>去年被灌到回不了家，今年打算吃東西為主，誰要來幫顧戰力。</t>
+  </si>
+  <si>
+    <t>花蓮旅遊但會累爆</t>
+  </si>
+  <si>
+    <t>有點後悔自己排這麼滿的行程，但錢都繳了只能硬著頭皮揪人了。</t>
+  </si>
+  <si>
+    <t>部門耶誕交換禮物（二刷）</t>
+  </si>
+  <si>
+    <t>我們部門自己辦的，可以帶朋友來！但先說活動很吵XD</t>
+  </si>
+  <si>
+    <t>吃吃找找行軍賽（超級混亂）</t>
+  </si>
+  <si>
+    <t>這不是什麼正經活動，單純揪大家一起吃+迷路，怕吵勿報。</t>
+  </si>
+  <si>
+    <t>學習營但中間有在偷玩</t>
+  </si>
+  <si>
+    <t>中間會有偷懶時段可以聊天，要認真學的人也歡迎，但我可能會滑手機。</t>
+  </si>
+  <si>
+    <t>週末沒事來跳舞？</t>
+  </si>
+  <si>
+    <t>音樂很大聲，但來了應該會很開心，穿輕鬆一點不要尷尬～</t>
+  </si>
+  <si>
+    <t>開發者社群小小揪</t>
+  </si>
+  <si>
+    <t>沒有很專業，真的就只是想找人一起講幹話，討論技術也可以。</t>
+  </si>
+  <si>
+    <t>要不要來學AI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>北海道泡湯團</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攝影展揪一波</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>啤酒節生死鬥</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>部門耶誕交換禮物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吃吃找找行軍賽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-04-24 11:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-04-14 11:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-03-01 11:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-01-12 13:00:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 13:00:00</t>
+  </si>
+  <si>
+    <t>2026-12-19 13:00:00</t>
+  </si>
+  <si>
+    <t>2026-03-15 10:00:00</t>
+  </si>
+  <si>
+    <t>2026-03-11 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-01-05 14:30:00</t>
+  </si>
+  <si>
+    <t>2026-01-22 12:00:00</t>
+  </si>
+  <si>
+    <t>2026-01-19 12:00:00</t>
+  </si>
+  <si>
+    <t>2026-01-09 12:00:00</t>
+  </si>
+  <si>
+    <t>2026-02-11 11:00:00</t>
+  </si>
+  <si>
+    <t>2026-02-08 11:00:00</t>
+  </si>
+  <si>
+    <t>2026-01-19 11:00:00</t>
+  </si>
+  <si>
+    <t>2026-03-12 16:00:00</t>
+  </si>
+  <si>
+    <t>2026-03-09 16:00:00</t>
+  </si>
+  <si>
+    <t>2026-02-16 16:00:00</t>
+  </si>
+  <si>
+    <t>2026-04-09 17:00:00</t>
+  </si>
+  <si>
+    <t>2026-03-26 17:00:00</t>
+  </si>
+  <si>
+    <t>2026-03-06 17:00:00</t>
+  </si>
+  <si>
+    <t>2026-04-09 19:00:00</t>
+  </si>
+  <si>
+    <t>2026-04-08 19:00:00</t>
+  </si>
+  <si>
+    <t>2026-03-24 19:00:00</t>
+  </si>
+  <si>
+    <t>2026-05-08 18:00:00</t>
+  </si>
+  <si>
+    <t>2026-05-04 18:00:00</t>
+  </si>
+  <si>
+    <t>2026-04-12 18:00:00</t>
+  </si>
+  <si>
+    <t>2026-04-29 18:00:00</t>
+  </si>
+  <si>
+    <t>2026-04-28 18:00:00</t>
+  </si>
+  <si>
+    <t>2026-04-14 18:00:00</t>
   </si>
 </sst>
 </file>
@@ -2589,7 +2633,7 @@
         <v>23</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="K1" s="11" t="s">
         <v>15</v>
@@ -2598,7 +2642,7 @@
         <v>24</v>
       </c>
       <c r="M1" s="11" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
@@ -2609,7 +2653,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>2</v>
@@ -2630,16 +2674,16 @@
         <v>7</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="K2" s="10" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="L2" s="10" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="M2" s="10" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
@@ -2647,22 +2691,22 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>516</v>
+        <v>639</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>538</v>
+        <v>620</v>
       </c>
       <c r="D3" s="2">
         <v>3</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>520</v>
+        <v>487</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G3" s="2">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H3" s="2">
         <v>500</v>
@@ -2671,16 +2715,16 @@
         <v>78</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>622</v>
+        <v>645</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>623</v>
+        <v>646</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>624</v>
+        <v>647</v>
       </c>
       <c r="M3" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3" s="13"/>
       <c r="O3" s="13"/>
@@ -2691,16 +2735,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>36</v>
+        <v>640</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>52</v>
+        <v>622</v>
       </c>
       <c r="D4" s="2">
         <v>5</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>11</v>
@@ -2715,16 +2759,16 @@
         <v>5</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>271</v>
+        <v>648</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>378</v>
+        <v>649</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>365</v>
+        <v>650</v>
       </c>
       <c r="M4" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
@@ -2735,16 +2779,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>478</v>
+        <v>641</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>495</v>
+        <v>624</v>
       </c>
       <c r="D5" s="2">
         <v>4</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>479</v>
+        <v>447</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>11</v>
@@ -2759,16 +2803,16 @@
         <v>65</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>552</v>
+        <v>651</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>553</v>
+        <v>653</v>
       </c>
       <c r="M5" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" s="7"/>
       <c r="P5" s="7"/>
@@ -2779,16 +2823,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>155</v>
+        <v>642</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>184</v>
+        <v>626</v>
       </c>
       <c r="D6" s="2">
         <v>8</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>11</v>
@@ -2803,16 +2847,16 @@
         <v>2</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>244</v>
+        <v>654</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>379</v>
+        <v>655</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>338</v>
+        <v>656</v>
       </c>
       <c r="M6" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
@@ -2823,16 +2867,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>154</v>
+        <v>627</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>183</v>
+        <v>628</v>
       </c>
       <c r="D7" s="2">
         <v>5</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>11</v>
@@ -2847,16 +2891,16 @@
         <v>48</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>261</v>
+        <v>657</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>380</v>
+        <v>658</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>355</v>
+        <v>659</v>
       </c>
       <c r="M7" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
@@ -2864,16 +2908,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>129</v>
+        <v>643</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>161</v>
+        <v>630</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>11</v>
@@ -2888,16 +2932,16 @@
         <v>12</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>264</v>
+        <v>660</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>381</v>
+        <v>661</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>358</v>
+        <v>662</v>
       </c>
       <c r="M8" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
@@ -2908,16 +2952,16 @@
         <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>504</v>
+        <v>644</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>532</v>
+        <v>632</v>
       </c>
       <c r="D9" s="2">
         <v>7</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>11</v>
@@ -2932,16 +2976,16 @@
         <v>57</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>583</v>
+        <v>663</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>584</v>
+        <v>664</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>585</v>
+        <v>665</v>
       </c>
       <c r="M9" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" s="7"/>
       <c r="P9" s="7"/>
@@ -2952,16 +2996,16 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>70</v>
+        <v>633</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>89</v>
+        <v>634</v>
       </c>
       <c r="D10" s="2">
         <v>3</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>11</v>
@@ -2976,16 +3020,16 @@
         <v>20</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>237</v>
+        <v>666</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>382</v>
+        <v>667</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>331</v>
+        <v>668</v>
       </c>
       <c r="M10" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" s="7"/>
       <c r="P10" s="7"/>
@@ -2996,16 +3040,16 @@
         <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>8</v>
+        <v>635</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>162</v>
+        <v>636</v>
       </c>
       <c r="D11" s="2">
         <v>1</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>11</v>
@@ -3020,16 +3064,16 @@
         <v>37</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>243</v>
+        <v>669</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>383</v>
+        <v>670</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>337</v>
+        <v>671</v>
       </c>
       <c r="M11" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" s="7"/>
       <c r="P11" s="7"/>
@@ -3040,16 +3084,16 @@
         <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>26</v>
+        <v>637</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>171</v>
+        <v>638</v>
       </c>
       <c r="D12" s="2">
         <v>3</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>11</v>
@@ -3064,16 +3108,16 @@
         <v>21</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>249</v>
+        <v>672</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>384</v>
+        <v>673</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>343</v>
+        <v>674</v>
       </c>
       <c r="M12" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" s="7"/>
       <c r="P12" s="7"/>
@@ -3084,16 +3128,16 @@
         <v>11</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="D13" s="2">
         <v>9</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>11</v>
@@ -3108,13 +3152,13 @@
         <v>27</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>385</v>
+        <v>354</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>339</v>
+        <v>319</v>
       </c>
       <c r="M13" s="8">
         <v>1</v>
@@ -3131,13 +3175,13 @@
         <v>26</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="D14" s="2">
         <v>3</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>11</v>
@@ -3152,13 +3196,13 @@
         <v>16</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>386</v>
+        <v>355</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="M14" s="8">
         <v>1</v>
@@ -3172,16 +3216,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="D15" s="2">
         <v>7</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>11</v>
@@ -3196,13 +3240,13 @@
         <v>12</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>387</v>
+        <v>356</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>352</v>
+        <v>331</v>
       </c>
       <c r="M15" s="8">
         <v>1</v>
@@ -3216,16 +3260,16 @@
         <v>14</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>484</v>
+        <v>452</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>498</v>
+        <v>465</v>
       </c>
       <c r="D16" s="2">
         <v>7</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>485</v>
+        <v>453</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>11</v>
@@ -3240,13 +3284,13 @@
         <v>12</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>559</v>
+        <v>523</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>560</v>
+        <v>524</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>561</v>
+        <v>525</v>
       </c>
       <c r="M16" s="8">
         <v>1</v>
@@ -3260,16 +3304,16 @@
         <v>15</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>529</v>
+        <v>496</v>
       </c>
       <c r="D17" s="2">
         <v>8</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>505</v>
+        <v>472</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>11</v>
@@ -3284,13 +3328,13 @@
         <v>75</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>574</v>
+        <v>538</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>575</v>
+        <v>539</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>576</v>
+        <v>540</v>
       </c>
       <c r="M17" s="8">
         <v>1</v>
@@ -3304,16 +3348,16 @@
         <v>16</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="D18" s="2">
         <v>8</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>11</v>
@@ -3328,13 +3372,13 @@
         <v>44</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>330</v>
+        <v>313</v>
       </c>
       <c r="M18" s="8">
         <v>1</v>
@@ -3348,16 +3392,16 @@
         <v>17</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D19" s="2">
         <v>6</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>11</v>
@@ -3372,13 +3416,13 @@
         <v>20</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>389</v>
+        <v>358</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="M19" s="8">
         <v>1</v>
@@ -3395,13 +3439,13 @@
         <v>34</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="D20" s="2">
         <v>4</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>11</v>
@@ -3416,13 +3460,13 @@
         <v>7</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>390</v>
+        <v>359</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
       <c r="M20" s="8">
         <v>1</v>
@@ -3436,16 +3480,16 @@
         <v>19</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D21" s="2">
         <v>7</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>11</v>
@@ -3460,13 +3504,13 @@
         <v>49</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>391</v>
+        <v>360</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>341</v>
+        <v>321</v>
       </c>
       <c r="M21" s="8">
         <v>1</v>
@@ -3504,13 +3548,13 @@
         <v>42</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>282</v>
+        <v>265</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>392</v>
+        <v>361</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
       <c r="M22" s="8">
         <v>1</v>
@@ -3527,13 +3571,13 @@
         <v>12</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="D23" s="2">
         <v>2</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>11</v>
@@ -3548,13 +3592,13 @@
         <v>19</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>393</v>
+        <v>362</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>328</v>
+        <v>311</v>
       </c>
       <c r="M23" s="8">
         <v>1</v>
@@ -3571,13 +3615,13 @@
         <v>12</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="D24" s="2">
         <v>2</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>11</v>
@@ -3592,13 +3636,13 @@
         <v>50</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>394</v>
+        <v>363</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>367</v>
+        <v>343</v>
       </c>
       <c r="M24" s="8">
         <v>1</v>
@@ -3612,16 +3656,16 @@
         <v>23</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D25" s="2">
         <v>7</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>11</v>
@@ -3636,13 +3680,13 @@
         <v>7</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>278</v>
+        <v>261</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>395</v>
+        <v>364</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>372</v>
+        <v>348</v>
       </c>
       <c r="M25" s="8">
         <v>1</v>
@@ -3656,16 +3700,16 @@
         <v>24</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D26" s="2">
         <v>7</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>11</v>
@@ -3680,13 +3724,13 @@
         <v>9</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>270</v>
+        <v>254</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>396</v>
+        <v>365</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>364</v>
+        <v>341</v>
       </c>
       <c r="M26" s="8">
         <v>1</v>
@@ -3700,16 +3744,16 @@
         <v>25</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="D27" s="2">
         <v>4</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>11</v>
@@ -3724,13 +3768,13 @@
         <v>29</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>397</v>
+        <v>366</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>360</v>
+        <v>337</v>
       </c>
       <c r="M27" s="8">
         <v>1</v>
@@ -3768,13 +3812,13 @@
         <v>1</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>280</v>
+        <v>263</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>398</v>
+        <v>367</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
       <c r="M28" s="8">
         <v>1</v>
@@ -3788,16 +3832,16 @@
         <v>27</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="D29" s="2">
         <v>4</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>11</v>
@@ -3812,13 +3856,13 @@
         <v>14</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>399</v>
+        <v>368</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>344</v>
+        <v>323</v>
       </c>
       <c r="M29" s="8">
         <v>1</v>
@@ -3835,7 +3879,7 @@
         <v>34</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D30" s="2">
         <v>4</v>
@@ -3856,13 +3900,13 @@
         <v>4</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>265</v>
+        <v>249</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>400</v>
+        <v>369</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="M30" s="8">
         <v>1</v>
@@ -3876,16 +3920,16 @@
         <v>29</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D31" s="2">
         <v>1</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>11</v>
@@ -3900,13 +3944,13 @@
         <v>40</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>401</v>
+        <v>370</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>335</v>
+        <v>317</v>
       </c>
       <c r="M31" s="8">
         <v>1</v>
@@ -3944,13 +3988,13 @@
         <v>1</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>281</v>
+        <v>264</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>402</v>
+        <v>371</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>375</v>
+        <v>351</v>
       </c>
       <c r="M32" s="8">
         <v>1</v>
@@ -3964,16 +4008,16 @@
         <v>31</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>488</v>
+        <v>456</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>500</v>
+        <v>467</v>
       </c>
       <c r="D33" s="2">
         <v>9</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>489</v>
+        <v>457</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>11</v>
@@ -3988,13 +4032,13 @@
         <v>61</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>565</v>
+        <v>529</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>566</v>
+        <v>530</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>567</v>
+        <v>531</v>
       </c>
       <c r="M33" s="8">
         <v>1</v>
@@ -4008,16 +4052,16 @@
         <v>32</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>480</v>
+        <v>448</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>496</v>
+        <v>463</v>
       </c>
       <c r="D34" s="2">
         <v>5</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>481</v>
+        <v>449</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>11</v>
@@ -4032,13 +4076,13 @@
         <v>99</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>554</v>
+        <v>518</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>555</v>
+        <v>519</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>556</v>
+        <v>520</v>
       </c>
       <c r="M34" s="8">
         <v>1</v>
@@ -4052,16 +4096,16 @@
         <v>33</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D35" s="2">
         <v>6</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>11</v>
@@ -4076,13 +4120,13 @@
         <v>6</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>403</v>
+        <v>372</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>354</v>
+        <v>333</v>
       </c>
       <c r="M35" s="8">
         <v>1</v>
@@ -4099,13 +4143,13 @@
         <v>26</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="D36" s="2">
         <v>3</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>11</v>
@@ -4120,13 +4164,13 @@
         <v>2</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>404</v>
+        <v>373</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>357</v>
+        <v>335</v>
       </c>
       <c r="M36" s="8">
         <v>1</v>
@@ -4140,16 +4184,16 @@
         <v>35</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="D37" s="2">
         <v>5</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>11</v>
@@ -4164,13 +4208,13 @@
         <v>42</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>405</v>
+        <v>374</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>351</v>
+        <v>330</v>
       </c>
       <c r="M37" s="8">
         <v>1</v>
@@ -4184,16 +4228,16 @@
         <v>36</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="D38" s="2">
         <v>7</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>11</v>
@@ -4208,13 +4252,13 @@
         <v>34</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>406</v>
+        <v>375</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>333</v>
+        <v>315</v>
       </c>
       <c r="M38" s="8">
         <v>1</v>
@@ -4228,16 +4272,16 @@
         <v>37</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D39" s="2">
         <v>8</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>11</v>
@@ -4252,13 +4296,13 @@
         <v>8</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>268</v>
+        <v>252</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>407</v>
+        <v>376</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>362</v>
+        <v>339</v>
       </c>
       <c r="M39" s="8">
         <v>0</v>
@@ -4275,7 +4319,7 @@
         <v>8</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D40" s="2">
         <v>1</v>
@@ -4296,13 +4340,13 @@
         <v>1</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>408</v>
+        <v>377</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>347</v>
+        <v>326</v>
       </c>
       <c r="M40" s="8">
         <v>1</v>
@@ -4316,16 +4360,16 @@
         <v>39</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D41" s="2">
         <v>3</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>11</v>
@@ -4340,13 +4384,13 @@
         <v>4</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>409</v>
+        <v>378</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>336</v>
+        <v>318</v>
       </c>
       <c r="M41" s="8">
         <v>1</v>
@@ -4360,16 +4404,16 @@
         <v>40</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D42" s="2">
         <v>8</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>11</v>
@@ -4384,13 +4428,13 @@
         <v>30</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>410</v>
+        <v>379</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>353</v>
+        <v>332</v>
       </c>
       <c r="M42" s="8">
         <v>0</v>
@@ -4404,16 +4448,16 @@
         <v>41</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>476</v>
+        <v>445</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>494</v>
+        <v>462</v>
       </c>
       <c r="D43" s="2">
         <v>3</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>477</v>
+        <v>446</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>11</v>
@@ -4428,13 +4472,13 @@
         <v>35</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>549</v>
+        <v>515</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>550</v>
+        <v>516</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>551</v>
+        <v>517</v>
       </c>
       <c r="M43" s="8">
         <v>0</v>
@@ -4448,16 +4492,16 @@
         <v>42</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="D44" s="2">
         <v>1</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>11</v>
@@ -4472,13 +4516,13 @@
         <v>8</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>411</v>
+        <v>380</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="M44" s="8">
         <v>0</v>
@@ -4492,16 +4536,16 @@
         <v>43</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>533</v>
+        <v>500</v>
       </c>
       <c r="D45" s="2">
         <v>9</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>526</v>
+        <v>493</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>11</v>
@@ -4516,13 +4560,13 @@
         <v>43</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>649</v>
+        <v>607</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>650</v>
+        <v>608</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>651</v>
+        <v>609</v>
       </c>
       <c r="M45" s="8">
         <v>0</v>
@@ -4560,13 +4604,13 @@
         <v>10</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>283</v>
+        <v>266</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>412</v>
+        <v>381</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>377</v>
+        <v>353</v>
       </c>
       <c r="M46" s="8">
         <v>0</v>
@@ -4580,16 +4624,16 @@
         <v>45</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="D47" s="2">
         <v>6</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>11</v>
@@ -4604,13 +4648,13 @@
         <v>15</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>276</v>
+        <v>259</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>413</v>
+        <v>382</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>370</v>
+        <v>346</v>
       </c>
       <c r="M47" s="8">
         <v>0</v>
@@ -4624,16 +4668,16 @@
         <v>46</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="D48" s="2">
         <v>9</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>11</v>
@@ -4648,13 +4692,13 @@
         <v>35</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>414</v>
+        <v>383</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>371</v>
+        <v>347</v>
       </c>
       <c r="M48" s="8">
         <v>0</v>
@@ -4671,7 +4715,7 @@
         <v>12</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D49" s="2">
         <v>2</v>
@@ -4692,13 +4736,13 @@
         <v>2</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>415</v>
+        <v>384</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
       <c r="M49" s="8">
         <v>0</v>
@@ -4712,16 +4756,16 @@
         <v>48</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="D50" s="2">
         <v>3</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>11</v>
@@ -4736,13 +4780,13 @@
         <v>30</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>275</v>
+        <v>258</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>416</v>
+        <v>385</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>369</v>
+        <v>345</v>
       </c>
       <c r="M50" s="8">
         <v>0</v>
@@ -4756,16 +4800,16 @@
         <v>49</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>482</v>
+        <v>450</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>497</v>
+        <v>464</v>
       </c>
       <c r="D51" s="2">
         <v>6</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>483</v>
+        <v>451</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>11</v>
@@ -4780,13 +4824,13 @@
         <v>21</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>557</v>
+        <v>521</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>660</v>
+        <v>617</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>558</v>
+        <v>522</v>
       </c>
       <c r="M51" s="8">
         <v>0</v>
@@ -4800,16 +4844,16 @@
         <v>50</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>522</v>
+        <v>489</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>541</v>
+        <v>507</v>
       </c>
       <c r="D52" s="2">
         <v>9</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>514</v>
+        <v>481</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>11</v>
@@ -4824,13 +4868,13 @@
         <v>5</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>637</v>
+        <v>595</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>638</v>
+        <v>596</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>639</v>
+        <v>597</v>
       </c>
       <c r="M52" s="8">
         <v>0</v>
@@ -4844,16 +4888,16 @@
         <v>51</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D53" s="2">
         <v>2</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>11</v>
@@ -4868,13 +4912,13 @@
         <v>14</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>417</v>
+        <v>386</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>334</v>
+        <v>316</v>
       </c>
       <c r="M53" s="8">
         <v>0</v>
@@ -4888,16 +4932,16 @@
         <v>52</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="D54" s="2">
         <v>9</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>11</v>
@@ -4912,13 +4956,13 @@
         <v>42</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>269</v>
+        <v>253</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>418</v>
+        <v>387</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>363</v>
+        <v>340</v>
       </c>
       <c r="M54" s="8">
         <v>0</v>
@@ -4932,16 +4976,16 @@
         <v>53</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>521</v>
+        <v>488</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>540</v>
+        <v>506</v>
       </c>
       <c r="D55" s="2">
         <v>5</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>523</v>
+        <v>490</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>11</v>
@@ -4956,13 +5000,13 @@
         <v>50</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>634</v>
+        <v>592</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>635</v>
+        <v>593</v>
       </c>
       <c r="L55" s="3" t="s">
-        <v>636</v>
+        <v>594</v>
       </c>
       <c r="M55" s="8">
         <v>0</v>
@@ -4976,16 +5020,16 @@
         <v>54</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D56" s="2">
         <v>7</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>11</v>
@@ -5000,13 +5044,13 @@
         <v>4</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>419</v>
+        <v>388</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>346</v>
+        <v>325</v>
       </c>
       <c r="M56" s="8">
         <v>0</v>
@@ -5020,16 +5064,16 @@
         <v>55</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D57" s="2">
         <v>3</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>11</v>
@@ -5044,13 +5088,13 @@
         <v>19</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>420</v>
+        <v>389</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>312</v>
+        <v>295</v>
       </c>
       <c r="M57" s="8">
         <v>0</v>
@@ -5064,16 +5108,16 @@
         <v>56</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>522</v>
+        <v>489</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>533</v>
+        <v>500</v>
       </c>
       <c r="D58" s="2">
         <v>2</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>512</v>
+        <v>479</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>11</v>
@@ -5088,13 +5132,13 @@
         <v>41</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>616</v>
+        <v>577</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>617</v>
+        <v>578</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>618</v>
+        <v>579</v>
       </c>
       <c r="M58" s="8">
         <v>0</v>
@@ -5108,16 +5152,16 @@
         <v>57</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="D59" s="2">
         <v>9</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>11</v>
@@ -5132,13 +5176,13 @@
         <v>22</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>267</v>
+        <v>251</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>421</v>
+        <v>390</v>
       </c>
       <c r="L59" s="3" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="M59" s="8">
         <v>0</v>
@@ -5152,16 +5196,16 @@
         <v>58</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="D60" s="2">
         <v>5</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>11</v>
@@ -5176,13 +5220,13 @@
         <v>10</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>422</v>
+        <v>391</v>
       </c>
       <c r="L60" s="3" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
       <c r="M60" s="8">
         <v>0</v>
@@ -5196,16 +5240,16 @@
         <v>59</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>472</v>
+        <v>441</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>492</v>
+        <v>460</v>
       </c>
       <c r="D61" s="2">
         <v>1</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>473</v>
+        <v>442</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>11</v>
@@ -5220,13 +5264,13 @@
         <v>87</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>544</v>
+        <v>510</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>658</v>
+        <v>616</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>545</v>
+        <v>511</v>
       </c>
       <c r="M61" s="8">
         <v>0</v>
@@ -5240,16 +5284,16 @@
         <v>60</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="D62" s="2">
         <v>9</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>11</v>
@@ -5264,13 +5308,13 @@
         <v>38</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>423</v>
+        <v>392</v>
       </c>
       <c r="L62" s="3" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="M62" s="8">
         <v>0</v>
@@ -5287,7 +5331,7 @@
         <v>32</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D63" s="2">
         <v>3</v>
@@ -5308,13 +5352,13 @@
         <v>3</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>424</v>
+        <v>393</v>
       </c>
       <c r="L63" s="3" t="s">
-        <v>356</v>
+        <v>334</v>
       </c>
       <c r="M63" s="8">
         <v>0</v>
@@ -5328,16 +5372,16 @@
         <v>62</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D64" s="2">
         <v>7</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>11</v>
@@ -5352,13 +5396,13 @@
         <v>20</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>272</v>
+        <v>255</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>425</v>
+        <v>394</v>
       </c>
       <c r="L64" s="3" t="s">
-        <v>366</v>
+        <v>342</v>
       </c>
       <c r="M64" s="8">
         <v>0</v>
@@ -5372,16 +5416,16 @@
         <v>63</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D65" s="2">
         <v>7</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>11</v>
@@ -5396,13 +5440,13 @@
         <v>46</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>426</v>
+        <v>395</v>
       </c>
       <c r="L65" s="3" t="s">
-        <v>350</v>
+        <v>329</v>
       </c>
       <c r="M65" s="8">
         <v>0</v>
@@ -5416,16 +5460,16 @@
         <v>64</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>518</v>
+        <v>485</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>537</v>
+        <v>504</v>
       </c>
       <c r="D66" s="2">
         <v>8</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>519</v>
+        <v>486</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>11</v>
@@ -5440,13 +5484,13 @@
         <v>7</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>601</v>
+        <v>562</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>602</v>
+        <v>563</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>603</v>
+        <v>564</v>
       </c>
       <c r="M66" s="8">
         <v>0</v>
@@ -5463,13 +5507,13 @@
         <v>34</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="D67" s="2">
         <v>4</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>11</v>
@@ -5484,13 +5528,13 @@
         <v>35</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>427</v>
+        <v>396</v>
       </c>
       <c r="L67" s="3" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="M67" s="8">
         <v>0</v>
@@ -5504,16 +5548,16 @@
         <v>66</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D68" s="2">
         <v>3</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>11</v>
@@ -5528,13 +5572,13 @@
         <v>10</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>279</v>
+        <v>262</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L68" s="3" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
       <c r="M68" s="8">
         <v>0</v>
@@ -5548,16 +5592,16 @@
         <v>67</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="D69" s="2">
         <v>4</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>11</v>
@@ -5572,13 +5616,13 @@
         <v>20</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>429</v>
+        <v>398</v>
       </c>
       <c r="L69" s="3" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="M69" s="8">
         <v>0</v>
@@ -5592,16 +5636,16 @@
         <v>68</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="D70" s="2">
         <v>1</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>11</v>
@@ -5616,13 +5660,13 @@
         <v>49</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>430</v>
+        <v>399</v>
       </c>
       <c r="L70" s="3" t="s">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="M70" s="8">
         <v>0</v>
@@ -5636,16 +5680,16 @@
         <v>69</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D71" s="2">
         <v>6</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>11</v>
@@ -5660,13 +5704,13 @@
         <v>2</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>431</v>
+        <v>400</v>
       </c>
       <c r="L71" s="3" t="s">
-        <v>342</v>
+        <v>322</v>
       </c>
       <c r="M71" s="8">
         <v>0</v>
@@ -5680,16 +5724,16 @@
         <v>70</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>486</v>
+        <v>454</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="D72" s="2">
         <v>8</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>487</v>
+        <v>455</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>11</v>
@@ -5704,13 +5748,13 @@
         <v>55</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>562</v>
+        <v>526</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>563</v>
+        <v>527</v>
       </c>
       <c r="L72" s="3" t="s">
-        <v>564</v>
+        <v>528</v>
       </c>
       <c r="M72" s="8">
         <v>0</v>
@@ -5724,16 +5768,16 @@
         <v>71</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="D73" s="2">
         <v>6</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>11</v>
@@ -5748,13 +5792,13 @@
         <v>6</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>274</v>
+        <v>257</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>432</v>
+        <v>401</v>
       </c>
       <c r="L73" s="3" t="s">
-        <v>368</v>
+        <v>344</v>
       </c>
       <c r="M73" s="8">
         <v>0</v>
@@ -5768,16 +5812,16 @@
         <v>72</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D74" s="2">
         <v>7</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>11</v>
@@ -5792,13 +5836,13 @@
         <v>9</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>433</v>
+        <v>402</v>
       </c>
       <c r="L74" s="3" t="s">
-        <v>345</v>
+        <v>324</v>
       </c>
       <c r="M74" s="8">
         <v>0</v>
@@ -5812,16 +5856,16 @@
         <v>73</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D75" s="2">
         <v>5</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>11</v>
@@ -5836,13 +5880,13 @@
         <v>1</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>434</v>
+        <v>403</v>
       </c>
       <c r="L75" s="3" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
       <c r="M75" s="8">
         <v>0</v>
@@ -5856,16 +5900,16 @@
         <v>74</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D76" s="2">
         <v>4</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>11</v>
@@ -5880,13 +5924,13 @@
         <v>41</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>435</v>
+        <v>404</v>
       </c>
       <c r="L76" s="3" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="M76" s="8">
         <v>0</v>
@@ -5900,16 +5944,16 @@
         <v>75</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="D77" s="2">
         <v>2</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>11</v>
@@ -5924,13 +5968,13 @@
         <v>49</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>436</v>
+        <v>405</v>
       </c>
       <c r="L77" s="3" t="s">
-        <v>302</v>
+        <v>285</v>
       </c>
       <c r="M77" s="8">
         <v>0</v>
@@ -5944,16 +5988,16 @@
         <v>76</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>513</v>
+        <v>480</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>534</v>
+        <v>501</v>
       </c>
       <c r="D78" s="2">
         <v>3</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>514</v>
+        <v>481</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>11</v>
@@ -5968,13 +6012,13 @@
         <v>99</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>592</v>
+        <v>553</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>593</v>
+        <v>554</v>
       </c>
       <c r="L78" s="3" t="s">
-        <v>594</v>
+        <v>555</v>
       </c>
       <c r="M78" s="8">
         <v>0</v>
@@ -5988,16 +6032,16 @@
         <v>77</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>474</v>
+        <v>443</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>493</v>
+        <v>461</v>
       </c>
       <c r="D79" s="2">
         <v>2</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>475</v>
+        <v>444</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>11</v>
@@ -6012,13 +6056,13 @@
         <v>42</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>546</v>
+        <v>512</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>547</v>
+        <v>513</v>
       </c>
       <c r="L79" s="3" t="s">
-        <v>548</v>
+        <v>514</v>
       </c>
       <c r="M79" s="8">
         <v>0</v>
@@ -6032,16 +6076,16 @@
         <v>78</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D80" s="2">
         <v>3</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>11</v>
@@ -6056,13 +6100,13 @@
         <v>40</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>437</v>
+        <v>406</v>
       </c>
       <c r="L80" s="3" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="M80" s="8">
         <v>0</v>
@@ -6076,16 +6120,16 @@
         <v>79</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D81" s="2">
         <v>2</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>11</v>
@@ -6100,13 +6144,13 @@
         <v>9</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>438</v>
+        <v>407</v>
       </c>
       <c r="L81" s="3" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
       <c r="M81" s="8">
         <v>0</v>
@@ -6120,16 +6164,16 @@
         <v>80</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D82" s="2">
         <v>5</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>11</v>
@@ -6144,13 +6188,13 @@
         <v>26</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>439</v>
+        <v>408</v>
       </c>
       <c r="L82" s="3" t="s">
-        <v>304</v>
+        <v>287</v>
       </c>
       <c r="M82" s="8">
         <v>0</v>
@@ -6164,16 +6208,16 @@
         <v>81</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="D83" s="2">
         <v>6</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>11</v>
@@ -6188,13 +6232,13 @@
         <v>41</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>440</v>
+        <v>409</v>
       </c>
       <c r="L83" s="3" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="M83" s="8">
         <v>0</v>
@@ -6208,16 +6252,16 @@
         <v>82</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D84" s="2">
         <v>8</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>11</v>
@@ -6232,13 +6276,13 @@
         <v>39</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="K84" s="3" t="s">
-        <v>441</v>
+        <v>410</v>
       </c>
       <c r="L84" s="3" t="s">
-        <v>308</v>
+        <v>291</v>
       </c>
       <c r="M84" s="8">
         <v>0</v>
@@ -6252,16 +6296,16 @@
         <v>83</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D85" s="2">
         <v>1</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>11</v>
@@ -6276,13 +6320,13 @@
         <v>4</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>442</v>
+        <v>411</v>
       </c>
       <c r="L85" s="3" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="M85" s="8">
         <v>0</v>
@@ -6296,16 +6340,16 @@
         <v>84</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D86" s="2">
         <v>9</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>11</v>
@@ -6320,13 +6364,13 @@
         <v>14</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="K86" s="3" t="s">
-        <v>443</v>
+        <v>412</v>
       </c>
       <c r="L86" s="3" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="M86" s="8">
         <v>0</v>
@@ -6340,16 +6384,16 @@
         <v>85</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D87" s="2">
         <v>6</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>11</v>
@@ -6364,13 +6408,13 @@
         <v>45</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="K87" s="3" t="s">
-        <v>444</v>
+        <v>413</v>
       </c>
       <c r="L87" s="3" t="s">
-        <v>314</v>
+        <v>297</v>
       </c>
       <c r="M87" s="8">
         <v>0</v>
@@ -6384,16 +6428,16 @@
         <v>86</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>518</v>
+        <v>485</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>531</v>
+        <v>498</v>
       </c>
       <c r="D88" s="2">
         <v>8</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>527</v>
+        <v>494</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>11</v>
@@ -6408,13 +6452,13 @@
         <v>83</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>655</v>
+        <v>613</v>
       </c>
       <c r="K88" s="3" t="s">
-        <v>656</v>
+        <v>614</v>
       </c>
       <c r="L88" s="3" t="s">
-        <v>657</v>
+        <v>615</v>
       </c>
       <c r="M88" s="8">
         <v>0</v>
@@ -6428,16 +6472,16 @@
         <v>87</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>509</v>
+        <v>476</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>529</v>
+        <v>496</v>
       </c>
       <c r="D89" s="2">
         <v>5</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>510</v>
+        <v>477</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>11</v>
@@ -6452,13 +6496,13 @@
         <v>69</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>613</v>
+        <v>574</v>
       </c>
       <c r="K89" s="3" t="s">
-        <v>614</v>
+        <v>575</v>
       </c>
       <c r="L89" s="3" t="s">
-        <v>615</v>
+        <v>576</v>
       </c>
       <c r="M89" s="8">
         <v>0</v>
@@ -6472,16 +6516,16 @@
         <v>88</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>521</v>
+        <v>488</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>537</v>
+        <v>504</v>
       </c>
       <c r="D90" s="2">
         <v>6</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>505</v>
+        <v>472</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>11</v>
@@ -6496,13 +6540,13 @@
         <v>38</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>607</v>
+        <v>568</v>
       </c>
       <c r="K90" s="3" t="s">
-        <v>608</v>
+        <v>569</v>
       </c>
       <c r="L90" s="3" t="s">
-        <v>609</v>
+        <v>570</v>
       </c>
       <c r="M90" s="8">
         <v>0</v>
@@ -6516,16 +6560,16 @@
         <v>89</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>522</v>
+        <v>489</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>535</v>
+        <v>502</v>
       </c>
       <c r="D91" s="2">
         <v>2</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>11</v>
@@ -6540,13 +6584,13 @@
         <v>53</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>619</v>
+        <v>580</v>
       </c>
       <c r="K91" s="3" t="s">
-        <v>620</v>
+        <v>581</v>
       </c>
       <c r="L91" s="3" t="s">
-        <v>621</v>
+        <v>582</v>
       </c>
       <c r="M91" s="8">
         <v>0</v>
@@ -6560,16 +6604,16 @@
         <v>90</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D92" s="2">
         <v>6</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>11</v>
@@ -6584,13 +6628,13 @@
         <v>4</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="K92" s="3" t="s">
-        <v>445</v>
+        <v>414</v>
       </c>
       <c r="L92" s="3" t="s">
-        <v>291</v>
+        <v>274</v>
       </c>
       <c r="M92" s="8">
         <v>0</v>
@@ -6604,16 +6648,16 @@
         <v>91</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>509</v>
+        <v>476</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>533</v>
+        <v>500</v>
       </c>
       <c r="D93" s="2">
         <v>4</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>510</v>
+        <v>477</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>11</v>
@@ -6628,13 +6672,13 @@
         <v>43</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>586</v>
+        <v>547</v>
       </c>
       <c r="K93" s="3" t="s">
-        <v>587</v>
+        <v>548</v>
       </c>
       <c r="L93" s="3" t="s">
-        <v>588</v>
+        <v>549</v>
       </c>
       <c r="M93" s="8">
         <v>0</v>
@@ -6648,16 +6692,16 @@
         <v>92</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D94" s="2">
         <v>1</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>11</v>
@@ -6672,13 +6716,13 @@
         <v>47</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="K94" s="3" t="s">
-        <v>446</v>
+        <v>415</v>
       </c>
       <c r="L94" s="3" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="M94" s="8">
         <v>0</v>
@@ -6692,16 +6736,16 @@
         <v>93</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D95" s="2">
         <v>3</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>11</v>
@@ -6716,13 +6760,13 @@
         <v>21</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="K95" s="3" t="s">
-        <v>447</v>
+        <v>416</v>
       </c>
       <c r="L95" s="3" t="s">
-        <v>305</v>
+        <v>288</v>
       </c>
       <c r="M95" s="8">
         <v>0</v>
@@ -6736,16 +6780,16 @@
         <v>94</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="D96" s="2">
         <v>3</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>11</v>
@@ -6760,13 +6804,13 @@
         <v>2</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="K96" s="3" t="s">
-        <v>448</v>
+        <v>417</v>
       </c>
       <c r="L96" s="3" t="s">
-        <v>290</v>
+        <v>273</v>
       </c>
       <c r="M96" s="8">
         <v>0</v>
@@ -6780,16 +6824,16 @@
         <v>95</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D97" s="2">
         <v>8</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>11</v>
@@ -6804,13 +6848,13 @@
         <v>40</v>
       </c>
       <c r="J97" s="3" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="K97" s="3" t="s">
-        <v>449</v>
+        <v>418</v>
       </c>
       <c r="L97" s="3" t="s">
-        <v>313</v>
+        <v>296</v>
       </c>
       <c r="M97" s="8">
         <v>0</v>
@@ -6824,16 +6868,16 @@
         <v>96</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="D98" s="2">
         <v>6</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>11</v>
@@ -6848,13 +6892,13 @@
         <v>21</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="K98" s="3" t="s">
-        <v>450</v>
+        <v>419</v>
       </c>
       <c r="L98" s="3" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="M98" s="8">
         <v>0</v>
@@ -6868,16 +6912,16 @@
         <v>97</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>490</v>
+        <v>458</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="D99" s="2">
         <v>6</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>491</v>
+        <v>459</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>11</v>
@@ -6892,13 +6936,13 @@
         <v>90</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>568</v>
+        <v>532</v>
       </c>
       <c r="K99" s="3" t="s">
-        <v>569</v>
+        <v>533</v>
       </c>
       <c r="L99" s="3" t="s">
-        <v>570</v>
+        <v>534</v>
       </c>
       <c r="M99" s="8">
         <v>0</v>
@@ -6909,16 +6953,16 @@
         <v>98</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>532</v>
+        <v>499</v>
       </c>
       <c r="D100" s="2">
         <v>4</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>512</v>
+        <v>479</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>11</v>
@@ -6933,13 +6977,13 @@
         <v>79</v>
       </c>
       <c r="J100" s="3" t="s">
-        <v>640</v>
+        <v>598</v>
       </c>
       <c r="K100" s="3" t="s">
-        <v>641</v>
+        <v>599</v>
       </c>
       <c r="L100" s="3" t="s">
-        <v>642</v>
+        <v>600</v>
       </c>
       <c r="M100" s="8">
         <v>0</v>
@@ -6950,16 +6994,16 @@
         <v>99</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>522</v>
+        <v>489</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>542</v>
+        <v>508</v>
       </c>
       <c r="D101" s="2">
         <v>1</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>525</v>
+        <v>492</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>11</v>
@@ -6974,13 +7018,13 @@
         <v>65</v>
       </c>
       <c r="J101" s="3" t="s">
-        <v>643</v>
+        <v>601</v>
       </c>
       <c r="K101" s="3" t="s">
-        <v>644</v>
+        <v>602</v>
       </c>
       <c r="L101" s="3" t="s">
-        <v>645</v>
+        <v>603</v>
       </c>
       <c r="M101" s="8">
         <v>0</v>
@@ -6991,16 +7035,16 @@
         <v>100</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>516</v>
+        <v>483</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>531</v>
+        <v>498</v>
       </c>
       <c r="D102" s="2">
         <v>3</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>515</v>
+        <v>482</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>11</v>
@@ -7015,13 +7059,13 @@
         <v>89</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>610</v>
+        <v>571</v>
       </c>
       <c r="K102" s="3" t="s">
-        <v>611</v>
+        <v>572</v>
       </c>
       <c r="L102" s="3" t="s">
-        <v>612</v>
+        <v>573</v>
       </c>
       <c r="M102" s="8">
         <v>0</v>
@@ -7032,16 +7076,16 @@
         <v>101</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>530</v>
+        <v>497</v>
       </c>
       <c r="D103" s="2">
         <v>1</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>11</v>
@@ -7056,13 +7100,13 @@
         <v>30</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>577</v>
+        <v>541</v>
       </c>
       <c r="K103" s="3" t="s">
-        <v>578</v>
+        <v>542</v>
       </c>
       <c r="L103" s="3" t="s">
-        <v>579</v>
+        <v>543</v>
       </c>
       <c r="M103" s="8">
         <v>0</v>
@@ -7073,16 +7117,16 @@
         <v>102</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>508</v>
+        <v>475</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>531</v>
+        <v>498</v>
       </c>
       <c r="D104" s="2">
         <v>3</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>11</v>
@@ -7097,13 +7141,13 @@
         <v>74</v>
       </c>
       <c r="J104" s="3" t="s">
-        <v>580</v>
+        <v>544</v>
       </c>
       <c r="K104" s="3" t="s">
-        <v>581</v>
+        <v>545</v>
       </c>
       <c r="L104" s="3" t="s">
-        <v>582</v>
+        <v>546</v>
       </c>
       <c r="M104" s="8">
         <v>0</v>
@@ -7114,16 +7158,16 @@
         <v>103</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D105" s="2">
         <v>4</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>11</v>
@@ -7138,13 +7182,13 @@
         <v>31</v>
       </c>
       <c r="J105" s="3" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="K105" s="3" t="s">
-        <v>451</v>
+        <v>420</v>
       </c>
       <c r="L105" s="3" t="s">
-        <v>319</v>
+        <v>302</v>
       </c>
       <c r="M105" s="8">
         <v>0</v>
@@ -7155,16 +7199,16 @@
         <v>104</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D106" s="2">
         <v>3</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>11</v>
@@ -7179,13 +7223,13 @@
         <v>11</v>
       </c>
       <c r="J106" s="3" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="K106" s="3" t="s">
-        <v>452</v>
+        <v>421</v>
       </c>
       <c r="L106" s="3" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="M106" s="8">
         <v>0</v>
@@ -7196,16 +7240,16 @@
         <v>105</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>516</v>
+        <v>483</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>536</v>
+        <v>503</v>
       </c>
       <c r="D107" s="2">
         <v>3</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>517</v>
+        <v>484</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>11</v>
@@ -7220,13 +7264,13 @@
         <v>98</v>
       </c>
       <c r="J107" s="3" t="s">
-        <v>598</v>
+        <v>559</v>
       </c>
       <c r="K107" s="3" t="s">
-        <v>599</v>
+        <v>560</v>
       </c>
       <c r="L107" s="3" t="s">
-        <v>600</v>
+        <v>561</v>
       </c>
       <c r="M107" s="8">
         <v>0</v>
@@ -7237,16 +7281,16 @@
         <v>106</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D108" s="2">
         <v>8</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>11</v>
@@ -7261,13 +7305,13 @@
         <v>11</v>
       </c>
       <c r="J108" s="3" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="K108" s="3" t="s">
-        <v>453</v>
+        <v>422</v>
       </c>
       <c r="L108" s="3" t="s">
-        <v>301</v>
+        <v>284</v>
       </c>
       <c r="M108" s="8">
         <v>0</v>
@@ -7278,16 +7322,16 @@
         <v>107</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>522</v>
+        <v>489</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>543</v>
+        <v>509</v>
       </c>
       <c r="D109" s="2">
         <v>1</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>510</v>
+        <v>477</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>11</v>
@@ -7302,13 +7346,13 @@
         <v>32</v>
       </c>
       <c r="J109" s="3" t="s">
-        <v>646</v>
+        <v>604</v>
       </c>
       <c r="K109" s="3" t="s">
-        <v>647</v>
+        <v>605</v>
       </c>
       <c r="L109" s="3" t="s">
-        <v>648</v>
+        <v>606</v>
       </c>
       <c r="M109" s="8">
         <v>0</v>
@@ -7319,16 +7363,16 @@
         <v>108</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D110" s="2">
         <v>7</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>11</v>
@@ -7343,13 +7387,13 @@
         <v>4</v>
       </c>
       <c r="J110" s="3" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="K110" s="3" t="s">
-        <v>454</v>
+        <v>423</v>
       </c>
       <c r="L110" s="3" t="s">
-        <v>311</v>
+        <v>294</v>
       </c>
       <c r="M110" s="8">
         <v>0</v>
@@ -7360,16 +7404,16 @@
         <v>109</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D111" s="2">
         <v>7</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>11</v>
@@ -7384,13 +7428,13 @@
         <v>46</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="K111" s="3" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="L111" s="3" t="s">
-        <v>317</v>
+        <v>300</v>
       </c>
       <c r="M111" s="8">
         <v>0</v>
@@ -7401,16 +7445,16 @@
         <v>110</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>511</v>
+        <v>478</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>533</v>
+        <v>500</v>
       </c>
       <c r="D112" s="2">
         <v>9</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>512</v>
+        <v>479</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>11</v>
@@ -7425,13 +7469,13 @@
         <v>37</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>589</v>
+        <v>550</v>
       </c>
       <c r="K112" s="3" t="s">
-        <v>590</v>
+        <v>551</v>
       </c>
       <c r="L112" s="3" t="s">
-        <v>591</v>
+        <v>552</v>
       </c>
       <c r="M112" s="8">
         <v>0</v>
@@ -7442,16 +7486,16 @@
         <v>111</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="D113" s="2">
         <v>2</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>11</v>
@@ -7466,13 +7510,13 @@
         <v>22</v>
       </c>
       <c r="J113" s="3" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="K113" s="3" t="s">
-        <v>456</v>
+        <v>425</v>
       </c>
       <c r="L113" s="3" t="s">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="M113" s="8">
         <v>0</v>
@@ -7483,16 +7527,16 @@
         <v>112</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D114" s="2">
         <v>1</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>11</v>
@@ -7507,13 +7551,13 @@
         <v>12</v>
       </c>
       <c r="J114" s="3" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="K114" s="3" t="s">
-        <v>457</v>
+        <v>426</v>
       </c>
       <c r="L114" s="3" t="s">
-        <v>321</v>
+        <v>304</v>
       </c>
       <c r="M114" s="8">
         <v>0</v>
@@ -7524,16 +7568,16 @@
         <v>113</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D115" s="2">
         <v>3</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>11</v>
@@ -7548,13 +7592,13 @@
         <v>17</v>
       </c>
       <c r="J115" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="K115" s="3" t="s">
-        <v>458</v>
+        <v>427</v>
       </c>
       <c r="L115" s="3" t="s">
-        <v>307</v>
+        <v>290</v>
       </c>
       <c r="M115" s="8">
         <v>0</v>
@@ -7565,16 +7609,16 @@
         <v>114</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>511</v>
+        <v>478</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>535</v>
+        <v>502</v>
       </c>
       <c r="D116" s="2">
         <v>2</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>520</v>
+        <v>487</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>11</v>
@@ -7589,13 +7633,13 @@
         <v>49</v>
       </c>
       <c r="J116" s="3" t="s">
-        <v>604</v>
+        <v>565</v>
       </c>
       <c r="K116" s="3" t="s">
-        <v>605</v>
+        <v>566</v>
       </c>
       <c r="L116" s="3" t="s">
-        <v>606</v>
+        <v>567</v>
       </c>
       <c r="M116" s="8">
         <v>0</v>
@@ -7606,16 +7650,16 @@
         <v>115</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>522</v>
+        <v>489</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>539</v>
+        <v>505</v>
       </c>
       <c r="D117" s="2">
         <v>1</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>514</v>
+        <v>481</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>11</v>
@@ -7630,13 +7674,13 @@
         <v>45</v>
       </c>
       <c r="J117" s="3" t="s">
-        <v>628</v>
+        <v>586</v>
       </c>
       <c r="K117" s="3" t="s">
-        <v>629</v>
+        <v>587</v>
       </c>
       <c r="L117" s="3" t="s">
-        <v>630</v>
+        <v>588</v>
       </c>
       <c r="M117" s="8">
         <v>0</v>
@@ -7647,16 +7691,16 @@
         <v>116</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D118" s="2">
         <v>1</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>11</v>
@@ -7671,13 +7715,13 @@
         <v>12</v>
       </c>
       <c r="J118" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K118" s="3" t="s">
-        <v>459</v>
+        <v>428</v>
       </c>
       <c r="L118" s="3" t="s">
-        <v>318</v>
+        <v>301</v>
       </c>
       <c r="M118" s="8">
         <v>0</v>
@@ -7688,16 +7732,16 @@
         <v>117</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D119" s="2">
         <v>5</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>11</v>
@@ -7712,13 +7756,13 @@
         <v>24</v>
       </c>
       <c r="J119" s="3" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="K119" s="3" t="s">
-        <v>460</v>
+        <v>429</v>
       </c>
       <c r="L119" s="3" t="s">
-        <v>320</v>
+        <v>303</v>
       </c>
       <c r="M119" s="8">
         <v>0</v>
@@ -7729,16 +7773,16 @@
         <v>118</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D120" s="2">
         <v>7</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>11</v>
@@ -7753,13 +7797,13 @@
         <v>21</v>
       </c>
       <c r="J120" s="3" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="K120" s="3" t="s">
-        <v>461</v>
+        <v>430</v>
       </c>
       <c r="L120" s="3" t="s">
-        <v>315</v>
+        <v>298</v>
       </c>
       <c r="M120" s="8">
         <v>0</v>
@@ -7770,16 +7814,16 @@
         <v>119</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>509</v>
+        <v>476</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>537</v>
+        <v>504</v>
       </c>
       <c r="D121" s="2">
         <v>4</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>520</v>
+        <v>487</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>11</v>
@@ -7794,13 +7838,13 @@
         <v>62</v>
       </c>
       <c r="J121" s="3" t="s">
-        <v>625</v>
+        <v>583</v>
       </c>
       <c r="K121" s="3" t="s">
-        <v>626</v>
+        <v>584</v>
       </c>
       <c r="L121" s="3" t="s">
-        <v>627</v>
+        <v>585</v>
       </c>
       <c r="M121" s="8">
         <v>0</v>
@@ -7811,16 +7855,16 @@
         <v>120</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>528</v>
+        <v>495</v>
       </c>
       <c r="D122" s="2">
         <v>8</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>11</v>
@@ -7835,13 +7879,13 @@
         <v>30</v>
       </c>
       <c r="J122" s="3" t="s">
-        <v>571</v>
+        <v>535</v>
       </c>
       <c r="K122" s="3" t="s">
-        <v>572</v>
+        <v>536</v>
       </c>
       <c r="L122" s="3" t="s">
-        <v>573</v>
+        <v>537</v>
       </c>
       <c r="M122" s="8">
         <v>0</v>
@@ -7852,16 +7896,16 @@
         <v>121</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>508</v>
+        <v>475</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>535</v>
+        <v>502</v>
       </c>
       <c r="D123" s="2">
         <v>2</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>515</v>
+        <v>482</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>11</v>
@@ -7876,13 +7920,13 @@
         <v>82</v>
       </c>
       <c r="J123" s="3" t="s">
-        <v>595</v>
+        <v>556</v>
       </c>
       <c r="K123" s="3" t="s">
-        <v>596</v>
+        <v>557</v>
       </c>
       <c r="L123" s="3" t="s">
-        <v>597</v>
+        <v>558</v>
       </c>
       <c r="M123" s="8">
         <v>0</v>
@@ -7893,16 +7937,16 @@
         <v>122</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D124" s="2">
         <v>2</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>11</v>
@@ -7917,13 +7961,13 @@
         <v>40</v>
       </c>
       <c r="J124" s="3" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="K124" s="3" t="s">
-        <v>462</v>
+        <v>431</v>
       </c>
       <c r="L124" s="3" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="M124" s="8">
         <v>0</v>
@@ -7934,16 +7978,16 @@
         <v>123</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D125" s="2">
         <v>9</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>11</v>
@@ -7958,13 +8002,13 @@
         <v>20</v>
       </c>
       <c r="J125" s="3" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="K125" s="3" t="s">
-        <v>463</v>
+        <v>432</v>
       </c>
       <c r="L125" s="3" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="M125" s="8">
         <v>0</v>
@@ -7975,16 +8019,16 @@
         <v>124</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D126" s="2">
         <v>4</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>11</v>
@@ -7999,13 +8043,13 @@
         <v>49</v>
       </c>
       <c r="J126" s="3" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="K126" s="3" t="s">
-        <v>464</v>
+        <v>433</v>
       </c>
       <c r="L126" s="3" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="M126" s="8">
         <v>0</v>
@@ -8016,16 +8060,16 @@
         <v>125</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>516</v>
+        <v>483</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>536</v>
+        <v>503</v>
       </c>
       <c r="D127" s="2">
         <v>3</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>11</v>
@@ -8040,13 +8084,13 @@
         <v>18</v>
       </c>
       <c r="J127" s="3" t="s">
-        <v>652</v>
+        <v>610</v>
       </c>
       <c r="K127" s="3" t="s">
-        <v>653</v>
+        <v>611</v>
       </c>
       <c r="L127" s="3" t="s">
-        <v>654</v>
+        <v>612</v>
       </c>
       <c r="M127" s="8">
         <v>0</v>
@@ -8057,16 +8101,16 @@
         <v>126</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D128" s="2">
         <v>3</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>11</v>
@@ -8081,13 +8125,13 @@
         <v>39</v>
       </c>
       <c r="J128" s="3" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="K128" s="3" t="s">
-        <v>465</v>
+        <v>434</v>
       </c>
       <c r="L128" s="3" t="s">
-        <v>316</v>
+        <v>299</v>
       </c>
       <c r="M128" s="8">
         <v>0</v>
@@ -8098,16 +8142,16 @@
         <v>127</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="D129" s="2">
         <v>1</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>11</v>
@@ -8122,13 +8166,13 @@
         <v>16</v>
       </c>
       <c r="J129" s="3" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="K129" s="3" t="s">
-        <v>466</v>
+        <v>435</v>
       </c>
       <c r="L129" s="3" t="s">
-        <v>323</v>
+        <v>306</v>
       </c>
       <c r="M129" s="8">
         <v>0</v>
@@ -8139,16 +8183,16 @@
         <v>128</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>513</v>
+        <v>480</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>540</v>
+        <v>506</v>
       </c>
       <c r="D130" s="2">
         <v>7</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>517</v>
+        <v>484</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>11</v>
@@ -8163,13 +8207,13 @@
         <v>56</v>
       </c>
       <c r="J130" s="3" t="s">
-        <v>631</v>
+        <v>589</v>
       </c>
       <c r="K130" s="3" t="s">
-        <v>632</v>
+        <v>590</v>
       </c>
       <c r="L130" s="3" t="s">
-        <v>633</v>
+        <v>591</v>
       </c>
       <c r="M130" s="8">
         <v>0</v>
@@ -8180,16 +8224,16 @@
         <v>129</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D131" s="2">
         <v>4</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>11</v>
@@ -8204,13 +8248,13 @@
         <v>12</v>
       </c>
       <c r="J131" s="3" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="K131" s="3" t="s">
-        <v>467</v>
+        <v>436</v>
       </c>
       <c r="L131" s="3" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="M131" s="8">
         <v>0</v>
@@ -8221,16 +8265,16 @@
         <v>130</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="D132" s="2">
         <v>8</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>11</v>
@@ -8245,13 +8289,13 @@
         <v>13</v>
       </c>
       <c r="J132" s="3" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="K132" s="3" t="s">
-        <v>468</v>
+        <v>437</v>
       </c>
       <c r="L132" s="3" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="M132" s="8">
         <v>0</v>
@@ -8262,16 +8306,16 @@
         <v>131</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D133" s="2">
         <v>3</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>11</v>
@@ -8286,13 +8330,13 @@
         <v>48</v>
       </c>
       <c r="J133" s="3" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="K133" s="3" t="s">
-        <v>469</v>
+        <v>438</v>
       </c>
       <c r="L133" s="3" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
       <c r="M133" s="8">
         <v>0</v>
@@ -8303,16 +8347,16 @@
         <v>132</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="D134" s="2">
         <v>7</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>11</v>
@@ -8327,13 +8371,13 @@
         <v>32</v>
       </c>
       <c r="J134" s="3" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="K134" s="3" t="s">
-        <v>470</v>
+        <v>439</v>
       </c>
       <c r="L134" s="3" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
       <c r="M134" s="8">
         <v>0</v>
@@ -8344,16 +8388,16 @@
         <v>133</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D135" s="2">
         <v>3</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>11</v>
@@ -8368,13 +8412,13 @@
         <v>2</v>
       </c>
       <c r="J135" s="3" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="K135" s="3" t="s">
-        <v>471</v>
+        <v>440</v>
       </c>
       <c r="L135" s="3" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="M135" s="8">
         <v>0</v>
@@ -8566,4 +8610,136 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55C6109F-48BB-4C16-92DE-F0286B802B61}">
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>619</v>
+      </c>
+      <c r="C2" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>621</v>
+      </c>
+      <c r="C3" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>623</v>
+      </c>
+      <c r="C4" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>625</v>
+      </c>
+      <c r="C5" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>627</v>
+      </c>
+      <c r="C6" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>629</v>
+      </c>
+      <c r="C7" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>631</v>
+      </c>
+      <c r="C8" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>633</v>
+      </c>
+      <c r="C9" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>635</v>
+      </c>
+      <c r="C10" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>637</v>
+      </c>
+      <c r="C11" t="s">
+        <v>638</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Confidential\Gathering_Island\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A08EF74-25C2-4BFA-9CC9-9438294711E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7950B90F-36BE-404B-B3E8-DE06B43B21F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-18255" yWindow="2790" windowWidth="19725" windowHeight="10830" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28350" yWindow="4080" windowWidth="19725" windowHeight="10830" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="events" sheetId="1" r:id="rId1"/>
     <sheet name="工作表1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">events!$A$1:$M$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">events!$A$1:$M$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
     <author>Romi</author>
   </authors>
   <commentList>
-    <comment ref="M2" authorId="0" shapeId="0" xr:uid="{17581C10-74D2-4259-AA8B-254741E2EF5B}">
+    <comment ref="J2" authorId="0" shapeId="0" xr:uid="{17581C10-74D2-4259-AA8B-254741E2EF5B}">
       <text>
         <r>
           <rPr>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1115" uniqueCount="677">
   <si>
     <t>event_id</t>
   </si>
@@ -2171,6 +2171,12 @@
   </si>
   <si>
     <t>2026-04-14 18:00:00</t>
+  </si>
+  <si>
+    <t>updated_at</t>
+  </si>
+  <si>
+    <t>最後更新資料時間</t>
   </si>
 </sst>
 </file>
@@ -2600,8 +2606,8 @@
     <col min="4" max="4" width="23.875" style="1" customWidth="1"/>
     <col min="5" max="5" width="40.625" style="1" customWidth="1"/>
     <col min="6" max="9" width="23.875" style="1" customWidth="1"/>
-    <col min="10" max="13" width="28.625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="1"/>
+    <col min="10" max="14" width="28.625" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
@@ -2633,16 +2639,19 @@
         <v>23</v>
       </c>
       <c r="J1" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="K1" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="L1" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="M1" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="M1" s="11" t="s">
-        <v>118</v>
+      <c r="N1" s="11" t="s">
+        <v>676</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
@@ -2674,16 +2683,19 @@
         <v>7</v>
       </c>
       <c r="J2" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="K2" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="L2" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="M2" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="M2" s="10" t="s">
-        <v>117</v>
+      <c r="N2" s="10" t="s">
+        <v>675</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
@@ -2714,19 +2726,21 @@
       <c r="I3" s="2">
         <v>78</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="8">
+        <v>0</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>645</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>646</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>647</v>
       </c>
-      <c r="M3" s="8">
-        <v>0</v>
-      </c>
-      <c r="N3" s="13"/>
+      <c r="N3" s="3" t="s">
+        <v>647</v>
+      </c>
       <c r="O3" s="13"/>
       <c r="P3" s="13"/>
     </row>
@@ -2758,17 +2772,20 @@
       <c r="I4" s="2">
         <v>5</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="8">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>649</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="M4" s="3" t="s">
         <v>650</v>
       </c>
-      <c r="M4" s="8">
-        <v>0</v>
+      <c r="N4" s="3" t="s">
+        <v>650</v>
       </c>
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
@@ -2802,17 +2819,20 @@
       <c r="I5" s="2">
         <v>65</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" s="8">
+        <v>0</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>651</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="L5" s="3" t="s">
         <v>652</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="M5" s="3" t="s">
         <v>653</v>
       </c>
-      <c r="M5" s="8">
-        <v>0</v>
+      <c r="N5" s="3" t="s">
+        <v>653</v>
       </c>
       <c r="O5" s="7"/>
       <c r="P5" s="7"/>
@@ -2846,17 +2866,20 @@
       <c r="I6" s="2">
         <v>2</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="J6" s="8">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3" t="s">
         <v>654</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="L6" s="3" t="s">
         <v>655</v>
       </c>
-      <c r="L6" s="3" t="s">
+      <c r="M6" s="3" t="s">
         <v>656</v>
       </c>
-      <c r="M6" s="8">
-        <v>0</v>
+      <c r="N6" s="3" t="s">
+        <v>656</v>
       </c>
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
@@ -2890,17 +2913,20 @@
       <c r="I7" s="2">
         <v>48</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="J7" s="8">
+        <v>0</v>
+      </c>
+      <c r="K7" s="3" t="s">
         <v>657</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="L7" s="3" t="s">
         <v>658</v>
       </c>
-      <c r="L7" s="3" t="s">
+      <c r="M7" s="3" t="s">
         <v>659</v>
       </c>
-      <c r="M7" s="8">
-        <v>0</v>
+      <c r="N7" s="3" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
@@ -2931,17 +2957,20 @@
       <c r="I8" s="2">
         <v>12</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="J8" s="8">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3" t="s">
         <v>660</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="L8" s="3" t="s">
         <v>661</v>
       </c>
-      <c r="L8" s="3" t="s">
+      <c r="M8" s="3" t="s">
         <v>662</v>
       </c>
-      <c r="M8" s="8">
-        <v>0</v>
+      <c r="N8" s="3" t="s">
+        <v>662</v>
       </c>
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
@@ -2975,17 +3004,20 @@
       <c r="I9" s="2">
         <v>57</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="J9" s="8">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3" t="s">
         <v>663</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="L9" s="3" t="s">
         <v>664</v>
       </c>
-      <c r="L9" s="3" t="s">
+      <c r="M9" s="3" t="s">
         <v>665</v>
       </c>
-      <c r="M9" s="8">
-        <v>0</v>
+      <c r="N9" s="3" t="s">
+        <v>665</v>
       </c>
       <c r="O9" s="7"/>
       <c r="P9" s="7"/>
@@ -3019,17 +3051,20 @@
       <c r="I10" s="2">
         <v>20</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="J10" s="8">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3" t="s">
         <v>666</v>
       </c>
-      <c r="K10" s="3" t="s">
+      <c r="L10" s="3" t="s">
         <v>667</v>
       </c>
-      <c r="L10" s="3" t="s">
+      <c r="M10" s="3" t="s">
         <v>668</v>
       </c>
-      <c r="M10" s="8">
-        <v>0</v>
+      <c r="N10" s="3" t="s">
+        <v>668</v>
       </c>
       <c r="O10" s="7"/>
       <c r="P10" s="7"/>
@@ -3063,17 +3098,20 @@
       <c r="I11" s="2">
         <v>37</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="J11" s="8">
+        <v>0</v>
+      </c>
+      <c r="K11" s="3" t="s">
         <v>669</v>
       </c>
-      <c r="K11" s="3" t="s">
+      <c r="L11" s="3" t="s">
         <v>670</v>
       </c>
-      <c r="L11" s="3" t="s">
+      <c r="M11" s="3" t="s">
         <v>671</v>
       </c>
-      <c r="M11" s="8">
-        <v>0</v>
+      <c r="N11" s="3" t="s">
+        <v>671</v>
       </c>
       <c r="O11" s="7"/>
       <c r="P11" s="7"/>
@@ -3107,17 +3145,20 @@
       <c r="I12" s="2">
         <v>21</v>
       </c>
-      <c r="J12" s="3" t="s">
+      <c r="J12" s="8">
+        <v>0</v>
+      </c>
+      <c r="K12" s="3" t="s">
         <v>672</v>
       </c>
-      <c r="K12" s="3" t="s">
+      <c r="L12" s="3" t="s">
         <v>673</v>
       </c>
-      <c r="L12" s="3" t="s">
+      <c r="M12" s="3" t="s">
         <v>674</v>
       </c>
-      <c r="M12" s="8">
-        <v>0</v>
+      <c r="N12" s="3" t="s">
+        <v>674</v>
       </c>
       <c r="O12" s="7"/>
       <c r="P12" s="7"/>
@@ -3151,17 +3192,20 @@
       <c r="I13" s="2">
         <v>27</v>
       </c>
-      <c r="J13" s="3" t="s">
+      <c r="J13" s="8">
+        <v>1</v>
+      </c>
+      <c r="K13" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="K13" s="3" t="s">
+      <c r="L13" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="L13" s="3" t="s">
+      <c r="M13" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="M13" s="8">
-        <v>1</v>
+      <c r="N13" s="3" t="s">
+        <v>319</v>
       </c>
       <c r="O13" s="7"/>
       <c r="P13" s="7"/>
@@ -3195,17 +3239,20 @@
       <c r="I14" s="2">
         <v>16</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="J14" s="8">
+        <v>1</v>
+      </c>
+      <c r="K14" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="M14" s="8">
-        <v>1</v>
+      <c r="N14" s="3" t="s">
+        <v>320</v>
       </c>
       <c r="O14" s="7"/>
       <c r="P14" s="7"/>
@@ -3239,17 +3286,20 @@
       <c r="I15" s="2">
         <v>12</v>
       </c>
-      <c r="J15" s="3" t="s">
+      <c r="J15" s="8">
+        <v>1</v>
+      </c>
+      <c r="K15" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="K15" s="3" t="s">
+      <c r="L15" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="L15" s="3" t="s">
+      <c r="M15" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="M15" s="8">
-        <v>1</v>
+      <c r="N15" s="3" t="s">
+        <v>331</v>
       </c>
       <c r="O15" s="7"/>
       <c r="P15" s="7"/>
@@ -3283,17 +3333,20 @@
       <c r="I16" s="2">
         <v>12</v>
       </c>
-      <c r="J16" s="3" t="s">
+      <c r="J16" s="8">
+        <v>1</v>
+      </c>
+      <c r="K16" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="K16" s="3" t="s">
+      <c r="L16" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="L16" s="3" t="s">
+      <c r="M16" s="3" t="s">
         <v>525</v>
       </c>
-      <c r="M16" s="8">
-        <v>1</v>
+      <c r="N16" s="3" t="s">
+        <v>525</v>
       </c>
       <c r="O16" s="7"/>
       <c r="P16" s="7"/>
@@ -3327,17 +3380,20 @@
       <c r="I17" s="2">
         <v>75</v>
       </c>
-      <c r="J17" s="3" t="s">
+      <c r="J17" s="8">
+        <v>1</v>
+      </c>
+      <c r="K17" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="K17" s="3" t="s">
+      <c r="L17" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="L17" s="3" t="s">
+      <c r="M17" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="M17" s="8">
-        <v>1</v>
+      <c r="N17" s="3" t="s">
+        <v>540</v>
       </c>
       <c r="O17" s="7"/>
       <c r="P17" s="7"/>
@@ -3371,17 +3427,20 @@
       <c r="I18" s="2">
         <v>44</v>
       </c>
-      <c r="J18" s="3" t="s">
+      <c r="J18" s="8">
+        <v>1</v>
+      </c>
+      <c r="K18" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="K18" s="3" t="s">
+      <c r="L18" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="L18" s="3" t="s">
+      <c r="M18" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="M18" s="8">
-        <v>1</v>
+      <c r="N18" s="3" t="s">
+        <v>313</v>
       </c>
       <c r="O18" s="7"/>
       <c r="P18" s="7"/>
@@ -3415,17 +3474,20 @@
       <c r="I19" s="2">
         <v>20</v>
       </c>
-      <c r="J19" s="3" t="s">
+      <c r="J19" s="8">
+        <v>1</v>
+      </c>
+      <c r="K19" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="K19" s="3" t="s">
+      <c r="L19" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="L19" s="3" t="s">
+      <c r="M19" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="M19" s="8">
-        <v>1</v>
+      <c r="N19" s="3" t="s">
+        <v>312</v>
       </c>
       <c r="O19" s="7"/>
       <c r="P19" s="7"/>
@@ -3459,17 +3521,20 @@
       <c r="I20" s="2">
         <v>7</v>
       </c>
-      <c r="J20" s="3" t="s">
+      <c r="J20" s="8">
+        <v>1</v>
+      </c>
+      <c r="K20" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="K20" s="3" t="s">
+      <c r="L20" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="L20" s="3" t="s">
+      <c r="M20" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="M20" s="8">
-        <v>1</v>
+      <c r="N20" s="3" t="s">
+        <v>327</v>
       </c>
       <c r="O20" s="7"/>
       <c r="P20" s="7"/>
@@ -3503,17 +3568,20 @@
       <c r="I21" s="2">
         <v>49</v>
       </c>
-      <c r="J21" s="3" t="s">
+      <c r="J21" s="8">
+        <v>1</v>
+      </c>
+      <c r="K21" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="K21" s="3" t="s">
+      <c r="L21" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="L21" s="3" t="s">
+      <c r="M21" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="M21" s="8">
-        <v>1</v>
+      <c r="N21" s="3" t="s">
+        <v>321</v>
       </c>
       <c r="O21" s="7"/>
       <c r="P21" s="7"/>
@@ -3547,17 +3615,20 @@
       <c r="I22" s="2">
         <v>42</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="J22" s="8">
+        <v>1</v>
+      </c>
+      <c r="K22" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="K22" s="3" t="s">
+      <c r="L22" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="L22" s="3" t="s">
+      <c r="M22" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="M22" s="8">
-        <v>1</v>
+      <c r="N22" s="3" t="s">
+        <v>352</v>
       </c>
       <c r="O22" s="7"/>
       <c r="P22" s="7"/>
@@ -3591,17 +3662,20 @@
       <c r="I23" s="2">
         <v>19</v>
       </c>
-      <c r="J23" s="3" t="s">
+      <c r="J23" s="8">
+        <v>1</v>
+      </c>
+      <c r="K23" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="K23" s="3" t="s">
+      <c r="L23" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="L23" s="3" t="s">
+      <c r="M23" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="M23" s="8">
-        <v>1</v>
+      <c r="N23" s="3" t="s">
+        <v>311</v>
       </c>
       <c r="O23" s="7"/>
       <c r="P23" s="7"/>
@@ -3635,17 +3709,20 @@
       <c r="I24" s="2">
         <v>50</v>
       </c>
-      <c r="J24" s="3" t="s">
+      <c r="J24" s="8">
+        <v>1</v>
+      </c>
+      <c r="K24" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="K24" s="3" t="s">
+      <c r="L24" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="L24" s="3" t="s">
+      <c r="M24" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="M24" s="8">
-        <v>1</v>
+      <c r="N24" s="3" t="s">
+        <v>343</v>
       </c>
       <c r="O24" s="7"/>
       <c r="P24" s="7"/>
@@ -3679,17 +3756,20 @@
       <c r="I25" s="2">
         <v>7</v>
       </c>
-      <c r="J25" s="3" t="s">
+      <c r="J25" s="8">
+        <v>1</v>
+      </c>
+      <c r="K25" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="K25" s="3" t="s">
+      <c r="L25" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="L25" s="3" t="s">
+      <c r="M25" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="M25" s="8">
-        <v>1</v>
+      <c r="N25" s="3" t="s">
+        <v>348</v>
       </c>
       <c r="O25" s="7"/>
       <c r="P25" s="7"/>
@@ -3723,17 +3803,20 @@
       <c r="I26" s="2">
         <v>9</v>
       </c>
-      <c r="J26" s="3" t="s">
+      <c r="J26" s="8">
+        <v>1</v>
+      </c>
+      <c r="K26" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="K26" s="3" t="s">
+      <c r="L26" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="L26" s="3" t="s">
+      <c r="M26" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="M26" s="8">
-        <v>1</v>
+      <c r="N26" s="3" t="s">
+        <v>341</v>
       </c>
       <c r="O26" s="7"/>
       <c r="P26" s="7"/>
@@ -3767,17 +3850,20 @@
       <c r="I27" s="2">
         <v>29</v>
       </c>
-      <c r="J27" s="3" t="s">
+      <c r="J27" s="8">
+        <v>1</v>
+      </c>
+      <c r="K27" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="K27" s="3" t="s">
+      <c r="L27" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="L27" s="3" t="s">
+      <c r="M27" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="M27" s="8">
-        <v>1</v>
+      <c r="N27" s="3" t="s">
+        <v>337</v>
       </c>
       <c r="O27" s="7"/>
       <c r="P27" s="7"/>
@@ -3811,17 +3897,20 @@
       <c r="I28" s="2">
         <v>1</v>
       </c>
-      <c r="J28" s="3" t="s">
+      <c r="J28" s="8">
+        <v>1</v>
+      </c>
+      <c r="K28" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="K28" s="3" t="s">
+      <c r="L28" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="L28" s="3" t="s">
+      <c r="M28" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="M28" s="8">
-        <v>1</v>
+      <c r="N28" s="3" t="s">
+        <v>350</v>
       </c>
       <c r="O28" s="7"/>
       <c r="P28" s="7"/>
@@ -3855,17 +3944,20 @@
       <c r="I29" s="2">
         <v>14</v>
       </c>
-      <c r="J29" s="3" t="s">
+      <c r="J29" s="8">
+        <v>1</v>
+      </c>
+      <c r="K29" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="K29" s="3" t="s">
+      <c r="L29" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="L29" s="3" t="s">
+      <c r="M29" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="M29" s="8">
-        <v>1</v>
+      <c r="N29" s="3" t="s">
+        <v>323</v>
       </c>
       <c r="O29" s="7"/>
       <c r="P29" s="7"/>
@@ -3899,17 +3991,20 @@
       <c r="I30" s="2">
         <v>4</v>
       </c>
-      <c r="J30" s="3" t="s">
+      <c r="J30" s="8">
+        <v>1</v>
+      </c>
+      <c r="K30" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="K30" s="3" t="s">
+      <c r="L30" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="L30" s="3" t="s">
+      <c r="M30" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="M30" s="8">
-        <v>1</v>
+      <c r="N30" s="3" t="s">
+        <v>336</v>
       </c>
       <c r="O30" s="7"/>
       <c r="P30" s="7"/>
@@ -3943,17 +4038,20 @@
       <c r="I31" s="2">
         <v>40</v>
       </c>
-      <c r="J31" s="3" t="s">
+      <c r="J31" s="8">
+        <v>1</v>
+      </c>
+      <c r="K31" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="K31" s="3" t="s">
+      <c r="L31" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="L31" s="3" t="s">
+      <c r="M31" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="M31" s="8">
-        <v>1</v>
+      <c r="N31" s="3" t="s">
+        <v>317</v>
       </c>
       <c r="O31" s="7"/>
       <c r="P31" s="7"/>
@@ -3987,17 +4085,20 @@
       <c r="I32" s="2">
         <v>1</v>
       </c>
-      <c r="J32" s="3" t="s">
+      <c r="J32" s="8">
+        <v>1</v>
+      </c>
+      <c r="K32" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="K32" s="3" t="s">
+      <c r="L32" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="L32" s="3" t="s">
+      <c r="M32" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="M32" s="8">
-        <v>1</v>
+      <c r="N32" s="3" t="s">
+        <v>351</v>
       </c>
       <c r="O32" s="7"/>
       <c r="P32" s="7"/>
@@ -4031,17 +4132,20 @@
       <c r="I33" s="2">
         <v>61</v>
       </c>
-      <c r="J33" s="3" t="s">
+      <c r="J33" s="8">
+        <v>1</v>
+      </c>
+      <c r="K33" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="K33" s="3" t="s">
+      <c r="L33" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="L33" s="3" t="s">
+      <c r="M33" s="3" t="s">
         <v>531</v>
       </c>
-      <c r="M33" s="8">
-        <v>1</v>
+      <c r="N33" s="3" t="s">
+        <v>531</v>
       </c>
       <c r="O33" s="7"/>
       <c r="P33" s="7"/>
@@ -4075,17 +4179,20 @@
       <c r="I34" s="2">
         <v>99</v>
       </c>
-      <c r="J34" s="3" t="s">
+      <c r="J34" s="8">
+        <v>1</v>
+      </c>
+      <c r="K34" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="K34" s="3" t="s">
+      <c r="L34" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="L34" s="3" t="s">
+      <c r="M34" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="M34" s="8">
-        <v>1</v>
+      <c r="N34" s="3" t="s">
+        <v>520</v>
       </c>
       <c r="O34" s="7"/>
       <c r="P34" s="7"/>
@@ -4119,17 +4226,20 @@
       <c r="I35" s="2">
         <v>6</v>
       </c>
-      <c r="J35" s="3" t="s">
+      <c r="J35" s="8">
+        <v>1</v>
+      </c>
+      <c r="K35" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="K35" s="3" t="s">
+      <c r="L35" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="L35" s="3" t="s">
+      <c r="M35" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="M35" s="8">
-        <v>1</v>
+      <c r="N35" s="3" t="s">
+        <v>333</v>
       </c>
       <c r="O35" s="7"/>
       <c r="P35" s="7"/>
@@ -4163,17 +4273,20 @@
       <c r="I36" s="2">
         <v>2</v>
       </c>
-      <c r="J36" s="3" t="s">
+      <c r="J36" s="8">
+        <v>1</v>
+      </c>
+      <c r="K36" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="K36" s="3" t="s">
+      <c r="L36" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="L36" s="3" t="s">
+      <c r="M36" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="M36" s="8">
-        <v>1</v>
+      <c r="N36" s="3" t="s">
+        <v>335</v>
       </c>
       <c r="O36" s="7"/>
       <c r="P36" s="7"/>
@@ -4207,17 +4320,20 @@
       <c r="I37" s="2">
         <v>42</v>
       </c>
-      <c r="J37" s="3" t="s">
+      <c r="J37" s="8">
+        <v>1</v>
+      </c>
+      <c r="K37" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="K37" s="3" t="s">
+      <c r="L37" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="L37" s="3" t="s">
+      <c r="M37" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="M37" s="8">
-        <v>1</v>
+      <c r="N37" s="3" t="s">
+        <v>330</v>
       </c>
       <c r="O37" s="7"/>
       <c r="P37" s="7"/>
@@ -4251,17 +4367,20 @@
       <c r="I38" s="2">
         <v>34</v>
       </c>
-      <c r="J38" s="3" t="s">
+      <c r="J38" s="8">
+        <v>1</v>
+      </c>
+      <c r="K38" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="K38" s="3" t="s">
+      <c r="L38" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="L38" s="3" t="s">
+      <c r="M38" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="M38" s="8">
-        <v>1</v>
+      <c r="N38" s="3" t="s">
+        <v>315</v>
       </c>
       <c r="O38" s="7"/>
       <c r="P38" s="7"/>
@@ -4295,17 +4414,20 @@
       <c r="I39" s="2">
         <v>8</v>
       </c>
-      <c r="J39" s="3" t="s">
+      <c r="J39" s="8">
+        <v>0</v>
+      </c>
+      <c r="K39" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="K39" s="3" t="s">
+      <c r="L39" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="L39" s="3" t="s">
+      <c r="M39" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="M39" s="8">
-        <v>0</v>
+      <c r="N39" s="3" t="s">
+        <v>339</v>
       </c>
       <c r="O39" s="7"/>
       <c r="P39" s="7"/>
@@ -4339,17 +4461,20 @@
       <c r="I40" s="2">
         <v>1</v>
       </c>
-      <c r="J40" s="3" t="s">
+      <c r="J40" s="8">
+        <v>1</v>
+      </c>
+      <c r="K40" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="K40" s="3" t="s">
+      <c r="L40" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="L40" s="3" t="s">
+      <c r="M40" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="M40" s="8">
-        <v>1</v>
+      <c r="N40" s="3" t="s">
+        <v>326</v>
       </c>
       <c r="O40" s="7"/>
       <c r="P40" s="7"/>
@@ -4383,17 +4508,20 @@
       <c r="I41" s="2">
         <v>4</v>
       </c>
-      <c r="J41" s="3" t="s">
+      <c r="J41" s="8">
+        <v>1</v>
+      </c>
+      <c r="K41" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="K41" s="3" t="s">
+      <c r="L41" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="L41" s="3" t="s">
+      <c r="M41" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="M41" s="8">
-        <v>1</v>
+      <c r="N41" s="3" t="s">
+        <v>318</v>
       </c>
       <c r="O41" s="7"/>
       <c r="P41" s="7"/>
@@ -4427,17 +4555,20 @@
       <c r="I42" s="2">
         <v>30</v>
       </c>
-      <c r="J42" s="3" t="s">
+      <c r="J42" s="8">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="K42" s="3" t="s">
+      <c r="L42" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="L42" s="3" t="s">
+      <c r="M42" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="M42" s="8">
-        <v>0</v>
+      <c r="N42" s="3" t="s">
+        <v>332</v>
       </c>
       <c r="O42" s="7"/>
       <c r="P42" s="7"/>
@@ -4471,17 +4602,20 @@
       <c r="I43" s="2">
         <v>35</v>
       </c>
-      <c r="J43" s="3" t="s">
+      <c r="J43" s="8">
+        <v>0</v>
+      </c>
+      <c r="K43" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="K43" s="3" t="s">
+      <c r="L43" s="3" t="s">
         <v>516</v>
       </c>
-      <c r="L43" s="3" t="s">
+      <c r="M43" s="3" t="s">
         <v>517</v>
       </c>
-      <c r="M43" s="8">
-        <v>0</v>
+      <c r="N43" s="3" t="s">
+        <v>517</v>
       </c>
       <c r="O43" s="7"/>
       <c r="P43" s="7"/>
@@ -4515,17 +4649,20 @@
       <c r="I44" s="2">
         <v>8</v>
       </c>
-      <c r="J44" s="3" t="s">
+      <c r="J44" s="8">
+        <v>0</v>
+      </c>
+      <c r="K44" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="K44" s="3" t="s">
+      <c r="L44" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="L44" s="3" t="s">
+      <c r="M44" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="M44" s="8">
-        <v>0</v>
+      <c r="N44" s="3" t="s">
+        <v>279</v>
       </c>
       <c r="O44" s="7"/>
       <c r="P44" s="7"/>
@@ -4559,17 +4696,20 @@
       <c r="I45" s="2">
         <v>43</v>
       </c>
-      <c r="J45" s="3" t="s">
+      <c r="J45" s="8">
+        <v>0</v>
+      </c>
+      <c r="K45" s="3" t="s">
         <v>607</v>
       </c>
-      <c r="K45" s="3" t="s">
+      <c r="L45" s="3" t="s">
         <v>608</v>
       </c>
-      <c r="L45" s="3" t="s">
+      <c r="M45" s="3" t="s">
         <v>609</v>
       </c>
-      <c r="M45" s="8">
-        <v>0</v>
+      <c r="N45" s="3" t="s">
+        <v>609</v>
       </c>
       <c r="O45" s="7"/>
       <c r="P45" s="7"/>
@@ -4603,17 +4743,20 @@
       <c r="I46" s="2">
         <v>10</v>
       </c>
-      <c r="J46" s="3" t="s">
+      <c r="J46" s="8">
+        <v>0</v>
+      </c>
+      <c r="K46" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="K46" s="3" t="s">
+      <c r="L46" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="L46" s="3" t="s">
+      <c r="M46" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="M46" s="8">
-        <v>0</v>
+      <c r="N46" s="3" t="s">
+        <v>353</v>
       </c>
       <c r="O46" s="7"/>
       <c r="P46" s="7"/>
@@ -4647,17 +4790,20 @@
       <c r="I47" s="2">
         <v>15</v>
       </c>
-      <c r="J47" s="3" t="s">
+      <c r="J47" s="8">
+        <v>0</v>
+      </c>
+      <c r="K47" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="K47" s="3" t="s">
+      <c r="L47" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="L47" s="3" t="s">
+      <c r="M47" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="M47" s="8">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>346</v>
       </c>
       <c r="O47" s="7"/>
       <c r="P47" s="7"/>
@@ -4691,17 +4837,20 @@
       <c r="I48" s="2">
         <v>35</v>
       </c>
-      <c r="J48" s="3" t="s">
+      <c r="J48" s="8">
+        <v>0</v>
+      </c>
+      <c r="K48" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="K48" s="3" t="s">
+      <c r="L48" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="L48" s="3" t="s">
+      <c r="M48" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="M48" s="8">
-        <v>0</v>
+      <c r="N48" s="3" t="s">
+        <v>347</v>
       </c>
       <c r="O48" s="7"/>
       <c r="P48" s="7"/>
@@ -4735,17 +4884,20 @@
       <c r="I49" s="2">
         <v>2</v>
       </c>
-      <c r="J49" s="3" t="s">
+      <c r="J49" s="8">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="K49" s="3" t="s">
+      <c r="L49" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="L49" s="3" t="s">
+      <c r="M49" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="M49" s="8">
-        <v>0</v>
+      <c r="N49" s="3" t="s">
+        <v>328</v>
       </c>
       <c r="O49" s="7"/>
       <c r="P49" s="7"/>
@@ -4779,17 +4931,20 @@
       <c r="I50" s="2">
         <v>30</v>
       </c>
-      <c r="J50" s="3" t="s">
+      <c r="J50" s="8">
+        <v>0</v>
+      </c>
+      <c r="K50" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="K50" s="3" t="s">
+      <c r="L50" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="L50" s="3" t="s">
+      <c r="M50" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="M50" s="8">
-        <v>0</v>
+      <c r="N50" s="3" t="s">
+        <v>345</v>
       </c>
       <c r="O50" s="7"/>
       <c r="P50" s="7"/>
@@ -4823,17 +4978,20 @@
       <c r="I51" s="2">
         <v>21</v>
       </c>
-      <c r="J51" s="3" t="s">
+      <c r="J51" s="8">
+        <v>0</v>
+      </c>
+      <c r="K51" s="3" t="s">
         <v>521</v>
       </c>
-      <c r="K51" s="3" t="s">
+      <c r="L51" s="3" t="s">
         <v>617</v>
       </c>
-      <c r="L51" s="3" t="s">
+      <c r="M51" s="3" t="s">
         <v>522</v>
       </c>
-      <c r="M51" s="8">
-        <v>0</v>
+      <c r="N51" s="3" t="s">
+        <v>522</v>
       </c>
       <c r="O51" s="7"/>
       <c r="P51" s="7"/>
@@ -4867,17 +5025,20 @@
       <c r="I52" s="2">
         <v>5</v>
       </c>
-      <c r="J52" s="3" t="s">
+      <c r="J52" s="8">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3" t="s">
         <v>595</v>
       </c>
-      <c r="K52" s="3" t="s">
+      <c r="L52" s="3" t="s">
         <v>596</v>
       </c>
-      <c r="L52" s="3" t="s">
+      <c r="M52" s="3" t="s">
         <v>597</v>
       </c>
-      <c r="M52" s="8">
-        <v>0</v>
+      <c r="N52" s="3" t="s">
+        <v>597</v>
       </c>
       <c r="O52" s="7"/>
       <c r="P52" s="7"/>
@@ -4911,17 +5072,20 @@
       <c r="I53" s="2">
         <v>14</v>
       </c>
-      <c r="J53" s="3" t="s">
+      <c r="J53" s="8">
+        <v>0</v>
+      </c>
+      <c r="K53" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="K53" s="3" t="s">
+      <c r="L53" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="L53" s="3" t="s">
+      <c r="M53" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="M53" s="8">
-        <v>0</v>
+      <c r="N53" s="3" t="s">
+        <v>316</v>
       </c>
       <c r="O53" s="7"/>
       <c r="P53" s="7"/>
@@ -4955,17 +5119,20 @@
       <c r="I54" s="2">
         <v>42</v>
       </c>
-      <c r="J54" s="3" t="s">
+      <c r="J54" s="8">
+        <v>0</v>
+      </c>
+      <c r="K54" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="K54" s="3" t="s">
+      <c r="L54" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="L54" s="3" t="s">
+      <c r="M54" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="M54" s="8">
-        <v>0</v>
+      <c r="N54" s="3" t="s">
+        <v>340</v>
       </c>
       <c r="O54" s="7"/>
       <c r="P54" s="7"/>
@@ -4999,17 +5166,20 @@
       <c r="I55" s="2">
         <v>50</v>
       </c>
-      <c r="J55" s="3" t="s">
+      <c r="J55" s="8">
+        <v>0</v>
+      </c>
+      <c r="K55" s="3" t="s">
         <v>592</v>
       </c>
-      <c r="K55" s="3" t="s">
+      <c r="L55" s="3" t="s">
         <v>593</v>
       </c>
-      <c r="L55" s="3" t="s">
+      <c r="M55" s="3" t="s">
         <v>594</v>
       </c>
-      <c r="M55" s="8">
-        <v>0</v>
+      <c r="N55" s="3" t="s">
+        <v>594</v>
       </c>
       <c r="O55" s="7"/>
       <c r="P55" s="7"/>
@@ -5043,17 +5213,20 @@
       <c r="I56" s="2">
         <v>4</v>
       </c>
-      <c r="J56" s="3" t="s">
+      <c r="J56" s="8">
+        <v>0</v>
+      </c>
+      <c r="K56" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="K56" s="3" t="s">
+      <c r="L56" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="L56" s="3" t="s">
+      <c r="M56" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="M56" s="8">
-        <v>0</v>
+      <c r="N56" s="3" t="s">
+        <v>325</v>
       </c>
       <c r="O56" s="7"/>
       <c r="P56" s="7"/>
@@ -5087,17 +5260,20 @@
       <c r="I57" s="2">
         <v>19</v>
       </c>
-      <c r="J57" s="3" t="s">
+      <c r="J57" s="8">
+        <v>0</v>
+      </c>
+      <c r="K57" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="K57" s="3" t="s">
+      <c r="L57" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="L57" s="3" t="s">
+      <c r="M57" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="M57" s="8">
-        <v>0</v>
+      <c r="N57" s="3" t="s">
+        <v>295</v>
       </c>
       <c r="O57" s="7"/>
       <c r="P57" s="7"/>
@@ -5131,17 +5307,20 @@
       <c r="I58" s="2">
         <v>41</v>
       </c>
-      <c r="J58" s="3" t="s">
+      <c r="J58" s="8">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="K58" s="3" t="s">
+      <c r="L58" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="L58" s="3" t="s">
+      <c r="M58" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="M58" s="8">
-        <v>0</v>
+      <c r="N58" s="3" t="s">
+        <v>579</v>
       </c>
       <c r="O58" s="7"/>
       <c r="P58" s="7"/>
@@ -5175,17 +5354,20 @@
       <c r="I59" s="2">
         <v>22</v>
       </c>
-      <c r="J59" s="3" t="s">
+      <c r="J59" s="8">
+        <v>0</v>
+      </c>
+      <c r="K59" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="K59" s="3" t="s">
+      <c r="L59" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="L59" s="3" t="s">
+      <c r="M59" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="M59" s="8">
-        <v>0</v>
+      <c r="N59" s="3" t="s">
+        <v>338</v>
       </c>
       <c r="O59" s="7"/>
       <c r="P59" s="7"/>
@@ -5219,17 +5401,20 @@
       <c r="I60" s="2">
         <v>10</v>
       </c>
-      <c r="J60" s="3" t="s">
+      <c r="J60" s="8">
+        <v>0</v>
+      </c>
+      <c r="K60" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="K60" s="3" t="s">
+      <c r="L60" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="L60" s="3" t="s">
+      <c r="M60" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="M60" s="8">
-        <v>0</v>
+      <c r="N60" s="3" t="s">
+        <v>309</v>
       </c>
       <c r="O60" s="7"/>
       <c r="P60" s="7"/>
@@ -5263,17 +5448,20 @@
       <c r="I61" s="2">
         <v>87</v>
       </c>
-      <c r="J61" s="3" t="s">
+      <c r="J61" s="8">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="K61" s="3" t="s">
+      <c r="L61" s="3" t="s">
         <v>616</v>
       </c>
-      <c r="L61" s="3" t="s">
+      <c r="M61" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="M61" s="8">
-        <v>0</v>
+      <c r="N61" s="3" t="s">
+        <v>511</v>
       </c>
       <c r="O61" s="7"/>
       <c r="P61" s="7"/>
@@ -5307,17 +5495,20 @@
       <c r="I62" s="2">
         <v>38</v>
       </c>
-      <c r="J62" s="3" t="s">
+      <c r="J62" s="8">
+        <v>0</v>
+      </c>
+      <c r="K62" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="K62" s="3" t="s">
+      <c r="L62" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="L62" s="3" t="s">
+      <c r="M62" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="M62" s="8">
-        <v>0</v>
+      <c r="N62" s="3" t="s">
+        <v>314</v>
       </c>
       <c r="O62" s="7"/>
       <c r="P62" s="7"/>
@@ -5351,17 +5542,20 @@
       <c r="I63" s="2">
         <v>3</v>
       </c>
-      <c r="J63" s="3" t="s">
+      <c r="J63" s="8">
+        <v>0</v>
+      </c>
+      <c r="K63" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="K63" s="3" t="s">
+      <c r="L63" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="L63" s="3" t="s">
+      <c r="M63" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="M63" s="8">
-        <v>0</v>
+      <c r="N63" s="3" t="s">
+        <v>334</v>
       </c>
       <c r="O63" s="7"/>
       <c r="P63" s="7"/>
@@ -5395,17 +5589,20 @@
       <c r="I64" s="2">
         <v>20</v>
       </c>
-      <c r="J64" s="3" t="s">
+      <c r="J64" s="8">
+        <v>0</v>
+      </c>
+      <c r="K64" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="K64" s="3" t="s">
+      <c r="L64" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="L64" s="3" t="s">
+      <c r="M64" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="M64" s="8">
-        <v>0</v>
+      <c r="N64" s="3" t="s">
+        <v>342</v>
       </c>
       <c r="O64" s="7"/>
       <c r="P64" s="7"/>
@@ -5439,17 +5636,20 @@
       <c r="I65" s="2">
         <v>46</v>
       </c>
-      <c r="J65" s="3" t="s">
+      <c r="J65" s="8">
+        <v>0</v>
+      </c>
+      <c r="K65" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="K65" s="3" t="s">
+      <c r="L65" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="L65" s="3" t="s">
+      <c r="M65" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="M65" s="8">
-        <v>0</v>
+      <c r="N65" s="3" t="s">
+        <v>329</v>
       </c>
       <c r="O65" s="7"/>
       <c r="P65" s="7"/>
@@ -5483,17 +5683,20 @@
       <c r="I66" s="2">
         <v>7</v>
       </c>
-      <c r="J66" s="3" t="s">
+      <c r="J66" s="8">
+        <v>0</v>
+      </c>
+      <c r="K66" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="K66" s="3" t="s">
+      <c r="L66" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="L66" s="3" t="s">
+      <c r="M66" s="3" t="s">
         <v>564</v>
       </c>
-      <c r="M66" s="8">
-        <v>0</v>
+      <c r="N66" s="3" t="s">
+        <v>564</v>
       </c>
       <c r="O66" s="7"/>
       <c r="P66" s="7"/>
@@ -5527,17 +5730,20 @@
       <c r="I67" s="2">
         <v>35</v>
       </c>
-      <c r="J67" s="3" t="s">
+      <c r="J67" s="8">
+        <v>0</v>
+      </c>
+      <c r="K67" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="K67" s="3" t="s">
+      <c r="L67" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="L67" s="3" t="s">
+      <c r="M67" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="M67" s="8">
-        <v>0</v>
+      <c r="N67" s="3" t="s">
+        <v>293</v>
       </c>
       <c r="O67" s="7"/>
       <c r="P67" s="7"/>
@@ -5571,17 +5777,20 @@
       <c r="I68" s="2">
         <v>10</v>
       </c>
-      <c r="J68" s="3" t="s">
+      <c r="J68" s="8">
+        <v>0</v>
+      </c>
+      <c r="K68" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="K68" s="3" t="s">
+      <c r="L68" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="L68" s="3" t="s">
+      <c r="M68" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="M68" s="8">
-        <v>0</v>
+      <c r="N68" s="3" t="s">
+        <v>349</v>
       </c>
       <c r="O68" s="7"/>
       <c r="P68" s="7"/>
@@ -5615,17 +5824,20 @@
       <c r="I69" s="2">
         <v>20</v>
       </c>
-      <c r="J69" s="3" t="s">
+      <c r="J69" s="8">
+        <v>0</v>
+      </c>
+      <c r="K69" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="K69" s="3" t="s">
+      <c r="L69" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="L69" s="3" t="s">
+      <c r="M69" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="M69" s="8">
-        <v>0</v>
+      <c r="N69" s="3" t="s">
+        <v>276</v>
       </c>
       <c r="O69" s="7"/>
       <c r="P69" s="7"/>
@@ -5659,17 +5871,20 @@
       <c r="I70" s="2">
         <v>49</v>
       </c>
-      <c r="J70" s="3" t="s">
+      <c r="J70" s="8">
+        <v>0</v>
+      </c>
+      <c r="K70" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="K70" s="3" t="s">
+      <c r="L70" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="L70" s="3" t="s">
+      <c r="M70" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="M70" s="8">
-        <v>0</v>
+      <c r="N70" s="3" t="s">
+        <v>305</v>
       </c>
       <c r="O70" s="7"/>
       <c r="P70" s="7"/>
@@ -5703,17 +5918,20 @@
       <c r="I71" s="2">
         <v>2</v>
       </c>
-      <c r="J71" s="3" t="s">
+      <c r="J71" s="8">
+        <v>0</v>
+      </c>
+      <c r="K71" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="K71" s="3" t="s">
+      <c r="L71" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="L71" s="3" t="s">
+      <c r="M71" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="M71" s="8">
-        <v>0</v>
+      <c r="N71" s="3" t="s">
+        <v>322</v>
       </c>
       <c r="O71" s="7"/>
       <c r="P71" s="7"/>
@@ -5747,17 +5965,20 @@
       <c r="I72" s="2">
         <v>55</v>
       </c>
-      <c r="J72" s="3" t="s">
+      <c r="J72" s="8">
+        <v>0</v>
+      </c>
+      <c r="K72" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="K72" s="3" t="s">
+      <c r="L72" s="3" t="s">
         <v>527</v>
       </c>
-      <c r="L72" s="3" t="s">
+      <c r="M72" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="M72" s="8">
-        <v>0</v>
+      <c r="N72" s="3" t="s">
+        <v>528</v>
       </c>
       <c r="O72" s="7"/>
       <c r="P72" s="7"/>
@@ -5791,17 +6012,20 @@
       <c r="I73" s="2">
         <v>6</v>
       </c>
-      <c r="J73" s="3" t="s">
+      <c r="J73" s="8">
+        <v>0</v>
+      </c>
+      <c r="K73" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="K73" s="3" t="s">
+      <c r="L73" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="L73" s="3" t="s">
+      <c r="M73" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="M73" s="8">
-        <v>0</v>
+      <c r="N73" s="3" t="s">
+        <v>344</v>
       </c>
       <c r="O73" s="7"/>
       <c r="P73" s="7"/>
@@ -5835,17 +6059,20 @@
       <c r="I74" s="2">
         <v>9</v>
       </c>
-      <c r="J74" s="3" t="s">
+      <c r="J74" s="8">
+        <v>0</v>
+      </c>
+      <c r="K74" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="K74" s="3" t="s">
+      <c r="L74" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="L74" s="3" t="s">
+      <c r="M74" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="M74" s="8">
-        <v>0</v>
+      <c r="N74" s="3" t="s">
+        <v>324</v>
       </c>
       <c r="O74" s="7"/>
       <c r="P74" s="7"/>
@@ -5879,17 +6106,20 @@
       <c r="I75" s="2">
         <v>1</v>
       </c>
-      <c r="J75" s="3" t="s">
+      <c r="J75" s="8">
+        <v>0</v>
+      </c>
+      <c r="K75" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="K75" s="3" t="s">
+      <c r="L75" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="L75" s="3" t="s">
+      <c r="M75" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="M75" s="8">
-        <v>0</v>
+      <c r="N75" s="3" t="s">
+        <v>310</v>
       </c>
       <c r="O75" s="7"/>
       <c r="P75" s="7"/>
@@ -5923,17 +6153,20 @@
       <c r="I76" s="2">
         <v>41</v>
       </c>
-      <c r="J76" s="3" t="s">
+      <c r="J76" s="8">
+        <v>0</v>
+      </c>
+      <c r="K76" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="K76" s="3" t="s">
+      <c r="L76" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="L76" s="3" t="s">
+      <c r="M76" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="M76" s="8">
-        <v>0</v>
+      <c r="N76" s="3" t="s">
+        <v>286</v>
       </c>
       <c r="O76" s="7"/>
       <c r="P76" s="7"/>
@@ -5967,17 +6200,20 @@
       <c r="I77" s="2">
         <v>49</v>
       </c>
-      <c r="J77" s="3" t="s">
+      <c r="J77" s="8">
+        <v>0</v>
+      </c>
+      <c r="K77" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="K77" s="3" t="s">
+      <c r="L77" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="L77" s="3" t="s">
+      <c r="M77" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="M77" s="8">
-        <v>0</v>
+      <c r="N77" s="3" t="s">
+        <v>285</v>
       </c>
       <c r="O77" s="7"/>
       <c r="P77" s="7"/>
@@ -6011,17 +6247,20 @@
       <c r="I78" s="2">
         <v>99</v>
       </c>
-      <c r="J78" s="3" t="s">
+      <c r="J78" s="8">
+        <v>0</v>
+      </c>
+      <c r="K78" s="3" t="s">
         <v>553</v>
       </c>
-      <c r="K78" s="3" t="s">
+      <c r="L78" s="3" t="s">
         <v>554</v>
       </c>
-      <c r="L78" s="3" t="s">
+      <c r="M78" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="M78" s="8">
-        <v>0</v>
+      <c r="N78" s="3" t="s">
+        <v>555</v>
       </c>
       <c r="O78" s="7"/>
       <c r="P78" s="7"/>
@@ -6055,17 +6294,20 @@
       <c r="I79" s="2">
         <v>42</v>
       </c>
-      <c r="J79" s="3" t="s">
+      <c r="J79" s="8">
+        <v>0</v>
+      </c>
+      <c r="K79" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="K79" s="3" t="s">
+      <c r="L79" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="L79" s="3" t="s">
+      <c r="M79" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="M79" s="8">
-        <v>0</v>
+      <c r="N79" s="3" t="s">
+        <v>514</v>
       </c>
       <c r="O79" s="7"/>
       <c r="P79" s="7"/>
@@ -6099,17 +6341,20 @@
       <c r="I80" s="2">
         <v>40</v>
       </c>
-      <c r="J80" s="3" t="s">
+      <c r="J80" s="8">
+        <v>0</v>
+      </c>
+      <c r="K80" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="K80" s="3" t="s">
+      <c r="L80" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="L80" s="3" t="s">
+      <c r="M80" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="M80" s="8">
-        <v>0</v>
+      <c r="N80" s="3" t="s">
+        <v>271</v>
       </c>
       <c r="O80" s="7"/>
       <c r="P80" s="7"/>
@@ -6143,17 +6388,20 @@
       <c r="I81" s="2">
         <v>9</v>
       </c>
-      <c r="J81" s="3" t="s">
+      <c r="J81" s="8">
+        <v>0</v>
+      </c>
+      <c r="K81" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="K81" s="3" t="s">
+      <c r="L81" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="L81" s="3" t="s">
+      <c r="M81" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="M81" s="8">
-        <v>0</v>
+      <c r="N81" s="3" t="s">
+        <v>308</v>
       </c>
       <c r="O81" s="7"/>
       <c r="P81" s="7"/>
@@ -6187,17 +6435,20 @@
       <c r="I82" s="2">
         <v>26</v>
       </c>
-      <c r="J82" s="3" t="s">
+      <c r="J82" s="8">
+        <v>0</v>
+      </c>
+      <c r="K82" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="K82" s="3" t="s">
+      <c r="L82" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="L82" s="3" t="s">
+      <c r="M82" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="M82" s="8">
-        <v>0</v>
+      <c r="N82" s="3" t="s">
+        <v>287</v>
       </c>
       <c r="O82" s="7"/>
       <c r="P82" s="7"/>
@@ -6231,17 +6482,20 @@
       <c r="I83" s="2">
         <v>41</v>
       </c>
-      <c r="J83" s="3" t="s">
+      <c r="J83" s="8">
+        <v>0</v>
+      </c>
+      <c r="K83" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="K83" s="3" t="s">
+      <c r="L83" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="L83" s="3" t="s">
+      <c r="M83" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="M83" s="8">
-        <v>0</v>
+      <c r="N83" s="3" t="s">
+        <v>281</v>
       </c>
       <c r="O83" s="7"/>
       <c r="P83" s="7"/>
@@ -6275,17 +6529,20 @@
       <c r="I84" s="2">
         <v>39</v>
       </c>
-      <c r="J84" s="3" t="s">
+      <c r="J84" s="8">
+        <v>0</v>
+      </c>
+      <c r="K84" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="K84" s="3" t="s">
+      <c r="L84" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="L84" s="3" t="s">
+      <c r="M84" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="M84" s="8">
-        <v>0</v>
+      <c r="N84" s="3" t="s">
+        <v>291</v>
       </c>
       <c r="O84" s="7"/>
       <c r="P84" s="7"/>
@@ -6319,17 +6576,20 @@
       <c r="I85" s="2">
         <v>4</v>
       </c>
-      <c r="J85" s="3" t="s">
+      <c r="J85" s="8">
+        <v>0</v>
+      </c>
+      <c r="K85" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="K85" s="3" t="s">
+      <c r="L85" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="L85" s="3" t="s">
+      <c r="M85" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="M85" s="8">
-        <v>0</v>
+      <c r="N85" s="3" t="s">
+        <v>283</v>
       </c>
       <c r="O85" s="7"/>
       <c r="P85" s="7"/>
@@ -6363,17 +6623,20 @@
       <c r="I86" s="2">
         <v>14</v>
       </c>
-      <c r="J86" s="3" t="s">
+      <c r="J86" s="8">
+        <v>0</v>
+      </c>
+      <c r="K86" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="K86" s="3" t="s">
+      <c r="L86" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="L86" s="3" t="s">
+      <c r="M86" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="M86" s="8">
-        <v>0</v>
+      <c r="N86" s="3" t="s">
+        <v>272</v>
       </c>
       <c r="O86" s="7"/>
       <c r="P86" s="7"/>
@@ -6407,17 +6670,20 @@
       <c r="I87" s="2">
         <v>45</v>
       </c>
-      <c r="J87" s="3" t="s">
+      <c r="J87" s="8">
+        <v>0</v>
+      </c>
+      <c r="K87" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="K87" s="3" t="s">
+      <c r="L87" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="L87" s="3" t="s">
+      <c r="M87" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="M87" s="8">
-        <v>0</v>
+      <c r="N87" s="3" t="s">
+        <v>297</v>
       </c>
       <c r="O87" s="7"/>
       <c r="P87" s="7"/>
@@ -6451,17 +6717,20 @@
       <c r="I88" s="2">
         <v>83</v>
       </c>
-      <c r="J88" s="3" t="s">
+      <c r="J88" s="8">
+        <v>0</v>
+      </c>
+      <c r="K88" s="3" t="s">
         <v>613</v>
       </c>
-      <c r="K88" s="3" t="s">
+      <c r="L88" s="3" t="s">
         <v>614</v>
       </c>
-      <c r="L88" s="3" t="s">
+      <c r="M88" s="3" t="s">
         <v>615</v>
       </c>
-      <c r="M88" s="8">
-        <v>0</v>
+      <c r="N88" s="3" t="s">
+        <v>615</v>
       </c>
       <c r="O88" s="7"/>
       <c r="P88" s="7"/>
@@ -6495,17 +6764,20 @@
       <c r="I89" s="2">
         <v>69</v>
       </c>
-      <c r="J89" s="3" t="s">
+      <c r="J89" s="8">
+        <v>0</v>
+      </c>
+      <c r="K89" s="3" t="s">
         <v>574</v>
       </c>
-      <c r="K89" s="3" t="s">
+      <c r="L89" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="L89" s="3" t="s">
+      <c r="M89" s="3" t="s">
         <v>576</v>
       </c>
-      <c r="M89" s="8">
-        <v>0</v>
+      <c r="N89" s="3" t="s">
+        <v>576</v>
       </c>
       <c r="O89" s="7"/>
       <c r="P89" s="7"/>
@@ -6539,17 +6811,20 @@
       <c r="I90" s="2">
         <v>38</v>
       </c>
-      <c r="J90" s="3" t="s">
+      <c r="J90" s="8">
+        <v>0</v>
+      </c>
+      <c r="K90" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="K90" s="3" t="s">
+      <c r="L90" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="L90" s="3" t="s">
+      <c r="M90" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="M90" s="8">
-        <v>0</v>
+      <c r="N90" s="3" t="s">
+        <v>570</v>
       </c>
       <c r="O90" s="7"/>
       <c r="P90" s="7"/>
@@ -6583,17 +6858,20 @@
       <c r="I91" s="2">
         <v>53</v>
       </c>
-      <c r="J91" s="3" t="s">
+      <c r="J91" s="8">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="K91" s="3" t="s">
+      <c r="L91" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="L91" s="3" t="s">
+      <c r="M91" s="3" t="s">
         <v>582</v>
       </c>
-      <c r="M91" s="8">
-        <v>0</v>
+      <c r="N91" s="3" t="s">
+        <v>582</v>
       </c>
       <c r="O91" s="7"/>
       <c r="P91" s="7"/>
@@ -6627,17 +6905,20 @@
       <c r="I92" s="2">
         <v>4</v>
       </c>
-      <c r="J92" s="3" t="s">
+      <c r="J92" s="8">
+        <v>0</v>
+      </c>
+      <c r="K92" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="K92" s="3" t="s">
+      <c r="L92" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="L92" s="3" t="s">
+      <c r="M92" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="M92" s="8">
-        <v>0</v>
+      <c r="N92" s="3" t="s">
+        <v>274</v>
       </c>
       <c r="O92" s="7"/>
       <c r="P92" s="7"/>
@@ -6671,17 +6952,20 @@
       <c r="I93" s="2">
         <v>43</v>
       </c>
-      <c r="J93" s="3" t="s">
+      <c r="J93" s="8">
+        <v>0</v>
+      </c>
+      <c r="K93" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="K93" s="3" t="s">
+      <c r="L93" s="3" t="s">
         <v>548</v>
       </c>
-      <c r="L93" s="3" t="s">
+      <c r="M93" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="M93" s="8">
-        <v>0</v>
+      <c r="N93" s="3" t="s">
+        <v>549</v>
       </c>
       <c r="O93" s="7"/>
       <c r="P93" s="7"/>
@@ -6715,17 +6999,20 @@
       <c r="I94" s="2">
         <v>47</v>
       </c>
-      <c r="J94" s="3" t="s">
+      <c r="J94" s="8">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="K94" s="3" t="s">
+      <c r="L94" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="L94" s="3" t="s">
+      <c r="M94" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="M94" s="8">
-        <v>0</v>
+      <c r="N94" s="3" t="s">
+        <v>282</v>
       </c>
       <c r="O94" s="7"/>
       <c r="P94" s="7"/>
@@ -6759,17 +7046,20 @@
       <c r="I95" s="2">
         <v>21</v>
       </c>
-      <c r="J95" s="3" t="s">
+      <c r="J95" s="8">
+        <v>0</v>
+      </c>
+      <c r="K95" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="K95" s="3" t="s">
+      <c r="L95" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="L95" s="3" t="s">
+      <c r="M95" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="M95" s="8">
-        <v>0</v>
+      <c r="N95" s="3" t="s">
+        <v>288</v>
       </c>
       <c r="O95" s="7"/>
       <c r="P95" s="7"/>
@@ -6803,17 +7093,20 @@
       <c r="I96" s="2">
         <v>2</v>
       </c>
-      <c r="J96" s="3" t="s">
+      <c r="J96" s="8">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="K96" s="3" t="s">
+      <c r="L96" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="L96" s="3" t="s">
+      <c r="M96" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="M96" s="8">
-        <v>0</v>
+      <c r="N96" s="3" t="s">
+        <v>273</v>
       </c>
       <c r="O96" s="7"/>
       <c r="P96" s="7"/>
@@ -6847,17 +7140,20 @@
       <c r="I97" s="2">
         <v>40</v>
       </c>
-      <c r="J97" s="3" t="s">
+      <c r="J97" s="8">
+        <v>0</v>
+      </c>
+      <c r="K97" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="K97" s="3" t="s">
+      <c r="L97" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="L97" s="3" t="s">
+      <c r="M97" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="M97" s="8">
-        <v>0</v>
+      <c r="N97" s="3" t="s">
+        <v>296</v>
       </c>
       <c r="O97" s="7"/>
       <c r="P97" s="7"/>
@@ -6891,17 +7187,20 @@
       <c r="I98" s="2">
         <v>21</v>
       </c>
-      <c r="J98" s="3" t="s">
+      <c r="J98" s="8">
+        <v>0</v>
+      </c>
+      <c r="K98" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="K98" s="3" t="s">
+      <c r="L98" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="L98" s="3" t="s">
+      <c r="M98" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="M98" s="8">
-        <v>0</v>
+      <c r="N98" s="3" t="s">
+        <v>289</v>
       </c>
       <c r="O98" s="7"/>
       <c r="P98" s="7"/>
@@ -6935,17 +7234,20 @@
       <c r="I99" s="2">
         <v>90</v>
       </c>
-      <c r="J99" s="3" t="s">
+      <c r="J99" s="8">
+        <v>0</v>
+      </c>
+      <c r="K99" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="K99" s="3" t="s">
+      <c r="L99" s="3" t="s">
         <v>533</v>
       </c>
-      <c r="L99" s="3" t="s">
+      <c r="M99" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="M99" s="8">
-        <v>0</v>
+      <c r="N99" s="3" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.3">
@@ -6976,17 +7278,20 @@
       <c r="I100" s="2">
         <v>79</v>
       </c>
-      <c r="J100" s="3" t="s">
+      <c r="J100" s="8">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3" t="s">
         <v>598</v>
       </c>
-      <c r="K100" s="3" t="s">
+      <c r="L100" s="3" t="s">
         <v>599</v>
       </c>
-      <c r="L100" s="3" t="s">
+      <c r="M100" s="3" t="s">
         <v>600</v>
       </c>
-      <c r="M100" s="8">
-        <v>0</v>
+      <c r="N100" s="3" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.3">
@@ -7017,17 +7322,20 @@
       <c r="I101" s="2">
         <v>65</v>
       </c>
-      <c r="J101" s="3" t="s">
+      <c r="J101" s="8">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3" t="s">
         <v>601</v>
       </c>
-      <c r="K101" s="3" t="s">
+      <c r="L101" s="3" t="s">
         <v>602</v>
       </c>
-      <c r="L101" s="3" t="s">
+      <c r="M101" s="3" t="s">
         <v>603</v>
       </c>
-      <c r="M101" s="8">
-        <v>0</v>
+      <c r="N101" s="3" t="s">
+        <v>603</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.3">
@@ -7058,17 +7366,20 @@
       <c r="I102" s="2">
         <v>89</v>
       </c>
-      <c r="J102" s="3" t="s">
+      <c r="J102" s="8">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="K102" s="3" t="s">
+      <c r="L102" s="3" t="s">
         <v>572</v>
       </c>
-      <c r="L102" s="3" t="s">
+      <c r="M102" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="M102" s="8">
-        <v>0</v>
+      <c r="N102" s="3" t="s">
+        <v>573</v>
       </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.3">
@@ -7099,17 +7410,20 @@
       <c r="I103" s="2">
         <v>30</v>
       </c>
-      <c r="J103" s="3" t="s">
+      <c r="J103" s="8">
+        <v>0</v>
+      </c>
+      <c r="K103" s="3" t="s">
         <v>541</v>
       </c>
-      <c r="K103" s="3" t="s">
+      <c r="L103" s="3" t="s">
         <v>542</v>
       </c>
-      <c r="L103" s="3" t="s">
+      <c r="M103" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="M103" s="8">
-        <v>0</v>
+      <c r="N103" s="3" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.3">
@@ -7140,17 +7454,20 @@
       <c r="I104" s="2">
         <v>74</v>
       </c>
-      <c r="J104" s="3" t="s">
+      <c r="J104" s="8">
+        <v>0</v>
+      </c>
+      <c r="K104" s="3" t="s">
         <v>544</v>
       </c>
-      <c r="K104" s="3" t="s">
+      <c r="L104" s="3" t="s">
         <v>545</v>
       </c>
-      <c r="L104" s="3" t="s">
+      <c r="M104" s="3" t="s">
         <v>546</v>
       </c>
-      <c r="M104" s="8">
-        <v>0</v>
+      <c r="N104" s="3" t="s">
+        <v>546</v>
       </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.3">
@@ -7181,17 +7498,20 @@
       <c r="I105" s="2">
         <v>31</v>
       </c>
-      <c r="J105" s="3" t="s">
+      <c r="J105" s="8">
+        <v>0</v>
+      </c>
+      <c r="K105" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="K105" s="3" t="s">
+      <c r="L105" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="L105" s="3" t="s">
+      <c r="M105" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="M105" s="8">
-        <v>0</v>
+      <c r="N105" s="3" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.3">
@@ -7222,17 +7542,20 @@
       <c r="I106" s="2">
         <v>11</v>
       </c>
-      <c r="J106" s="3" t="s">
+      <c r="J106" s="8">
+        <v>0</v>
+      </c>
+      <c r="K106" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="K106" s="3" t="s">
+      <c r="L106" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="L106" s="3" t="s">
+      <c r="M106" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="M106" s="8">
-        <v>0</v>
+      <c r="N106" s="3" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.3">
@@ -7263,17 +7586,20 @@
       <c r="I107" s="2">
         <v>98</v>
       </c>
-      <c r="J107" s="3" t="s">
+      <c r="J107" s="8">
+        <v>0</v>
+      </c>
+      <c r="K107" s="3" t="s">
         <v>559</v>
       </c>
-      <c r="K107" s="3" t="s">
+      <c r="L107" s="3" t="s">
         <v>560</v>
       </c>
-      <c r="L107" s="3" t="s">
+      <c r="M107" s="3" t="s">
         <v>561</v>
       </c>
-      <c r="M107" s="8">
-        <v>0</v>
+      <c r="N107" s="3" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.3">
@@ -7304,17 +7630,20 @@
       <c r="I108" s="2">
         <v>11</v>
       </c>
-      <c r="J108" s="3" t="s">
+      <c r="J108" s="8">
+        <v>0</v>
+      </c>
+      <c r="K108" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="K108" s="3" t="s">
+      <c r="L108" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="L108" s="3" t="s">
+      <c r="M108" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="M108" s="8">
-        <v>0</v>
+      <c r="N108" s="3" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.3">
@@ -7345,17 +7674,20 @@
       <c r="I109" s="2">
         <v>32</v>
       </c>
-      <c r="J109" s="3" t="s">
+      <c r="J109" s="8">
+        <v>0</v>
+      </c>
+      <c r="K109" s="3" t="s">
         <v>604</v>
       </c>
-      <c r="K109" s="3" t="s">
+      <c r="L109" s="3" t="s">
         <v>605</v>
       </c>
-      <c r="L109" s="3" t="s">
+      <c r="M109" s="3" t="s">
         <v>606</v>
       </c>
-      <c r="M109" s="8">
-        <v>0</v>
+      <c r="N109" s="3" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.3">
@@ -7386,17 +7718,20 @@
       <c r="I110" s="2">
         <v>4</v>
       </c>
-      <c r="J110" s="3" t="s">
+      <c r="J110" s="8">
+        <v>0</v>
+      </c>
+      <c r="K110" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="K110" s="3" t="s">
+      <c r="L110" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="L110" s="3" t="s">
+      <c r="M110" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="M110" s="8">
-        <v>0</v>
+      <c r="N110" s="3" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.3">
@@ -7427,17 +7762,20 @@
       <c r="I111" s="2">
         <v>46</v>
       </c>
-      <c r="J111" s="3" t="s">
+      <c r="J111" s="8">
+        <v>0</v>
+      </c>
+      <c r="K111" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="K111" s="3" t="s">
+      <c r="L111" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="L111" s="3" t="s">
+      <c r="M111" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="M111" s="8">
-        <v>0</v>
+      <c r="N111" s="3" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.3">
@@ -7468,20 +7806,23 @@
       <c r="I112" s="2">
         <v>37</v>
       </c>
-      <c r="J112" s="3" t="s">
+      <c r="J112" s="8">
+        <v>0</v>
+      </c>
+      <c r="K112" s="3" t="s">
         <v>550</v>
       </c>
-      <c r="K112" s="3" t="s">
+      <c r="L112" s="3" t="s">
         <v>551</v>
       </c>
-      <c r="L112" s="3" t="s">
+      <c r="M112" s="3" t="s">
         <v>552</v>
       </c>
-      <c r="M112" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N112" s="3" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A113" s="2">
         <v>111</v>
       </c>
@@ -7509,20 +7850,23 @@
       <c r="I113" s="2">
         <v>22</v>
       </c>
-      <c r="J113" s="3" t="s">
+      <c r="J113" s="8">
+        <v>0</v>
+      </c>
+      <c r="K113" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="K113" s="3" t="s">
+      <c r="L113" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="L113" s="3" t="s">
+      <c r="M113" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="M113" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N113" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A114" s="2">
         <v>112</v>
       </c>
@@ -7550,20 +7894,23 @@
       <c r="I114" s="2">
         <v>12</v>
       </c>
-      <c r="J114" s="3" t="s">
+      <c r="J114" s="8">
+        <v>0</v>
+      </c>
+      <c r="K114" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="K114" s="3" t="s">
+      <c r="L114" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="L114" s="3" t="s">
+      <c r="M114" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="M114" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N114" s="3" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A115" s="2">
         <v>113</v>
       </c>
@@ -7591,20 +7938,23 @@
       <c r="I115" s="2">
         <v>17</v>
       </c>
-      <c r="J115" s="3" t="s">
+      <c r="J115" s="8">
+        <v>0</v>
+      </c>
+      <c r="K115" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="K115" s="3" t="s">
+      <c r="L115" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="L115" s="3" t="s">
+      <c r="M115" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="M115" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N115" s="3" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A116" s="2">
         <v>114</v>
       </c>
@@ -7632,20 +7982,23 @@
       <c r="I116" s="2">
         <v>49</v>
       </c>
-      <c r="J116" s="3" t="s">
+      <c r="J116" s="8">
+        <v>0</v>
+      </c>
+      <c r="K116" s="3" t="s">
         <v>565</v>
       </c>
-      <c r="K116" s="3" t="s">
+      <c r="L116" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="L116" s="3" t="s">
+      <c r="M116" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="M116" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N116" s="3" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A117" s="2">
         <v>115</v>
       </c>
@@ -7673,20 +8026,23 @@
       <c r="I117" s="2">
         <v>45</v>
       </c>
-      <c r="J117" s="3" t="s">
+      <c r="J117" s="8">
+        <v>0</v>
+      </c>
+      <c r="K117" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="K117" s="3" t="s">
+      <c r="L117" s="3" t="s">
         <v>587</v>
       </c>
-      <c r="L117" s="3" t="s">
+      <c r="M117" s="3" t="s">
         <v>588</v>
       </c>
-      <c r="M117" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N117" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A118" s="2">
         <v>116</v>
       </c>
@@ -7714,20 +8070,23 @@
       <c r="I118" s="2">
         <v>12</v>
       </c>
-      <c r="J118" s="3" t="s">
+      <c r="J118" s="8">
+        <v>0</v>
+      </c>
+      <c r="K118" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="K118" s="3" t="s">
+      <c r="L118" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="L118" s="3" t="s">
+      <c r="M118" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="M118" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N118" s="3" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A119" s="2">
         <v>117</v>
       </c>
@@ -7755,20 +8114,23 @@
       <c r="I119" s="2">
         <v>24</v>
       </c>
-      <c r="J119" s="3" t="s">
+      <c r="J119" s="8">
+        <v>0</v>
+      </c>
+      <c r="K119" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="K119" s="3" t="s">
+      <c r="L119" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="L119" s="3" t="s">
+      <c r="M119" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="M119" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N119" s="3" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A120" s="2">
         <v>118</v>
       </c>
@@ -7796,20 +8158,23 @@
       <c r="I120" s="2">
         <v>21</v>
       </c>
-      <c r="J120" s="3" t="s">
+      <c r="J120" s="8">
+        <v>0</v>
+      </c>
+      <c r="K120" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="K120" s="3" t="s">
+      <c r="L120" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="L120" s="3" t="s">
+      <c r="M120" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="M120" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N120" s="3" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A121" s="2">
         <v>119</v>
       </c>
@@ -7837,20 +8202,23 @@
       <c r="I121" s="2">
         <v>62</v>
       </c>
-      <c r="J121" s="3" t="s">
+      <c r="J121" s="8">
+        <v>0</v>
+      </c>
+      <c r="K121" s="3" t="s">
         <v>583</v>
       </c>
-      <c r="K121" s="3" t="s">
+      <c r="L121" s="3" t="s">
         <v>584</v>
       </c>
-      <c r="L121" s="3" t="s">
+      <c r="M121" s="3" t="s">
         <v>585</v>
       </c>
-      <c r="M121" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N121" s="3" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A122" s="2">
         <v>120</v>
       </c>
@@ -7878,20 +8246,23 @@
       <c r="I122" s="2">
         <v>30</v>
       </c>
-      <c r="J122" s="3" t="s">
+      <c r="J122" s="8">
+        <v>0</v>
+      </c>
+      <c r="K122" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="K122" s="3" t="s">
+      <c r="L122" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="L122" s="3" t="s">
+      <c r="M122" s="3" t="s">
         <v>537</v>
       </c>
-      <c r="M122" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N122" s="3" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A123" s="2">
         <v>121</v>
       </c>
@@ -7919,20 +8290,23 @@
       <c r="I123" s="2">
         <v>82</v>
       </c>
-      <c r="J123" s="3" t="s">
+      <c r="J123" s="8">
+        <v>0</v>
+      </c>
+      <c r="K123" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="K123" s="3" t="s">
+      <c r="L123" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="L123" s="3" t="s">
+      <c r="M123" s="3" t="s">
         <v>558</v>
       </c>
-      <c r="M123" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N123" s="3" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A124" s="2">
         <v>122</v>
       </c>
@@ -7960,20 +8334,23 @@
       <c r="I124" s="2">
         <v>40</v>
       </c>
-      <c r="J124" s="3" t="s">
+      <c r="J124" s="8">
+        <v>0</v>
+      </c>
+      <c r="K124" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="K124" s="3" t="s">
+      <c r="L124" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="L124" s="3" t="s">
+      <c r="M124" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="M124" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N124" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A125" s="2">
         <v>123</v>
       </c>
@@ -8001,20 +8378,23 @@
       <c r="I125" s="2">
         <v>20</v>
       </c>
-      <c r="J125" s="3" t="s">
+      <c r="J125" s="8">
+        <v>0</v>
+      </c>
+      <c r="K125" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="K125" s="3" t="s">
+      <c r="L125" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="L125" s="3" t="s">
+      <c r="M125" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="M125" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N125" s="3" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A126" s="2">
         <v>124</v>
       </c>
@@ -8042,20 +8422,23 @@
       <c r="I126" s="2">
         <v>49</v>
       </c>
-      <c r="J126" s="3" t="s">
+      <c r="J126" s="8">
+        <v>0</v>
+      </c>
+      <c r="K126" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="K126" s="3" t="s">
+      <c r="L126" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="L126" s="3" t="s">
+      <c r="M126" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="M126" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N126" s="3" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A127" s="2">
         <v>125</v>
       </c>
@@ -8083,20 +8466,23 @@
       <c r="I127" s="2">
         <v>18</v>
       </c>
-      <c r="J127" s="3" t="s">
+      <c r="J127" s="8">
+        <v>0</v>
+      </c>
+      <c r="K127" s="3" t="s">
         <v>610</v>
       </c>
-      <c r="K127" s="3" t="s">
+      <c r="L127" s="3" t="s">
         <v>611</v>
       </c>
-      <c r="L127" s="3" t="s">
+      <c r="M127" s="3" t="s">
         <v>612</v>
       </c>
-      <c r="M127" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N127" s="3" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A128" s="2">
         <v>126</v>
       </c>
@@ -8124,20 +8510,23 @@
       <c r="I128" s="2">
         <v>39</v>
       </c>
-      <c r="J128" s="3" t="s">
+      <c r="J128" s="8">
+        <v>0</v>
+      </c>
+      <c r="K128" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="K128" s="3" t="s">
+      <c r="L128" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="L128" s="3" t="s">
+      <c r="M128" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="M128" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N128" s="3" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A129" s="2">
         <v>127</v>
       </c>
@@ -8165,20 +8554,23 @@
       <c r="I129" s="2">
         <v>16</v>
       </c>
-      <c r="J129" s="3" t="s">
+      <c r="J129" s="8">
+        <v>0</v>
+      </c>
+      <c r="K129" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="K129" s="3" t="s">
+      <c r="L129" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="L129" s="3" t="s">
+      <c r="M129" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="M129" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N129" s="3" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A130" s="2">
         <v>128</v>
       </c>
@@ -8206,20 +8598,23 @@
       <c r="I130" s="2">
         <v>56</v>
       </c>
-      <c r="J130" s="3" t="s">
+      <c r="J130" s="8">
+        <v>0</v>
+      </c>
+      <c r="K130" s="3" t="s">
         <v>589</v>
       </c>
-      <c r="K130" s="3" t="s">
+      <c r="L130" s="3" t="s">
         <v>590</v>
       </c>
-      <c r="L130" s="3" t="s">
+      <c r="M130" s="3" t="s">
         <v>591</v>
       </c>
-      <c r="M130" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N130" s="3" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A131" s="2">
         <v>129</v>
       </c>
@@ -8247,20 +8642,23 @@
       <c r="I131" s="2">
         <v>12</v>
       </c>
-      <c r="J131" s="3" t="s">
+      <c r="J131" s="8">
+        <v>0</v>
+      </c>
+      <c r="K131" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="K131" s="3" t="s">
+      <c r="L131" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="L131" s="3" t="s">
+      <c r="M131" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="M131" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N131" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A132" s="2">
         <v>130</v>
       </c>
@@ -8288,20 +8686,23 @@
       <c r="I132" s="2">
         <v>13</v>
       </c>
-      <c r="J132" s="3" t="s">
+      <c r="J132" s="8">
+        <v>0</v>
+      </c>
+      <c r="K132" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="K132" s="3" t="s">
+      <c r="L132" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="L132" s="3" t="s">
+      <c r="M132" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="M132" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N132" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A133" s="2">
         <v>131</v>
       </c>
@@ -8329,20 +8730,23 @@
       <c r="I133" s="2">
         <v>48</v>
       </c>
-      <c r="J133" s="3" t="s">
+      <c r="J133" s="8">
+        <v>0</v>
+      </c>
+      <c r="K133" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="K133" s="3" t="s">
+      <c r="L133" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="L133" s="3" t="s">
+      <c r="M133" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="M133" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N133" s="3" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A134" s="2">
         <v>132</v>
       </c>
@@ -8370,20 +8774,23 @@
       <c r="I134" s="2">
         <v>32</v>
       </c>
-      <c r="J134" s="3" t="s">
+      <c r="J134" s="8">
+        <v>0</v>
+      </c>
+      <c r="K134" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="K134" s="3" t="s">
+      <c r="L134" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="L134" s="3" t="s">
+      <c r="M134" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="M134" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N134" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A135" s="2">
         <v>133</v>
       </c>
@@ -8411,106 +8818,109 @@
       <c r="I135" s="2">
         <v>2</v>
       </c>
-      <c r="J135" s="3" t="s">
+      <c r="J135" s="8">
+        <v>0</v>
+      </c>
+      <c r="K135" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="K135" s="3" t="s">
+      <c r="L135" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="L135" s="3" t="s">
+      <c r="M135" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="M135" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N135" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F136" s="12"/>
       <c r="G136" s="12"/>
       <c r="H136" s="12"/>
       <c r="I136" s="12"/>
-      <c r="J136" s="14"/>
-      <c r="K136" s="12"/>
+      <c r="J136" s="12"/>
+      <c r="K136" s="14"/>
       <c r="L136" s="12"/>
       <c r="M136" s="12"/>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F137" s="12"/>
       <c r="G137" s="12"/>
       <c r="H137" s="12"/>
       <c r="I137" s="12"/>
-      <c r="J137" s="14"/>
-      <c r="K137" s="12"/>
+      <c r="J137" s="12"/>
+      <c r="K137" s="14"/>
       <c r="L137" s="12"/>
       <c r="M137" s="12"/>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F138" s="12"/>
       <c r="G138" s="12"/>
       <c r="H138" s="12"/>
       <c r="I138" s="12"/>
-      <c r="J138" s="14"/>
-      <c r="K138" s="12"/>
+      <c r="J138" s="12"/>
+      <c r="K138" s="14"/>
       <c r="L138" s="12"/>
       <c r="M138" s="12"/>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F139" s="12"/>
       <c r="G139" s="12"/>
       <c r="H139" s="12"/>
       <c r="I139" s="12"/>
-      <c r="J139" s="14"/>
-      <c r="K139" s="12"/>
+      <c r="J139" s="12"/>
+      <c r="K139" s="14"/>
       <c r="L139" s="12"/>
       <c r="M139" s="12"/>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F140" s="12"/>
       <c r="G140" s="12"/>
       <c r="H140" s="12"/>
       <c r="I140" s="12"/>
-      <c r="J140" s="14"/>
-      <c r="K140" s="12"/>
+      <c r="J140" s="12"/>
+      <c r="K140" s="14"/>
       <c r="L140" s="12"/>
       <c r="M140" s="12"/>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F141" s="12"/>
       <c r="G141" s="12"/>
       <c r="H141" s="12"/>
       <c r="I141" s="12"/>
-      <c r="J141" s="14"/>
-      <c r="K141" s="12"/>
+      <c r="J141" s="12"/>
+      <c r="K141" s="14"/>
       <c r="L141" s="12"/>
       <c r="M141" s="12"/>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F142" s="12"/>
       <c r="G142" s="12"/>
       <c r="H142" s="12"/>
       <c r="I142" s="12"/>
-      <c r="J142" s="14"/>
-      <c r="K142" s="12"/>
+      <c r="J142" s="12"/>
+      <c r="K142" s="14"/>
       <c r="L142" s="12"/>
       <c r="M142" s="12"/>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F143" s="12"/>
       <c r="G143" s="12"/>
       <c r="H143" s="12"/>
       <c r="I143" s="12"/>
-      <c r="J143" s="14"/>
-      <c r="K143" s="12"/>
+      <c r="J143" s="12"/>
+      <c r="K143" s="14"/>
       <c r="L143" s="12"/>
       <c r="M143" s="12"/>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F144" s="12"/>
       <c r="G144" s="12"/>
       <c r="H144" s="12"/>
       <c r="I144" s="12"/>
-      <c r="J144" s="14"/>
-      <c r="K144" s="12"/>
+      <c r="J144" s="12"/>
+      <c r="K144" s="14"/>
       <c r="L144" s="12"/>
       <c r="M144" s="12"/>
     </row>
@@ -8519,92 +8929,87 @@
       <c r="G145" s="12"/>
       <c r="H145" s="12"/>
       <c r="I145" s="12"/>
-      <c r="J145" s="14"/>
-      <c r="K145" s="12"/>
+      <c r="J145" s="12"/>
+      <c r="K145" s="14"/>
       <c r="L145" s="12"/>
       <c r="M145" s="12"/>
     </row>
     <row r="146" spans="6:13" x14ac:dyDescent="0.3">
-      <c r="J146" s="6"/>
       <c r="K146" s="6"/>
       <c r="L146" s="6"/>
+      <c r="M146" s="6"/>
     </row>
     <row r="147" spans="6:13" x14ac:dyDescent="0.3">
-      <c r="J147" s="6"/>
       <c r="K147" s="6"/>
       <c r="L147" s="6"/>
+      <c r="M147" s="6"/>
     </row>
     <row r="148" spans="6:13" x14ac:dyDescent="0.3">
-      <c r="J148" s="6"/>
       <c r="K148" s="6"/>
       <c r="L148" s="6"/>
+      <c r="M148" s="6"/>
     </row>
     <row r="149" spans="6:13" x14ac:dyDescent="0.3">
-      <c r="J149" s="6"/>
       <c r="K149" s="6"/>
       <c r="L149" s="6"/>
+      <c r="M149" s="6"/>
     </row>
     <row r="150" spans="6:13" x14ac:dyDescent="0.3">
-      <c r="J150" s="6"/>
       <c r="K150" s="6"/>
       <c r="L150" s="6"/>
+      <c r="M150" s="6"/>
     </row>
     <row r="151" spans="6:13" x14ac:dyDescent="0.3">
-      <c r="J151" s="6"/>
       <c r="K151" s="6"/>
       <c r="L151" s="6"/>
+      <c r="M151" s="6"/>
     </row>
     <row r="152" spans="6:13" x14ac:dyDescent="0.3">
-      <c r="J152" s="6"/>
       <c r="K152" s="6"/>
       <c r="L152" s="6"/>
+      <c r="M152" s="6"/>
     </row>
     <row r="153" spans="6:13" x14ac:dyDescent="0.3">
-      <c r="J153" s="6"/>
       <c r="K153" s="6"/>
       <c r="L153" s="6"/>
+      <c r="M153" s="6"/>
     </row>
     <row r="154" spans="6:13" x14ac:dyDescent="0.3">
-      <c r="J154" s="6"/>
       <c r="K154" s="6"/>
       <c r="L154" s="6"/>
+      <c r="M154" s="6"/>
     </row>
     <row r="155" spans="6:13" x14ac:dyDescent="0.3">
-      <c r="J155" s="6"/>
       <c r="K155" s="6"/>
       <c r="L155" s="6"/>
+      <c r="M155" s="6"/>
     </row>
     <row r="156" spans="6:13" x14ac:dyDescent="0.3">
-      <c r="J156" s="6"/>
       <c r="K156" s="6"/>
       <c r="L156" s="6"/>
+      <c r="M156" s="6"/>
     </row>
     <row r="157" spans="6:13" x14ac:dyDescent="0.3">
-      <c r="J157" s="6"/>
       <c r="K157" s="6"/>
       <c r="L157" s="6"/>
+      <c r="M157" s="6"/>
     </row>
     <row r="158" spans="6:13" x14ac:dyDescent="0.3">
-      <c r="J158" s="6"/>
       <c r="K158" s="6"/>
       <c r="L158" s="6"/>
+      <c r="M158" s="6"/>
     </row>
     <row r="159" spans="6:13" x14ac:dyDescent="0.3">
-      <c r="J159" s="6"/>
       <c r="K159" s="6"/>
       <c r="L159" s="6"/>
+      <c r="M159" s="6"/>
     </row>
     <row r="160" spans="6:13" x14ac:dyDescent="0.3">
-      <c r="J160" s="6"/>
       <c r="K160" s="6"/>
       <c r="L160" s="6"/>
+      <c r="M160" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M8" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M136">
-      <sortCondition ref="A1:A8"/>
-    </sortState>
-  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -5,16 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Confidential\Gathering_Island\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCreation\Web\Gathering_Island\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7950B90F-36BE-404B-B3E8-DE06B43B21F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3B469AC-BA91-46F0-AEFA-BF125FCEF860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28350" yWindow="4080" windowWidth="19725" windowHeight="10830" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="events" sheetId="1" r:id="rId1"/>
-    <sheet name="工作表1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0">events!$A$1:$M$8</definedName>
@@ -54,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1115" uniqueCount="677">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="670">
   <si>
     <t>event_id</t>
   </si>
@@ -1993,30 +1992,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>event_description</t>
-  </si>
-  <si>
-    <t>要不要來學AI（有冷氣）</t>
-  </si>
-  <si>
     <t>很怕報名的人都跑了所以先說：前面會有吃的，然後才是講座。一起坐一起滑手機也可以。</t>
   </si>
   <si>
-    <t>北海道泡湯團（雪厚到爆）</t>
-  </si>
-  <si>
     <t>純粹想泡湯，有人要跟嗎？白天行程我應該會亂走一通。</t>
   </si>
   <si>
-    <t>攝影展揪一波（不保證會看懂）</t>
-  </si>
-  <si>
     <t>主揪可能只會拍人，不一定在看展，想來亂晃的可以+1。</t>
   </si>
   <si>
-    <t>啤酒節生死鬥</t>
-  </si>
-  <si>
     <t>去年被灌到回不了家，今年打算吃東西為主，誰要來幫顧戰力。</t>
   </si>
   <si>
@@ -2026,13 +2010,7 @@
     <t>有點後悔自己排這麼滿的行程，但錢都繳了只能硬著頭皮揪人了。</t>
   </si>
   <si>
-    <t>部門耶誕交換禮物（二刷）</t>
-  </si>
-  <si>
     <t>我們部門自己辦的，可以帶朋友來！但先說活動很吵XD</t>
-  </si>
-  <si>
-    <t>吃吃找找行軍賽（超級混亂）</t>
   </si>
   <si>
     <t>這不是什麼正經活動，單純揪大家一起吃+迷路，怕吵勿報。</t>
@@ -2651,7 +2629,7 @@
         <v>24</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>676</v>
+        <v>669</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
@@ -2695,7 +2673,7 @@
         <v>178</v>
       </c>
       <c r="N2" s="10" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
@@ -2703,10 +2681,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>639</v>
+        <v>632</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="D3" s="2">
         <v>3</v>
@@ -2730,16 +2708,16 @@
         <v>0</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>646</v>
+        <v>639</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="O3" s="13"/>
       <c r="P3" s="13"/>
@@ -2749,10 +2727,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>640</v>
+        <v>633</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="D4" s="2">
         <v>5</v>
@@ -2776,16 +2754,16 @@
         <v>0</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>649</v>
+        <v>642</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
@@ -2796,10 +2774,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>641</v>
+        <v>634</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="D5" s="2">
         <v>4</v>
@@ -2823,16 +2801,16 @@
         <v>0</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>652</v>
+        <v>645</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
       <c r="O5" s="7"/>
       <c r="P5" s="7"/>
@@ -2843,10 +2821,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="D6" s="2">
         <v>8</v>
@@ -2870,16 +2848,16 @@
         <v>0</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
@@ -2890,10 +2868,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="D7" s="2">
         <v>5</v>
@@ -2917,16 +2895,16 @@
         <v>0</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>657</v>
+        <v>650</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>658</v>
+        <v>651</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
@@ -2934,10 +2912,10 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>643</v>
+        <v>636</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>
@@ -2961,16 +2939,16 @@
         <v>0</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>662</v>
+        <v>655</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>662</v>
+        <v>655</v>
       </c>
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
@@ -2981,10 +2959,10 @@
         <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>632</v>
+        <v>625</v>
       </c>
       <c r="D9" s="2">
         <v>7</v>
@@ -3008,16 +2986,16 @@
         <v>0</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>663</v>
+        <v>656</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="O9" s="7"/>
       <c r="P9" s="7"/>
@@ -3028,10 +3006,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>633</v>
+        <v>626</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>634</v>
+        <v>627</v>
       </c>
       <c r="D10" s="2">
         <v>3</v>
@@ -3055,16 +3033,16 @@
         <v>0</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>668</v>
+        <v>661</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>668</v>
+        <v>661</v>
       </c>
       <c r="O10" s="7"/>
       <c r="P10" s="7"/>
@@ -3075,10 +3053,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>635</v>
+        <v>628</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>636</v>
+        <v>629</v>
       </c>
       <c r="D11" s="2">
         <v>1</v>
@@ -3102,16 +3080,16 @@
         <v>0</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>671</v>
+        <v>664</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>671</v>
+        <v>664</v>
       </c>
       <c r="O11" s="7"/>
       <c r="P11" s="7"/>
@@ -3122,10 +3100,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>637</v>
+        <v>630</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="D12" s="2">
         <v>3</v>
@@ -3149,16 +3127,16 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>672</v>
+        <v>665</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>673</v>
+        <v>666</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="O12" s="7"/>
       <c r="P12" s="7"/>
@@ -9015,136 +8993,4 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55C6109F-48BB-4C16-92DE-F0286B802B61}">
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>619</v>
-      </c>
-      <c r="C2" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>621</v>
-      </c>
-      <c r="C3" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>623</v>
-      </c>
-      <c r="C4" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>625</v>
-      </c>
-      <c r="C5" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>627</v>
-      </c>
-      <c r="C6" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>629</v>
-      </c>
-      <c r="C7" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>631</v>
-      </c>
-      <c r="C8" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>633</v>
-      </c>
-      <c r="C9" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>635</v>
-      </c>
-      <c r="C10" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>637</v>
-      </c>
-      <c r="C11" t="s">
-        <v>638</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>